--- a/research/traditional_assets/database/data/argentina/argentina_oil_gas_integrated.xlsx
+++ b/research/traditional_assets/database/data/argentina/argentina_oil_gas_integrated.xlsx
@@ -641,10 +641,10 @@
         <v>0.07147677939513335</v>
       </c>
       <c r="X2">
-        <v>0.2958235815810246</v>
+        <v>0.2958849348805305</v>
       </c>
       <c r="Y2">
-        <v>-0.2243468021858913</v>
+        <v>-0.2244081554853971</v>
       </c>
       <c r="Z2">
         <v>0.8546252384846007</v>
@@ -653,10 +653,10 @@
         <v>0.1042300354319978</v>
       </c>
       <c r="AB2">
-        <v>0.2497103910093251</v>
+        <v>0.2497517474304445</v>
       </c>
       <c r="AC2">
-        <v>-0.1454803555773273</v>
+        <v>-0.1455217119984467</v>
       </c>
       <c r="AD2">
         <v>9278.9</v>
@@ -769,10 +769,10 @@
         <v>0.07147677939513335</v>
       </c>
       <c r="X3">
-        <v>0.2958235815810246</v>
+        <v>0.2958849348805305</v>
       </c>
       <c r="Y3">
-        <v>-0.2243468021858913</v>
+        <v>-0.2244081554853971</v>
       </c>
       <c r="Z3">
         <v>0.8546252384846007</v>
@@ -781,10 +781,10 @@
         <v>0.1042300354319978</v>
       </c>
       <c r="AB3">
-        <v>0.2497103910093251</v>
+        <v>0.2497517474304445</v>
       </c>
       <c r="AC3">
-        <v>-0.1454803555773273</v>
+        <v>-0.1455217119984467</v>
       </c>
       <c r="AD3">
         <v>9278.9</v>
@@ -1121,7 +1121,7 @@
         <v>3.08751816567092</v>
       </c>
       <c r="F2">
-        <v>10.2530660634676</v>
+        <v>10.3379280181065</v>
       </c>
       <c r="G2">
         <v>2.39128417905832</v>
@@ -1139,13 +1139,13 @@
         <v>19190.1</v>
       </c>
       <c r="L2">
-        <v>29323.409571282</v>
+        <v>29327.9120821097</v>
       </c>
       <c r="M2">
         <v>27593.4</v>
       </c>
       <c r="N2">
-        <v>29586.569571282</v>
+        <v>29591.0720821097</v>
       </c>
       <c r="O2">
         <v>9278.9</v>
@@ -1154,16 +1154,16 @@
         <v>1138.76</v>
       </c>
       <c r="Q2">
-        <v>0.249710391009325</v>
+        <v>0.249751747430444</v>
       </c>
       <c r="R2">
-        <v>0.235973482928487</v>
+        <v>0.23598311103874</v>
       </c>
       <c r="S2">
         <v>0.154341679374328</v>
       </c>
       <c r="T2">
-        <v>0.110856679374328</v>
+        <v>0.109946679374328</v>
       </c>
       <c r="U2" t="inlineStr">
         <is>
@@ -1176,10 +1176,10 @@
         </is>
       </c>
       <c r="W2">
-        <v>0.295823581581025</v>
+        <v>0.29588493488053</v>
       </c>
       <c r="X2">
-        <v>0.241186683076577</v>
+        <v>0.241234629024757</v>
       </c>
       <c r="Y2">
         <v>1.22876036297249</v>
@@ -1218,7 +1218,7 @@
         <v>19190.1</v>
       </c>
       <c r="AK2">
-        <v>0.2034762750453591</v>
+        <v>0.2035262060989271</v>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
@@ -1406,13 +1406,13 @@
         <v>0</v>
       </c>
       <c r="B2">
-        <v>0.2360344987358157</v>
+        <v>0.236081180389216</v>
       </c>
       <c r="C2">
-        <v>30452.67997585922</v>
+        <v>30451.42108769686</v>
       </c>
       <c r="D2">
-        <v>29577.07997585923</v>
+        <v>29575.82108769687</v>
       </c>
       <c r="E2">
         <v>-9278.9</v>
@@ -1457,19 +1457,19 @@
         <v>0</v>
       </c>
       <c r="S2">
-        <v>0.2360344987358157</v>
+        <v>0.236081180389216</v>
       </c>
       <c r="T2">
         <v>0.9349222590860211</v>
       </c>
       <c r="U2">
-        <v>0.1705487374989668</v>
+        <v>0.1691487374989669</v>
       </c>
       <c r="V2">
         <v>0.35</v>
       </c>
       <c r="W2">
-        <v>0.1108566793743285</v>
+        <v>0.1099466793743285</v>
       </c>
       <c r="X2" t="inlineStr">
         <is>
@@ -1488,13 +1488,13 @@
         <v>0.01</v>
       </c>
       <c r="B3">
-        <v>0.2360192447839836</v>
+        <v>0.2360566630515971</v>
       </c>
       <c r="C3">
-        <v>30170.36180397682</v>
+        <v>30170.54236231577</v>
       </c>
       <c r="D3">
-        <v>29579.45180397682</v>
+        <v>29579.63236231577</v>
       </c>
       <c r="E3">
         <v>-8994.209999999999</v>
@@ -1521,37 +1521,37 @@
         <v>1991.289795918367</v>
       </c>
       <c r="M3">
-        <v>48.55352007858087</v>
+        <v>48.15495407858088</v>
       </c>
       <c r="N3">
-        <v>1942.736275839786</v>
+        <v>1943.134841839787</v>
       </c>
       <c r="O3">
-        <v>679.9576965439252</v>
+        <v>680.0971946439253</v>
       </c>
       <c r="P3">
-        <v>1262.778579295861</v>
+        <v>1263.037647195861</v>
       </c>
       <c r="Q3">
-        <v>3230.978579295861</v>
+        <v>3231.237647195861</v>
       </c>
       <c r="R3">
         <v>0.0101010101010101</v>
       </c>
       <c r="S3">
-        <v>0.2372835131214549</v>
+        <v>0.2373305012705594</v>
       </c>
       <c r="T3">
         <v>0.9410606375547678</v>
       </c>
       <c r="U3">
-        <v>0.1705487374989668</v>
+        <v>0.1691487374989669</v>
       </c>
       <c r="V3">
         <v>0.35</v>
       </c>
       <c r="W3">
-        <v>0.1108566793743285</v>
+        <v>0.1099466793743285</v>
       </c>
       <c r="X3" t="inlineStr">
         <is>
@@ -1559,7 +1559,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>41.01226425387053</v>
+        <v>41.35171207242589</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1570,13 +1570,13 @@
         <v>0.02</v>
       </c>
       <c r="B4">
-        <v>0.2360039908321516</v>
+        <v>0.2360321457139781</v>
       </c>
       <c r="C4">
-        <v>29888.04401252545</v>
+        <v>29889.66461933757</v>
       </c>
       <c r="D4">
-        <v>29581.82401252545</v>
+        <v>29583.44461933757</v>
       </c>
       <c r="E4">
         <v>-8709.52</v>
@@ -1603,37 +1603,37 @@
         <v>1991.289795918367</v>
       </c>
       <c r="M4">
-        <v>97.10704015716175</v>
+        <v>96.30990815716176</v>
       </c>
       <c r="N4">
-        <v>1894.182755761206</v>
+        <v>1894.979887761206</v>
       </c>
       <c r="O4">
-        <v>662.9639645164219</v>
+        <v>663.242960716422</v>
       </c>
       <c r="P4">
-        <v>1231.218791244784</v>
+        <v>1231.736927044784</v>
       </c>
       <c r="Q4">
-        <v>3199.418791244784</v>
+        <v>3199.936927044784</v>
       </c>
       <c r="R4">
         <v>0.02040816326530612</v>
       </c>
       <c r="S4">
-        <v>0.2385580175965969</v>
+        <v>0.2386053184964199</v>
       </c>
       <c r="T4">
         <v>0.9473242890534888</v>
       </c>
       <c r="U4">
-        <v>0.1705487374989668</v>
+        <v>0.1691487374989669</v>
       </c>
       <c r="V4">
         <v>0.35</v>
       </c>
       <c r="W4">
-        <v>0.1108566793743285</v>
+        <v>0.1099466793743285</v>
       </c>
       <c r="X4" t="inlineStr">
         <is>
@@ -1641,7 +1641,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>20.50613212693527</v>
+        <v>20.67585603621295</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1652,13 +1652,13 @@
         <v>0.03</v>
       </c>
       <c r="B5">
-        <v>0.2359887368803195</v>
+        <v>0.2360076283763591</v>
       </c>
       <c r="C5">
-        <v>29605.72660159667</v>
+        <v>29608.78785914218</v>
       </c>
       <c r="D5">
-        <v>29584.19660159668</v>
+        <v>29587.25785914218</v>
       </c>
       <c r="E5">
         <v>-8424.83</v>
@@ -1685,37 +1685,37 @@
         <v>1991.289795918367</v>
       </c>
       <c r="M5">
-        <v>145.6605602357426</v>
+        <v>144.4648622357426</v>
       </c>
       <c r="N5">
-        <v>1845.629235682625</v>
+        <v>1846.824933682625</v>
       </c>
       <c r="O5">
-        <v>645.9702324889187</v>
+        <v>646.3887267889186</v>
       </c>
       <c r="P5">
-        <v>1199.659003193706</v>
+        <v>1200.436206893706</v>
       </c>
       <c r="Q5">
-        <v>3167.859003193706</v>
+        <v>3168.636206893706</v>
       </c>
       <c r="R5">
         <v>0.03092783505154639</v>
       </c>
       <c r="S5">
-        <v>0.2398588005145254</v>
+        <v>0.2399064206135353</v>
       </c>
       <c r="T5">
         <v>0.9537170880057916</v>
       </c>
       <c r="U5">
-        <v>0.1705487374989668</v>
+        <v>0.1691487374989669</v>
       </c>
       <c r="V5">
         <v>0.35</v>
       </c>
       <c r="W5">
-        <v>0.1108566793743285</v>
+        <v>0.1099466793743285</v>
       </c>
       <c r="X5" t="inlineStr">
         <is>
@@ -1723,7 +1723,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>13.67075475129018</v>
+        <v>13.78390402414196</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1734,13 +1734,13 @@
         <v>0.04</v>
       </c>
       <c r="B6">
-        <v>0.2359734829284874</v>
+        <v>0.2359831110387402</v>
       </c>
       <c r="C6">
-        <v>29323.40957128205</v>
+        <v>29327.91208210967</v>
       </c>
       <c r="D6">
-        <v>29586.56957128205</v>
+        <v>29591.07208210967</v>
       </c>
       <c r="E6">
         <v>-8140.139999999999</v>
@@ -1767,37 +1767,37 @@
         <v>1991.289795918367</v>
       </c>
       <c r="M6">
-        <v>194.2140803143235</v>
+        <v>192.6198163143235</v>
       </c>
       <c r="N6">
-        <v>1797.075715604044</v>
+        <v>1798.669979604044</v>
       </c>
       <c r="O6">
-        <v>628.9765004614154</v>
+        <v>629.5344928614153</v>
       </c>
       <c r="P6">
-        <v>1168.099215142629</v>
+        <v>1169.135486742628</v>
       </c>
       <c r="Q6">
-        <v>3136.299215142629</v>
+        <v>3137.335486742629</v>
       </c>
       <c r="R6">
         <v>0.04166666666666667</v>
       </c>
       <c r="S6">
-        <v>0.2411866830765774</v>
+        <v>0.2412346290247573</v>
       </c>
       <c r="T6">
         <v>0.9602430702696009</v>
       </c>
       <c r="U6">
-        <v>0.1705487374989668</v>
+        <v>0.1691487374989669</v>
       </c>
       <c r="V6">
         <v>0.35</v>
       </c>
       <c r="W6">
-        <v>0.1108566793743285</v>
+        <v>0.1099466793743285</v>
       </c>
       <c r="X6" t="inlineStr">
         <is>
@@ -1805,7 +1805,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>10.25306606346763</v>
+        <v>10.33792801810647</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1816,13 +1816,13 @@
         <v>0.05</v>
       </c>
       <c r="B7">
-        <v>0.2359939789766553</v>
+        <v>0.2360073437011212</v>
       </c>
       <c r="C7">
-        <v>29035.5312066539</v>
+        <v>29039.45214113207</v>
       </c>
       <c r="D7">
-        <v>29583.3812066539</v>
+        <v>29587.30214113207</v>
       </c>
       <c r="E7">
         <v>-7855.45</v>
@@ -1849,37 +1849,37 @@
         <v>1991.289795918367</v>
       </c>
       <c r="M7">
-        <v>244.3333953929044</v>
+        <v>242.9099453929044</v>
       </c>
       <c r="N7">
-        <v>1746.956400525463</v>
+        <v>1748.379850525463</v>
       </c>
       <c r="O7">
-        <v>611.434740183912</v>
+        <v>611.9329476839121</v>
       </c>
       <c r="P7">
-        <v>1135.521660341551</v>
+        <v>1136.446902841551</v>
       </c>
       <c r="Q7">
-        <v>3103.721660341551</v>
+        <v>3104.646902841551</v>
       </c>
       <c r="R7">
         <v>0.05263157894736843</v>
       </c>
       <c r="S7">
-        <v>0.2425425210609883</v>
+        <v>0.2425907997183208</v>
       </c>
       <c r="T7">
         <v>0.9669064416337008</v>
       </c>
       <c r="U7">
-        <v>0.1716487374989669</v>
+        <v>0.1706487374989669</v>
       </c>
       <c r="V7">
         <v>0.35</v>
       </c>
       <c r="W7">
-        <v>0.1115716793743285</v>
+        <v>0.1109216793743285</v>
       </c>
       <c r="X7" t="inlineStr">
         <is>
@@ -1887,7 +1887,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>8.149887954187518</v>
+        <v>8.197646221102541</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1898,13 +1898,13 @@
         <v>0.06</v>
       </c>
       <c r="B8">
-        <v>0.2359858750248233</v>
+        <v>0.2359925763635022</v>
       </c>
       <c r="C8">
-        <v>28752.1017750126</v>
+        <v>28757.05942154284</v>
       </c>
       <c r="D8">
-        <v>29584.6417750126</v>
+        <v>29589.59942154284</v>
       </c>
       <c r="E8">
         <v>-7570.76</v>
@@ -1931,37 +1931,37 @@
         <v>1991.289795918367</v>
       </c>
       <c r="M8">
-        <v>293.2000744714852</v>
+        <v>291.4919344714853</v>
       </c>
       <c r="N8">
-        <v>1698.089721446882</v>
+        <v>1699.797861446882</v>
       </c>
       <c r="O8">
-        <v>594.3314025064087</v>
+        <v>594.9292515064087</v>
       </c>
       <c r="P8">
-        <v>1103.758318940474</v>
+        <v>1104.868609940473</v>
       </c>
       <c r="Q8">
-        <v>3071.958318940474</v>
+        <v>3073.068609940474</v>
       </c>
       <c r="R8">
         <v>0.06382978723404255</v>
       </c>
       <c r="S8">
-        <v>0.2439272066620889</v>
+        <v>0.2439758251074921</v>
       </c>
       <c r="T8">
         <v>0.9737115868566114</v>
       </c>
       <c r="U8">
-        <v>0.1716487374989669</v>
+        <v>0.1706487374989669</v>
       </c>
       <c r="V8">
         <v>0.35</v>
       </c>
       <c r="W8">
-        <v>0.1115716793743285</v>
+        <v>0.1109216793743285</v>
       </c>
       <c r="X8" t="inlineStr">
         <is>
@@ -1969,7 +1969,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>6.791573295156266</v>
+        <v>6.831371850918785</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1980,13 +1980,13 @@
         <v>0.07000000000000001</v>
       </c>
       <c r="B9">
-        <v>0.2360778710729912</v>
+        <v>0.2360551590258833</v>
       </c>
       <c r="C9">
-        <v>28453.10811419057</v>
+        <v>28462.63619843304</v>
       </c>
       <c r="D9">
-        <v>29570.33811419058</v>
+        <v>29579.86619843304</v>
       </c>
       <c r="E9">
         <v>-7286.07</v>
@@ -2013,37 +2013,37 @@
         <v>1991.289795918367</v>
       </c>
       <c r="M9">
-        <v>346.4509795500661</v>
+        <v>343.4617345500662</v>
       </c>
       <c r="N9">
-        <v>1644.838816368301</v>
+        <v>1647.828061368301</v>
       </c>
       <c r="O9">
-        <v>575.6935857289054</v>
+        <v>576.7398214789054</v>
       </c>
       <c r="P9">
-        <v>1069.145230639396</v>
+        <v>1071.088239889396</v>
       </c>
       <c r="Q9">
-        <v>3037.345230639396</v>
+        <v>3039.288239889396</v>
       </c>
       <c r="R9">
         <v>0.07526881720430109</v>
       </c>
       <c r="S9">
-        <v>0.2453416704481594</v>
+        <v>0.2453906359889035</v>
       </c>
       <c r="T9">
         <v>0.9806630792886167</v>
       </c>
       <c r="U9">
-        <v>0.1738487374989668</v>
+        <v>0.1723487374989669</v>
       </c>
       <c r="V9">
         <v>0.35</v>
       </c>
       <c r="W9">
-        <v>0.1130016793743285</v>
+        <v>0.1120266793743285</v>
       </c>
       <c r="X9" t="inlineStr">
         <is>
@@ -2051,7 +2051,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>5.747681240516173</v>
+        <v>5.797704942377208</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2062,13 +2062,13 @@
         <v>0.08</v>
       </c>
       <c r="B10">
-        <v>0.2361620671211591</v>
+        <v>0.2360930416882643</v>
       </c>
       <c r="C10">
-        <v>28155.33932360033</v>
+        <v>28172.05757489468</v>
       </c>
       <c r="D10">
-        <v>29557.25932360033</v>
+        <v>29573.97757489468</v>
       </c>
       <c r="E10">
         <v>-7001.379999999999</v>
@@ -2095,37 +2095,37 @@
         <v>1991.289795918367</v>
       </c>
       <c r="M10">
-        <v>399.3602566286469</v>
+        <v>394.349712628647</v>
       </c>
       <c r="N10">
-        <v>1591.92953928972</v>
+        <v>1596.94008328972</v>
       </c>
       <c r="O10">
-        <v>557.1753387514021</v>
+        <v>558.9290291514021</v>
       </c>
       <c r="P10">
-        <v>1034.754200538318</v>
+        <v>1038.011054138318</v>
       </c>
       <c r="Q10">
-        <v>3002.954200538319</v>
+        <v>3006.211054138319</v>
       </c>
       <c r="R10">
         <v>0.08695652173913043</v>
       </c>
       <c r="S10">
-        <v>0.2467868834469705</v>
+        <v>0.2468362036286065</v>
       </c>
       <c r="T10">
         <v>0.9877656911213178</v>
       </c>
       <c r="U10">
-        <v>0.1753487374989668</v>
+        <v>0.1731487374989669</v>
       </c>
       <c r="V10">
         <v>0.35</v>
       </c>
       <c r="W10">
-        <v>0.1139766793743285</v>
+        <v>0.1125466793743285</v>
       </c>
       <c r="X10" t="inlineStr">
         <is>
@@ -2133,7 +2133,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>4.986199209527271</v>
+        <v>5.049553054432003</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2144,13 +2144,13 @@
         <v>0.09</v>
       </c>
       <c r="B11">
-        <v>0.2361780131693271</v>
+        <v>0.2360945243506453</v>
       </c>
       <c r="C11">
-        <v>27868.17360976636</v>
+        <v>27887.13715195342</v>
       </c>
       <c r="D11">
-        <v>29554.78360976636</v>
+        <v>29573.74715195342</v>
       </c>
       <c r="E11">
         <v>-6716.69</v>
@@ -2177,37 +2177,37 @@
         <v>1991.289795918367</v>
       </c>
       <c r="M11">
-        <v>449.2802887072278</v>
+        <v>443.6434267072279</v>
       </c>
       <c r="N11">
-        <v>1542.00950721114</v>
+        <v>1547.646369211139</v>
       </c>
       <c r="O11">
-        <v>539.7033275238988</v>
+        <v>541.6762292238988</v>
       </c>
       <c r="P11">
-        <v>1002.306179687241</v>
+        <v>1005.970139987241</v>
       </c>
       <c r="Q11">
-        <v>2970.506179687241</v>
+        <v>2974.170139987241</v>
       </c>
       <c r="R11">
         <v>0.0989010989010989</v>
       </c>
       <c r="S11">
-        <v>0.2482638593688324</v>
+        <v>0.2483135419856657</v>
       </c>
       <c r="T11">
         <v>0.9950244043129796</v>
       </c>
       <c r="U11">
-        <v>0.1753487374989668</v>
+        <v>0.1731487374989669</v>
       </c>
       <c r="V11">
         <v>0.35</v>
       </c>
       <c r="W11">
-        <v>0.1139766793743285</v>
+        <v>0.1125466793743285</v>
       </c>
       <c r="X11" t="inlineStr">
         <is>
@@ -2215,7 +2215,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>4.432177075135352</v>
+        <v>4.488491603939559</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2226,13 +2226,13 @@
         <v>0.1</v>
       </c>
       <c r="B12">
-        <v>0.236284959217495</v>
+        <v>0.2361610070130264</v>
       </c>
       <c r="C12">
-        <v>27566.89034526659</v>
+        <v>27592.11866358231</v>
       </c>
       <c r="D12">
-        <v>29538.1903452666</v>
+        <v>29563.41866358231</v>
       </c>
       <c r="E12">
         <v>-6432</v>
@@ -2259,37 +2259,37 @@
         <v>1991.289795918367</v>
       </c>
       <c r="M12">
-        <v>503.1859807858087</v>
+        <v>495.7840407858088</v>
       </c>
       <c r="N12">
-        <v>1488.103815132559</v>
+        <v>1495.505755132559</v>
       </c>
       <c r="O12">
-        <v>520.8363352963955</v>
+        <v>523.4270142963954</v>
       </c>
       <c r="P12">
-        <v>967.2674798361633</v>
+        <v>972.0787408361631</v>
       </c>
       <c r="Q12">
-        <v>2935.467479836163</v>
+        <v>2940.278740836163</v>
       </c>
       <c r="R12">
         <v>0.1111111111111111</v>
       </c>
       <c r="S12">
-        <v>0.2497736569778468</v>
+        <v>0.2498237100839928</v>
       </c>
       <c r="T12">
         <v>1.002444422242234</v>
       </c>
       <c r="U12">
-        <v>0.1767487374989669</v>
+        <v>0.1741487374989669</v>
       </c>
       <c r="V12">
         <v>0.35</v>
       </c>
       <c r="W12">
-        <v>0.1148866793743285</v>
+        <v>0.1131966793743285</v>
       </c>
       <c r="X12" t="inlineStr">
         <is>
@@ -2297,7 +2297,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>3.95736342417298</v>
+        <v>4.016445936343995</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2308,13 +2308,13 @@
         <v>0.11</v>
       </c>
       <c r="B13">
-        <v>0.236310005265663</v>
+        <v>0.2361689896754074</v>
       </c>
       <c r="C13">
-        <v>27278.31700624117</v>
+        <v>27306.18899324302</v>
       </c>
       <c r="D13">
-        <v>29534.30700624118</v>
+        <v>29562.17899324303</v>
       </c>
       <c r="E13">
         <v>-6147.309999999999</v>
@@ -2341,37 +2341,37 @@
         <v>1991.289795918367</v>
       </c>
       <c r="M13">
-        <v>553.5045788643896</v>
+        <v>545.3624448643897</v>
       </c>
       <c r="N13">
-        <v>1437.785217053978</v>
+        <v>1445.927351053978</v>
       </c>
       <c r="O13">
-        <v>503.2248259688922</v>
+        <v>506.0745728688922</v>
       </c>
       <c r="P13">
-        <v>934.5603910850855</v>
+        <v>939.8527781850856</v>
       </c>
       <c r="Q13">
-        <v>2902.760391085086</v>
+        <v>2908.052778185086</v>
       </c>
       <c r="R13">
         <v>0.1235955056179775</v>
       </c>
       <c r="S13">
-        <v>0.2513173826230189</v>
+        <v>0.2513678145440801</v>
       </c>
       <c r="T13">
         <v>1.010031182147426</v>
       </c>
       <c r="U13">
-        <v>0.1767487374989669</v>
+        <v>0.1741487374989669</v>
       </c>
       <c r="V13">
         <v>0.35</v>
       </c>
       <c r="W13">
-        <v>0.1148866793743285</v>
+        <v>0.1131966793743285</v>
       </c>
       <c r="X13" t="inlineStr">
         <is>
@@ -2379,7 +2379,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>3.597603112884527</v>
+        <v>3.651314487585451</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2390,13 +2390,13 @@
         <v>0.12</v>
       </c>
       <c r="B14">
-        <v>0.2363350513138309</v>
+        <v>0.2361769723377884</v>
       </c>
       <c r="C14">
-        <v>26989.74468815438</v>
+        <v>27020.25942686453</v>
       </c>
       <c r="D14">
-        <v>29530.42468815438</v>
+        <v>29560.93942686453</v>
       </c>
       <c r="E14">
         <v>-5862.62</v>
@@ -2423,37 +2423,37 @@
         <v>1991.289795918367</v>
       </c>
       <c r="M14">
-        <v>603.8231769429705</v>
+        <v>594.9408489429704</v>
       </c>
       <c r="N14">
-        <v>1387.466618975397</v>
+        <v>1396.348946975397</v>
       </c>
       <c r="O14">
-        <v>485.613316641389</v>
+        <v>488.7221314413889</v>
       </c>
       <c r="P14">
-        <v>901.853302334008</v>
+        <v>907.6268155340081</v>
       </c>
       <c r="Q14">
-        <v>2870.053302334009</v>
+        <v>2875.826815534008</v>
       </c>
       <c r="R14">
         <v>0.1363636363636364</v>
       </c>
       <c r="S14">
-        <v>0.2528961929419448</v>
+        <v>0.2529470122873511</v>
       </c>
       <c r="T14">
         <v>1.0177903684141</v>
       </c>
       <c r="U14">
-        <v>0.1767487374989669</v>
+        <v>0.1741487374989669</v>
       </c>
       <c r="V14">
         <v>0.35</v>
       </c>
       <c r="W14">
-        <v>0.1148866793743285</v>
+        <v>0.1131966793743285</v>
       </c>
       <c r="X14" t="inlineStr">
         <is>
@@ -2461,7 +2461,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>3.297802853477484</v>
+        <v>3.347038280286664</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2472,13 +2472,13 @@
         <v>0.13</v>
       </c>
       <c r="B15">
-        <v>0.2363600973619988</v>
+        <v>0.2361849550001694</v>
       </c>
       <c r="C15">
-        <v>26701.17339060364</v>
+        <v>26734.32996443374</v>
       </c>
       <c r="D15">
-        <v>29526.54339060364</v>
+        <v>29559.69996443374</v>
       </c>
       <c r="E15">
         <v>-5577.929999999999</v>
@@ -2505,37 +2505,37 @@
         <v>1991.289795918367</v>
       </c>
       <c r="M15">
-        <v>654.1417750215514</v>
+        <v>644.5192530215514</v>
       </c>
       <c r="N15">
-        <v>1337.148020896816</v>
+        <v>1346.770542896816</v>
       </c>
       <c r="O15">
-        <v>468.0018073138855</v>
+        <v>471.3696900138856</v>
       </c>
       <c r="P15">
-        <v>869.1462135829304</v>
+        <v>875.4008528829305</v>
       </c>
       <c r="Q15">
-        <v>2837.34621358293</v>
+        <v>2843.600852882931</v>
       </c>
       <c r="R15">
         <v>0.1494252873563219</v>
       </c>
       <c r="S15">
-        <v>0.254511297750961</v>
+        <v>0.2545625134270192</v>
       </c>
       <c r="T15">
         <v>1.025727926778859</v>
       </c>
       <c r="U15">
-        <v>0.1767487374989669</v>
+        <v>0.1741487374989669</v>
       </c>
       <c r="V15">
         <v>0.35</v>
       </c>
       <c r="W15">
-        <v>0.1148866793743285</v>
+        <v>0.1131966793743285</v>
       </c>
       <c r="X15" t="inlineStr">
         <is>
@@ -2543,7 +2543,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>3.044125710902292</v>
+        <v>3.089573797187689</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2554,13 +2554,13 @@
         <v>0.14</v>
       </c>
       <c r="B16">
-        <v>0.2366217434101667</v>
+        <v>0.2364204376625505</v>
       </c>
       <c r="C16">
-        <v>26375.9979445735</v>
+        <v>26413.12343487287</v>
       </c>
       <c r="D16">
-        <v>29486.0579445735</v>
+        <v>29523.18343487287</v>
       </c>
       <c r="E16">
         <v>-5293.24</v>
@@ -2587,37 +2587,37 @@
         <v>1991.289795918367</v>
       </c>
       <c r="M16">
-        <v>714.8230891001323</v>
+        <v>704.0618071001323</v>
       </c>
       <c r="N16">
-        <v>1276.466706818235</v>
+        <v>1287.227988818235</v>
       </c>
       <c r="O16">
-        <v>446.7633473863823</v>
+        <v>450.5297960863823</v>
       </c>
       <c r="P16">
-        <v>829.703359431853</v>
+        <v>836.6981927318529</v>
       </c>
       <c r="Q16">
-        <v>2797.903359431853</v>
+        <v>2804.898192731853</v>
       </c>
       <c r="R16">
         <v>0.1627906976744186</v>
       </c>
       <c r="S16">
-        <v>0.2561639631369311</v>
+        <v>0.2562155843606331</v>
       </c>
       <c r="T16">
         <v>1.033850079524193</v>
       </c>
       <c r="U16">
-        <v>0.1793487374989668</v>
+        <v>0.1766487374989669</v>
       </c>
       <c r="V16">
         <v>0.35</v>
       </c>
       <c r="W16">
-        <v>0.1165766793743285</v>
+        <v>0.1148216793743285</v>
       </c>
       <c r="X16" t="inlineStr">
         <is>
@@ -2625,7 +2625,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>2.785709955767011</v>
+        <v>2.828288334684748</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2636,13 +2636,13 @@
         <v>0.15</v>
       </c>
       <c r="B17">
-        <v>0.2366636894583347</v>
+        <v>0.2364446703249314</v>
       </c>
       <c r="C17">
-        <v>26084.82780363975</v>
+        <v>26124.68077115891</v>
       </c>
       <c r="D17">
-        <v>29479.57780363975</v>
+        <v>29519.43077115891</v>
       </c>
       <c r="E17">
         <v>-5008.55</v>
@@ -2669,37 +2669,37 @@
         <v>1991.289795918367</v>
       </c>
       <c r="M17">
-        <v>765.881881178713</v>
+        <v>754.3519361787131</v>
       </c>
       <c r="N17">
-        <v>1225.407914739654</v>
+        <v>1236.937859739654</v>
       </c>
       <c r="O17">
-        <v>428.892770158879</v>
+        <v>432.928250908879</v>
       </c>
       <c r="P17">
-        <v>796.5151445807753</v>
+        <v>804.0096088307754</v>
       </c>
       <c r="Q17">
-        <v>2764.715144580776</v>
+        <v>2772.209608830776</v>
       </c>
       <c r="R17">
         <v>0.1764705882352941</v>
       </c>
       <c r="S17">
-        <v>0.2578555147672769</v>
+        <v>0.2579075510809202</v>
       </c>
       <c r="T17">
         <v>1.042163341745888</v>
       </c>
       <c r="U17">
-        <v>0.1793487374989668</v>
+        <v>0.1766487374989669</v>
       </c>
       <c r="V17">
         <v>0.35</v>
       </c>
       <c r="W17">
-        <v>0.1165766793743285</v>
+        <v>0.1148216793743285</v>
       </c>
       <c r="X17" t="inlineStr">
         <is>
@@ -2707,7 +2707,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>2.599995958715877</v>
+        <v>2.639735779039099</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2718,13 +2718,13 @@
         <v>0.16</v>
       </c>
       <c r="B18">
-        <v>0.2369864355065026</v>
+        <v>0.2368329029873125</v>
       </c>
       <c r="C18">
-        <v>25750.37267667047</v>
+        <v>25779.99897382428</v>
       </c>
       <c r="D18">
-        <v>29429.81267667047</v>
+        <v>29459.43897382428</v>
       </c>
       <c r="E18">
         <v>-4723.86</v>
@@ -2751,37 +2751,37 @@
         <v>1991.289795918367</v>
       </c>
       <c r="M18">
-        <v>829.239281257294</v>
+        <v>820.5847052572941</v>
       </c>
       <c r="N18">
-        <v>1162.050514661074</v>
+        <v>1170.705090661073</v>
       </c>
       <c r="O18">
-        <v>406.7176801313757</v>
+        <v>409.7467817313757</v>
       </c>
       <c r="P18">
-        <v>755.3328345296978</v>
+        <v>760.9583089296978</v>
       </c>
       <c r="Q18">
-        <v>2723.532834529698</v>
+        <v>2729.158308929698</v>
       </c>
       <c r="R18">
         <v>0.1904761904761905</v>
       </c>
       <c r="S18">
-        <v>0.2595873414364405</v>
+        <v>0.259639802723119</v>
       </c>
       <c r="T18">
         <v>1.050674538782386</v>
       </c>
       <c r="U18">
-        <v>0.1820487374989669</v>
+        <v>0.1801487374989669</v>
       </c>
       <c r="V18">
         <v>0.35</v>
       </c>
       <c r="W18">
-        <v>0.1183316793743285</v>
+        <v>0.1170966793743285</v>
       </c>
       <c r="X18" t="inlineStr">
         <is>
@@ -2789,7 +2789,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>2.401345234030846</v>
+        <v>2.426671839190568</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2800,13 +2800,13 @@
         <v>0.17</v>
       </c>
       <c r="B19">
-        <v>0.2370459315546705</v>
+        <v>0.2368798856496936</v>
       </c>
       <c r="C19">
-        <v>25456.5271482974</v>
+        <v>25488.06549620477</v>
       </c>
       <c r="D19">
-        <v>29420.6571482974</v>
+        <v>29452.19549620477</v>
       </c>
       <c r="E19">
         <v>-4439.169999999999</v>
@@ -2833,37 +2833,37 @@
         <v>1991.289795918367</v>
       </c>
       <c r="M19">
-        <v>881.0667363358749</v>
+        <v>871.8712493358751</v>
       </c>
       <c r="N19">
-        <v>1110.223059582493</v>
+        <v>1119.418546582492</v>
       </c>
       <c r="O19">
-        <v>388.5780708538724</v>
+        <v>391.7964913038723</v>
       </c>
       <c r="P19">
-        <v>721.6449887286202</v>
+        <v>727.6220552786201</v>
       </c>
       <c r="Q19">
-        <v>2689.844988728621</v>
+        <v>2695.822055278621</v>
       </c>
       <c r="R19">
         <v>0.2048192771084338</v>
       </c>
       <c r="S19">
-        <v>0.2613608988687165</v>
+        <v>0.2614137953687443</v>
       </c>
       <c r="T19">
         <v>1.0593908249041</v>
       </c>
       <c r="U19">
-        <v>0.1820487374989669</v>
+        <v>0.1801487374989669</v>
       </c>
       <c r="V19">
         <v>0.35</v>
       </c>
       <c r="W19">
-        <v>0.1183316793743285</v>
+        <v>0.1170966793743285</v>
       </c>
       <c r="X19" t="inlineStr">
         <is>
@@ -2871,7 +2871,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>2.260089632029032</v>
+        <v>2.28392643688524</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2882,13 +2882,13 @@
         <v>0.18</v>
       </c>
       <c r="B20">
-        <v>0.2376553276028384</v>
+        <v>0.2372544683120746</v>
       </c>
       <c r="C20">
-        <v>25078.38739933974</v>
+        <v>25145.75196879797</v>
       </c>
       <c r="D20">
-        <v>29327.20739933974</v>
+        <v>29394.57196879797</v>
       </c>
       <c r="E20">
         <v>-4154.48</v>
@@ -2915,37 +2915,37 @@
         <v>1991.289795918367</v>
       </c>
       <c r="M20">
-        <v>956.9789654144558</v>
+        <v>937.5061694144558</v>
       </c>
       <c r="N20">
-        <v>1034.310830503912</v>
+        <v>1053.783626503912</v>
       </c>
       <c r="O20">
-        <v>362.008790676369</v>
+        <v>368.824269276369</v>
       </c>
       <c r="P20">
-        <v>672.3020398275426</v>
+        <v>684.9593572275426</v>
       </c>
       <c r="Q20">
-        <v>2640.502039827543</v>
+        <v>2653.159357227543</v>
       </c>
       <c r="R20">
         <v>0.2195121951219512</v>
       </c>
       <c r="S20">
-        <v>0.2631777137993406</v>
+        <v>0.2632310561276774</v>
       </c>
       <c r="T20">
         <v>1.068319703370246</v>
       </c>
       <c r="U20">
-        <v>0.1867487374989669</v>
+        <v>0.1829487374989669</v>
       </c>
       <c r="V20">
         <v>0.35</v>
       </c>
       <c r="W20">
-        <v>0.1213866793743285</v>
+        <v>0.1189166793743285</v>
       </c>
       <c r="X20" t="inlineStr">
         <is>
@@ -2953,7 +2953,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>2.080808322736711</v>
+        <v>2.124028471366839</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2964,13 +2964,13 @@
         <v>0.19</v>
       </c>
       <c r="B21">
-        <v>0.2388939236510064</v>
+        <v>0.2373196509744556</v>
       </c>
       <c r="C21">
-        <v>24605.57877550216</v>
+        <v>24851.05768751024</v>
       </c>
       <c r="D21">
-        <v>29139.08877550216</v>
+        <v>29384.56768751024</v>
       </c>
       <c r="E21">
         <v>-3869.79</v>
@@ -2997,45 +2997,45 @@
         <v>1991.289795918367</v>
       </c>
       <c r="M21">
-        <v>1060.449186493036</v>
+        <v>989.5898454930366</v>
       </c>
       <c r="N21">
-        <v>930.840609425331</v>
+        <v>1001.699950425331</v>
       </c>
       <c r="O21">
-        <v>325.7942132988658</v>
+        <v>350.5949826488658</v>
       </c>
       <c r="P21">
-        <v>605.0463961264652</v>
+        <v>651.1049677764651</v>
       </c>
       <c r="Q21">
-        <v>2573.246396126466</v>
+        <v>2619.304967776465</v>
       </c>
       <c r="R21">
         <v>0.2345679012345679</v>
       </c>
       <c r="S21">
-        <v>0.2650393883578814</v>
+        <v>0.2650931875226336</v>
       </c>
       <c r="T21">
         <v>1.077469047971359</v>
       </c>
       <c r="U21">
-        <v>0.1960487374989668</v>
+        <v>0.1829487374989669</v>
       </c>
       <c r="V21">
         <v>0.35</v>
       </c>
       <c r="W21">
-        <v>0.1274316793743284</v>
+        <v>0.1189166793743285</v>
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y21">
-        <v>1.877779549724275</v>
+        <v>2.012237499189637</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3046,13 +3046,13 @@
         <v>0.2</v>
       </c>
       <c r="B22">
-        <v>0.2390444196991743</v>
+        <v>0.2383988336368367</v>
       </c>
       <c r="C22">
-        <v>24298.1956611822</v>
+        <v>24401.71811310151</v>
       </c>
       <c r="D22">
-        <v>29116.3956611822</v>
+        <v>29219.91811310151</v>
       </c>
       <c r="E22">
         <v>-3585.099999999999</v>
@@ -3079,37 +3079,37 @@
         <v>1991.289795918367</v>
       </c>
       <c r="M22">
-        <v>1116.262301571617</v>
+        <v>1086.085161571618</v>
       </c>
       <c r="N22">
-        <v>875.02749434675</v>
+        <v>905.2046343467498</v>
       </c>
       <c r="O22">
-        <v>306.2596230213625</v>
+        <v>316.8216220213624</v>
       </c>
       <c r="P22">
-        <v>568.7678713253875</v>
+        <v>588.3830123253874</v>
       </c>
       <c r="Q22">
-        <v>2536.967871325388</v>
+        <v>2556.583012325388</v>
       </c>
       <c r="R22">
         <v>0.25</v>
       </c>
       <c r="S22">
-        <v>0.2669476047803858</v>
+        <v>0.2670018722024637</v>
       </c>
       <c r="T22">
         <v>1.0868471261875</v>
       </c>
       <c r="U22">
-        <v>0.1960487374989668</v>
+        <v>0.1907487374989669</v>
       </c>
       <c r="V22">
         <v>0.35</v>
       </c>
       <c r="W22">
-        <v>0.1274316793743284</v>
+        <v>0.1239866793743285</v>
       </c>
       <c r="X22" t="inlineStr">
         <is>
@@ -3117,7 +3117,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>1.783890572238061</v>
+        <v>1.833456405054715</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3128,13 +3128,13 @@
         <v>0.21</v>
       </c>
       <c r="B23">
-        <v>0.2398364657473422</v>
+        <v>0.2390470662992177</v>
       </c>
       <c r="C23">
-        <v>23894.65415545359</v>
+        <v>24019.01210863765</v>
       </c>
       <c r="D23">
-        <v>28997.54415545359</v>
+        <v>29121.90210863766</v>
       </c>
       <c r="E23">
         <v>-3300.41</v>
@@ -3161,37 +3161,37 @@
         <v>1991.289795918367</v>
       </c>
       <c r="M23">
-        <v>1200.174319650198</v>
+        <v>1163.705530650198</v>
       </c>
       <c r="N23">
-        <v>791.1154762681692</v>
+        <v>827.584265268169</v>
       </c>
       <c r="O23">
-        <v>276.8904166938592</v>
+        <v>289.6544928438591</v>
       </c>
       <c r="P23">
-        <v>514.2250595743101</v>
+        <v>537.9297724243099</v>
       </c>
       <c r="Q23">
-        <v>2482.425059574311</v>
+        <v>2506.12977242431</v>
       </c>
       <c r="R23">
         <v>0.2658227848101266</v>
       </c>
       <c r="S23">
-        <v>0.2689041304794091</v>
+        <v>0.2689588780134287</v>
       </c>
       <c r="T23">
         <v>1.096462624105315</v>
       </c>
       <c r="U23">
-        <v>0.2007487374989669</v>
+        <v>0.1946487374989669</v>
       </c>
       <c r="V23">
         <v>0.35</v>
       </c>
       <c r="W23">
-        <v>0.1304866793743285</v>
+        <v>0.1265216793743285</v>
       </c>
       <c r="X23" t="inlineStr">
         <is>
@@ -3199,7 +3199,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>1.659167142068785</v>
+        <v>1.711162956152466</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3210,13 +3210,13 @@
         <v>0.22</v>
       </c>
       <c r="B24">
-        <v>0.2400175117955102</v>
+        <v>0.2391882989615987</v>
       </c>
       <c r="C24">
-        <v>23582.93316979535</v>
+        <v>23713.05420468231</v>
       </c>
       <c r="D24">
-        <v>28970.51316979535</v>
+        <v>29100.63420468231</v>
       </c>
       <c r="E24">
         <v>-3015.719999999999</v>
@@ -3243,37 +3243,37 @@
         <v>1991.289795918367</v>
       </c>
       <c r="M24">
-        <v>1257.325477728779</v>
+        <v>1219.120079728779</v>
       </c>
       <c r="N24">
-        <v>733.9643181895881</v>
+        <v>772.1697161895881</v>
       </c>
       <c r="O24">
-        <v>256.8875113663558</v>
+        <v>270.2594006663558</v>
       </c>
       <c r="P24">
-        <v>477.0768068232323</v>
+        <v>501.9103155232323</v>
       </c>
       <c r="Q24">
-        <v>2445.276806823233</v>
+        <v>2470.110315523233</v>
       </c>
       <c r="R24">
         <v>0.282051282051282</v>
       </c>
       <c r="S24">
-        <v>0.2709108235040486</v>
+        <v>0.2709660634605723</v>
       </c>
       <c r="T24">
         <v>1.106324673251792</v>
       </c>
       <c r="U24">
-        <v>0.2007487374989669</v>
+        <v>0.1946487374989669</v>
       </c>
       <c r="V24">
         <v>0.35</v>
       </c>
       <c r="W24">
-        <v>0.1304866793743285</v>
+        <v>0.1265216793743285</v>
       </c>
       <c r="X24" t="inlineStr">
         <is>
@@ -3281,7 +3281,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>1.583750453792931</v>
+        <v>1.633382821781899</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3292,13 +3292,13 @@
         <v>0.23</v>
       </c>
       <c r="B25">
-        <v>0.2401985578436781</v>
+        <v>0.2393295316239797</v>
       </c>
       <c r="C25">
-        <v>23271.26253279389</v>
+        <v>23407.12734221891</v>
       </c>
       <c r="D25">
-        <v>28943.53253279389</v>
+        <v>29079.39734221891</v>
       </c>
       <c r="E25">
         <v>-2731.03</v>
@@ -3325,37 +3325,37 @@
         <v>1991.289795918367</v>
       </c>
       <c r="M25">
-        <v>1314.47663580736</v>
+        <v>1274.53462880736</v>
       </c>
       <c r="N25">
-        <v>676.8131601110074</v>
+        <v>716.7551671110073</v>
       </c>
       <c r="O25">
-        <v>236.8846060388526</v>
+        <v>250.8643084888525</v>
       </c>
       <c r="P25">
-        <v>439.9285540721548</v>
+        <v>465.8908586221547</v>
       </c>
       <c r="Q25">
-        <v>2408.128554072155</v>
+        <v>2434.090858622155</v>
       </c>
       <c r="R25">
         <v>0.2987012987012987</v>
       </c>
       <c r="S25">
-        <v>0.2729696384254319</v>
+        <v>0.2730253835946548</v>
       </c>
       <c r="T25">
         <v>1.116442879518956</v>
       </c>
       <c r="U25">
-        <v>0.2007487374989669</v>
+        <v>0.1946487374989669</v>
       </c>
       <c r="V25">
         <v>0.35</v>
       </c>
       <c r="W25">
-        <v>0.1304866793743285</v>
+        <v>0.1265216793743285</v>
       </c>
       <c r="X25" t="inlineStr">
         <is>
@@ -3363,7 +3363,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>1.51489173841063</v>
+        <v>1.562366177356599</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3374,13 +3374,13 @@
         <v>0.24</v>
       </c>
       <c r="B26">
-        <v>0.242922403891846</v>
+        <v>0.2416859642863607</v>
       </c>
       <c r="C26">
-        <v>22586.62952706267</v>
+        <v>22772.62339843177</v>
       </c>
       <c r="D26">
-        <v>28543.58952706266</v>
+        <v>28729.58339843177</v>
       </c>
       <c r="E26">
         <v>-2446.34</v>
@@ -3407,37 +3407,37 @@
         <v>1991.289795918367</v>
       </c>
       <c r="M26">
-        <v>1482.998521885941</v>
+        <v>1426.971529885941</v>
       </c>
       <c r="N26">
-        <v>508.2912740324266</v>
+        <v>564.3182660324264</v>
       </c>
       <c r="O26">
-        <v>177.9019459113493</v>
+        <v>197.5113931113492</v>
       </c>
       <c r="P26">
-        <v>330.3893281210773</v>
+        <v>366.8068729210772</v>
       </c>
       <c r="Q26">
-        <v>2298.589328121077</v>
+        <v>2335.006872921078</v>
       </c>
       <c r="R26">
         <v>0.3157894736842105</v>
       </c>
       <c r="S26">
-        <v>0.2750826326868515</v>
+        <v>0.2751388963638446</v>
       </c>
       <c r="T26">
         <v>1.126827354372099</v>
       </c>
       <c r="U26">
-        <v>0.2170487374989669</v>
+        <v>0.2088487374989669</v>
       </c>
       <c r="V26">
         <v>0.35</v>
       </c>
       <c r="W26">
-        <v>0.1410816793743285</v>
+        <v>0.1357516793743285</v>
       </c>
       <c r="X26" t="inlineStr">
         <is>
@@ -3445,7 +3445,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>1.34274563765986</v>
+        <v>1.395465679737516</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3456,13 +3456,13 @@
         <v>0.25</v>
       </c>
       <c r="B27">
-        <v>0.243209399940014</v>
+        <v>0.2419194969487418</v>
       </c>
       <c r="C27">
-        <v>22260.44252946637</v>
+        <v>22453.72315312461</v>
       </c>
       <c r="D27">
-        <v>28502.09252946637</v>
+        <v>28695.37315312461</v>
       </c>
       <c r="E27">
         <v>-2161.65</v>
@@ -3489,37 +3489,37 @@
         <v>1991.289795918367</v>
       </c>
       <c r="M27">
-        <v>1544.790126964522</v>
+        <v>1486.428676964522</v>
       </c>
       <c r="N27">
-        <v>446.4996689538455</v>
+        <v>504.8611189538453</v>
       </c>
       <c r="O27">
-        <v>156.2748841338459</v>
+        <v>176.7013916338458</v>
       </c>
       <c r="P27">
-        <v>290.2247848199996</v>
+        <v>328.1597273199995</v>
       </c>
       <c r="Q27">
-        <v>2258.42478482</v>
+        <v>2296.35972732</v>
       </c>
       <c r="R27">
         <v>0.3333333333333333</v>
       </c>
       <c r="S27">
-        <v>0.2772519734619092</v>
+        <v>0.2773087694735462</v>
       </c>
       <c r="T27">
         <v>1.137488748554659</v>
       </c>
       <c r="U27">
-        <v>0.2170487374989669</v>
+        <v>0.2088487374989669</v>
       </c>
       <c r="V27">
         <v>0.35</v>
       </c>
       <c r="W27">
-        <v>0.1410816793743285</v>
+        <v>0.1357516793743285</v>
       </c>
       <c r="X27" t="inlineStr">
         <is>
@@ -3527,7 +3527,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>1.289035812153465</v>
+        <v>1.339647052548015</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3538,13 +3538,13 @@
         <v>0.26</v>
       </c>
       <c r="B28">
-        <v>0.2490226959881819</v>
+        <v>0.2421530296111228</v>
       </c>
       <c r="C28">
-        <v>21160.43462877432</v>
+        <v>22134.90428379297</v>
       </c>
       <c r="D28">
-        <v>27686.77462877432</v>
+        <v>28661.24428379298</v>
       </c>
       <c r="E28">
         <v>-1876.959999999999</v>
@@ -3571,45 +3571,45 @@
         <v>1991.289795918367</v>
       </c>
       <c r="M28">
-        <v>1848.625170043103</v>
+        <v>1545.885824043103</v>
       </c>
       <c r="N28">
-        <v>142.6646258752644</v>
+        <v>445.4039718752645</v>
       </c>
       <c r="O28">
-        <v>49.93261905634253</v>
+        <v>155.8913901563425</v>
       </c>
       <c r="P28">
-        <v>92.73200681892186</v>
+        <v>289.5125817189219</v>
       </c>
       <c r="Q28">
-        <v>2060.932006818922</v>
+        <v>2257.712581718922</v>
       </c>
       <c r="R28">
         <v>0.3513513513513514</v>
       </c>
       <c r="S28">
-        <v>0.279479945068725</v>
+        <v>0.2795372878024289</v>
       </c>
       <c r="T28">
         <v>1.148438288525937</v>
       </c>
       <c r="U28">
-        <v>0.2497487374989669</v>
+        <v>0.2088487374989669</v>
       </c>
       <c r="V28">
         <v>0.35</v>
       </c>
       <c r="W28">
-        <v>0.1623366793743285</v>
+        <v>0.1357516793743285</v>
       </c>
       <c r="X28" t="inlineStr">
         <is>
-          <t>Caa/CCC</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y28">
-        <v>1.077173365475673</v>
+        <v>1.288122165911553</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3620,13 +3620,13 @@
         <v>0.27</v>
       </c>
       <c r="B29">
-        <v>0.2495222420363498</v>
+        <v>0.2474058622735038</v>
       </c>
       <c r="C29">
-        <v>20807.85406015467</v>
+        <v>21103.44671254971</v>
       </c>
       <c r="D29">
-        <v>27618.88406015467</v>
+        <v>27914.47671254972</v>
       </c>
       <c r="E29">
         <v>-1592.27</v>
@@ -3653,37 +3653,37 @@
         <v>1991.289795918367</v>
       </c>
       <c r="M29">
-        <v>1919.726138121684</v>
+        <v>1825.180589121684</v>
       </c>
       <c r="N29">
-        <v>71.56365779668363</v>
+        <v>166.1092067966838</v>
       </c>
       <c r="O29">
-        <v>25.04728022883927</v>
+        <v>58.13822237883932</v>
       </c>
       <c r="P29">
-        <v>46.51637756784436</v>
+        <v>107.9709844178445</v>
       </c>
       <c r="Q29">
-        <v>2014.716377567845</v>
+        <v>2076.170984417845</v>
       </c>
       <c r="R29">
         <v>0.3698630136986302</v>
       </c>
       <c r="S29">
-        <v>0.2817689569935358</v>
+        <v>0.2818268614279933</v>
       </c>
       <c r="T29">
         <v>1.159687815893688</v>
       </c>
       <c r="U29">
-        <v>0.2497487374989669</v>
+        <v>0.2374487374989669</v>
       </c>
       <c r="V29">
         <v>0.35</v>
       </c>
       <c r="W29">
-        <v>0.1623366793743285</v>
+        <v>0.1543416793743285</v>
       </c>
       <c r="X29" t="inlineStr">
         <is>
@@ -3691,7 +3691,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>1.037278055643241</v>
+        <v>1.091009737768808</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3702,13 +3702,13 @@
         <v>0.28</v>
       </c>
       <c r="B30">
-        <v>0.2500217880845177</v>
+        <v>0.2478252949358848</v>
       </c>
       <c r="C30">
-        <v>20455.60562519792</v>
+        <v>20760.80236930654</v>
       </c>
       <c r="D30">
-        <v>27551.32562519792</v>
+        <v>27856.52236930654</v>
       </c>
       <c r="E30">
         <v>-1307.579999999999</v>
@@ -3735,37 +3735,37 @@
         <v>1991.289795918367</v>
       </c>
       <c r="M30">
-        <v>1990.827106200265</v>
+        <v>1892.779870200265</v>
       </c>
       <c r="N30">
-        <v>0.4626897181026379</v>
+        <v>98.50992571810275</v>
       </c>
       <c r="O30">
-        <v>0.1619414013359233</v>
+        <v>34.47847400133596</v>
       </c>
       <c r="P30">
-        <v>0.3007483167667147</v>
+        <v>64.03145171676678</v>
       </c>
       <c r="Q30">
-        <v>1968.500748316767</v>
+        <v>2032.231451716767</v>
       </c>
       <c r="R30">
         <v>0.388888888888889</v>
       </c>
       <c r="S30">
-        <v>0.2841215525829247</v>
+        <v>0.2841800343209346</v>
       </c>
       <c r="T30">
         <v>1.171249830132765</v>
       </c>
       <c r="U30">
-        <v>0.2497487374989669</v>
+        <v>0.2374487374989669</v>
       </c>
       <c r="V30">
         <v>0.35</v>
       </c>
       <c r="W30">
-        <v>0.1623366793743285</v>
+        <v>0.1543416793743285</v>
       </c>
       <c r="X30" t="inlineStr">
         <is>
@@ -3773,7 +3773,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>1.000232410798839</v>
+        <v>1.052045104277065</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3784,13 +3784,13 @@
         <v>0.29</v>
       </c>
       <c r="B31">
-        <v>0.2520512542876773</v>
+        <v>0.2482447275982659</v>
       </c>
       <c r="C31">
-        <v>19899.81674436108</v>
+        <v>20418.39817007473</v>
       </c>
       <c r="D31">
-        <v>27280.22674436108</v>
+        <v>27798.80817007474</v>
       </c>
       <c r="E31">
         <v>-1022.889999999999</v>
@@ -3817,37 +3817,37 @@
         <v>1991.289795918367</v>
       </c>
       <c r="M31">
-        <v>2061.928074278846</v>
+        <v>1960.379151278845</v>
       </c>
       <c r="N31">
-        <v>-70.63827836047813</v>
+        <v>30.91064463952193</v>
       </c>
       <c r="O31">
-        <v>-24.72339742616734</v>
+        <v>10.81872562383268</v>
       </c>
       <c r="P31">
-        <v>-45.91488093431079</v>
+        <v>20.09191901568926</v>
       </c>
       <c r="Q31">
-        <v>1922.28511906569</v>
+        <v>1988.291919015689</v>
       </c>
       <c r="R31">
         <v>0.4084507042253521</v>
       </c>
       <c r="S31">
-        <v>0.2874720915910248</v>
+        <v>0.2865994937742403</v>
       </c>
       <c r="T31">
-        <v>1.187716315020761</v>
+        <v>1.183137534913789</v>
       </c>
       <c r="U31">
-        <v>0.2497487374989669</v>
+        <v>0.2374487374989669</v>
       </c>
       <c r="V31">
-        <v>0.3380095733044353</v>
+        <v>0.35</v>
       </c>
       <c r="W31">
-        <v>0.1653312733036197</v>
+        <v>0.1543416793743285</v>
       </c>
       <c r="X31" t="inlineStr">
         <is>
@@ -3855,7 +3855,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>0.9657416380126723</v>
+        <v>1.015767686888201</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3866,13 +3866,13 @@
         <v>0.3</v>
       </c>
       <c r="B32">
-        <v>0.2540907416626669</v>
+        <v>0.2494766673643309</v>
       </c>
       <c r="C32">
-        <v>19348.01128071707</v>
+        <v>19965.56688184034</v>
       </c>
       <c r="D32">
-        <v>27013.11128071707</v>
+        <v>27630.66688184033</v>
       </c>
       <c r="E32">
         <v>-738.2000000000007</v>
@@ -3899,37 +3899,37 @@
         <v>1991.289795918367</v>
       </c>
       <c r="M32">
-        <v>2133.029042357426</v>
+        <v>2027.978432357426</v>
       </c>
       <c r="N32">
-        <v>-141.7392464390587</v>
+        <v>-36.68863643905866</v>
       </c>
       <c r="O32">
-        <v>-49.60873625367053</v>
+        <v>-12.84102275367053</v>
       </c>
       <c r="P32">
-        <v>-92.13051018538813</v>
+        <v>-23.84761368538813</v>
       </c>
       <c r="Q32">
-        <v>1876.069489814612</v>
+        <v>1944.352386314612</v>
       </c>
       <c r="R32">
         <v>0.4285714285714286</v>
       </c>
       <c r="S32">
-        <v>0.2909245500423251</v>
+        <v>0.289604443901845</v>
       </c>
       <c r="T32">
-        <v>1.204683690949629</v>
+        <v>1.19790197328859</v>
       </c>
       <c r="U32">
-        <v>0.2497487374989669</v>
+        <v>0.2374487374989669</v>
       </c>
       <c r="V32">
-        <v>0.3267425875276209</v>
+        <v>0.3436680673971747</v>
       </c>
       <c r="W32">
-        <v>0.1681451887767979</v>
+        <v>0.1558451887767979</v>
       </c>
       <c r="X32" t="inlineStr">
         <is>
@@ -3937,7 +3937,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>0.9335502500789168</v>
+        <v>0.9819087639919277</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3948,13 +3948,13 @@
         <v>0.31</v>
       </c>
       <c r="B33">
-        <v>0.2561302290376566</v>
+        <v>0.2513931547393206</v>
       </c>
       <c r="C33">
-        <v>18801.38603884392</v>
+        <v>19423.31079551448</v>
       </c>
       <c r="D33">
-        <v>26751.17603884392</v>
+        <v>27373.10079551448</v>
       </c>
       <c r="E33">
         <v>-453.5100000000002</v>
@@ -3981,37 +3981,37 @@
         <v>1991.289795918367</v>
       </c>
       <c r="M33">
-        <v>2204.130010436007</v>
+        <v>2095.577713436007</v>
       </c>
       <c r="N33">
-        <v>-212.8402145176397</v>
+        <v>-104.2879175176395</v>
       </c>
       <c r="O33">
-        <v>-74.49407508117388</v>
+        <v>-36.50077113117381</v>
       </c>
       <c r="P33">
-        <v>-138.3461394364658</v>
+        <v>-67.78714638646565</v>
       </c>
       <c r="Q33">
-        <v>1829.853860563534</v>
+        <v>1900.412853613535</v>
       </c>
       <c r="R33">
         <v>0.4492753623188406</v>
       </c>
       <c r="S33">
-        <v>0.2944770797530835</v>
+        <v>0.293137841639553</v>
       </c>
       <c r="T33">
-        <v>1.222142874876435</v>
+        <v>1.215262871452193</v>
       </c>
       <c r="U33">
-        <v>0.2497487374989669</v>
+        <v>0.2374487374989669</v>
       </c>
       <c r="V33">
-        <v>0.3162025040589879</v>
+        <v>0.3325820007069433</v>
       </c>
       <c r="W33">
-        <v>0.1707775613162227</v>
+        <v>0.1584775613162227</v>
       </c>
       <c r="X33" t="inlineStr">
         <is>
@@ -4019,7 +4019,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>0.9034357258828226</v>
+        <v>0.9502342877341237</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4030,13 +4030,13 @@
         <v>0.32</v>
       </c>
       <c r="B34">
-        <v>0.2581697164126462</v>
+        <v>0.2533096421143102</v>
       </c>
       <c r="C34">
-        <v>18259.79177434258</v>
+        <v>18885.81229199432</v>
       </c>
       <c r="D34">
-        <v>26494.27177434258</v>
+        <v>27120.29229199432</v>
       </c>
       <c r="E34">
         <v>-168.8199999999997</v>
@@ -4063,37 +4063,37 @@
         <v>1991.289795918367</v>
       </c>
       <c r="M34">
-        <v>2275.230978514588</v>
+        <v>2163.176994514588</v>
       </c>
       <c r="N34">
-        <v>-283.9411825962206</v>
+        <v>-171.8871985962205</v>
       </c>
       <c r="O34">
-        <v>-99.37941390867722</v>
+        <v>-60.16051950867718</v>
       </c>
       <c r="P34">
-        <v>-184.5617686875434</v>
+        <v>-111.7266790875433</v>
       </c>
       <c r="Q34">
-        <v>1783.638231312457</v>
+        <v>1856.473320912457</v>
       </c>
       <c r="R34">
         <v>0.4705882352941177</v>
       </c>
       <c r="S34">
-        <v>0.2981340956318053</v>
+        <v>0.2967751628401346</v>
       </c>
       <c r="T34">
-        <v>1.240115564212854</v>
+        <v>1.233134384267666</v>
       </c>
       <c r="U34">
-        <v>0.2497487374989669</v>
+        <v>0.2374487374989669</v>
       </c>
       <c r="V34">
-        <v>0.3063211758071445</v>
+        <v>0.3221888131848513</v>
       </c>
       <c r="W34">
-        <v>0.1732454105719335</v>
+        <v>0.1609454105719334</v>
       </c>
       <c r="X34" t="inlineStr">
         <is>
@@ -4101,7 +4101,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>0.8752033594489843</v>
+        <v>0.9205394662424322</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4112,13 +4112,13 @@
         <v>0.33</v>
       </c>
       <c r="B35">
-        <v>0.260209203787636</v>
+        <v>0.2552261294892999</v>
       </c>
       <c r="C35">
-        <v>17723.08492134015</v>
+        <v>18352.94075939195</v>
       </c>
       <c r="D35">
-        <v>26242.25492134015</v>
+        <v>26872.11075939195</v>
       </c>
       <c r="E35">
         <v>115.8700000000008</v>
@@ -4145,37 +4145,37 @@
         <v>1991.289795918367</v>
       </c>
       <c r="M35">
-        <v>2346.331946593169</v>
+        <v>2230.776275593169</v>
       </c>
       <c r="N35">
-        <v>-355.0421506748016</v>
+        <v>-239.4864796748016</v>
       </c>
       <c r="O35">
-        <v>-124.2647527361806</v>
+        <v>-83.82026788618055</v>
       </c>
       <c r="P35">
-        <v>-230.777397938621</v>
+        <v>-155.666211788621</v>
       </c>
       <c r="Q35">
-        <v>1737.422602061379</v>
+        <v>1812.533788211379</v>
       </c>
       <c r="R35">
         <v>0.4925373134328359</v>
       </c>
       <c r="S35">
-        <v>0.3019002761636233</v>
+        <v>0.3005210607929725</v>
       </c>
       <c r="T35">
-        <v>1.258624751738419</v>
+        <v>1.251539375077632</v>
       </c>
       <c r="U35">
-        <v>0.2497487374989669</v>
+        <v>0.2374487374989669</v>
       </c>
       <c r="V35">
-        <v>0.2970387159342007</v>
+        <v>0.3124255158156133</v>
       </c>
       <c r="W35">
-        <v>0.175563693206086</v>
+        <v>0.163263693206086</v>
       </c>
       <c r="X35" t="inlineStr">
         <is>
@@ -4183,7 +4183,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>0.8486820455262878</v>
+        <v>0.8926443309017523</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4194,13 +4194,13 @@
         <v>0.34</v>
       </c>
       <c r="B36">
-        <v>0.2622486911626256</v>
+        <v>0.2571426168642896</v>
       </c>
       <c r="C36">
-        <v>17191.12732496035</v>
+        <v>17824.57032345427</v>
       </c>
       <c r="D36">
-        <v>25994.98732496036</v>
+        <v>26628.43032345427</v>
       </c>
       <c r="E36">
         <v>400.5600000000013</v>
@@ -4227,37 +4227,37 @@
         <v>1991.289795918367</v>
       </c>
       <c r="M36">
-        <v>2417.43291467175</v>
+        <v>2298.37555667175</v>
       </c>
       <c r="N36">
-        <v>-426.1431187533826</v>
+        <v>-307.0857607533826</v>
       </c>
       <c r="O36">
-        <v>-149.1500915636839</v>
+        <v>-107.4800162636839</v>
       </c>
       <c r="P36">
-        <v>-276.9930271896988</v>
+        <v>-199.6057444896987</v>
       </c>
       <c r="Q36">
-        <v>1691.206972810302</v>
+        <v>1768.594255510302</v>
       </c>
       <c r="R36">
         <v>0.5151515151515152</v>
       </c>
       <c r="S36">
-        <v>0.3057805833782237</v>
+        <v>0.3043804708049872</v>
       </c>
       <c r="T36">
-        <v>1.277694823734455</v>
+        <v>1.270502092881838</v>
       </c>
       <c r="U36">
-        <v>0.2497487374989669</v>
+        <v>0.2374487374989669</v>
       </c>
       <c r="V36">
-        <v>0.2883022831126066</v>
+        <v>0.3032365300563306</v>
       </c>
       <c r="W36">
-        <v>0.1777456062735237</v>
+        <v>0.1654456062735236</v>
       </c>
       <c r="X36" t="inlineStr">
         <is>
@@ -4265,7 +4265,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>0.8237208088931617</v>
+        <v>0.8663900858752301</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4276,13 +4276,13 @@
         <v>0.35</v>
       </c>
       <c r="B37">
-        <v>0.2642881785376153</v>
+        <v>0.2590591042392792</v>
       </c>
       <c r="C37">
-        <v>16663.78598877767</v>
+        <v>17300.5796346854</v>
       </c>
       <c r="D37">
-        <v>25752.33598877767</v>
+        <v>26389.1296346854</v>
       </c>
       <c r="E37">
         <v>685.2500000000018</v>
@@ -4309,37 +4309,37 @@
         <v>1991.289795918367</v>
       </c>
       <c r="M37">
-        <v>2488.533882750331</v>
+        <v>2365.974837750331</v>
       </c>
       <c r="N37">
-        <v>-497.2440868319636</v>
+        <v>-374.6850418319636</v>
       </c>
       <c r="O37">
-        <v>-174.0354303911872</v>
+        <v>-131.1397646411873</v>
       </c>
       <c r="P37">
-        <v>-323.2086564407764</v>
+        <v>-243.5452771907764</v>
       </c>
       <c r="Q37">
-        <v>1644.991343559224</v>
+        <v>1724.654722809224</v>
       </c>
       <c r="R37">
         <v>0.5384615384615385</v>
       </c>
       <c r="S37">
-        <v>0.3097802846609656</v>
+        <v>0.3083586318942947</v>
       </c>
       <c r="T37">
-        <v>1.297351667176524</v>
+        <v>1.290048278926174</v>
       </c>
       <c r="U37">
-        <v>0.2497487374989669</v>
+        <v>0.2374487374989669</v>
       </c>
       <c r="V37">
-        <v>0.2800650750236749</v>
+        <v>0.2945726291975782</v>
       </c>
       <c r="W37">
-        <v>0.1798028385942506</v>
+        <v>0.1675028385942506</v>
       </c>
       <c r="X37" t="inlineStr">
         <is>
@@ -4347,7 +4347,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>0.8001859286390713</v>
+        <v>0.8416360834216521</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4358,13 +4358,13 @@
         <v>0.36</v>
       </c>
       <c r="B38">
-        <v>0.2802585254762615</v>
+        <v>0.2609755916142689</v>
       </c>
       <c r="C38">
-        <v>14624.95316379004</v>
+        <v>16780.85166684515</v>
       </c>
       <c r="D38">
-        <v>23998.19316379004</v>
+        <v>26154.09166684515</v>
       </c>
       <c r="E38">
         <v>969.9400000000005</v>
@@ -4391,45 +4391,45 @@
         <v>1991.289795918367</v>
       </c>
       <c r="M38">
-        <v>2894.771918828912</v>
+        <v>2433.574118828912</v>
       </c>
       <c r="N38">
-        <v>-903.4821229105441</v>
+        <v>-442.2843229105442</v>
       </c>
       <c r="O38">
-        <v>-316.2187430186904</v>
+        <v>-154.7995130186905</v>
       </c>
       <c r="P38">
-        <v>-587.2633798918537</v>
+        <v>-287.4848098918537</v>
       </c>
       <c r="Q38">
-        <v>1380.936620108147</v>
+        <v>1680.715190108147</v>
       </c>
       <c r="R38">
         <v>0.5625</v>
       </c>
       <c r="S38">
-        <v>0.3172781946770064</v>
+        <v>0.3124611105176431</v>
       </c>
       <c r="T38">
-        <v>1.334200729871275</v>
+        <v>1.310205283284396</v>
       </c>
       <c r="U38">
-        <v>0.2824487374989669</v>
+        <v>0.2374487374989669</v>
       </c>
       <c r="V38">
-        <v>0.2407621215468272</v>
+        <v>0.2863900561643122</v>
       </c>
       <c r="W38">
-        <v>0.2144457802304927</v>
+        <v>0.1694457802304927</v>
       </c>
       <c r="X38" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>Caa/CCC</t>
         </is>
       </c>
       <c r="Y38">
-        <v>0.6878917758480777</v>
+        <v>0.8182573033266063</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4440,13 +4440,13 @@
         <v>0.37</v>
       </c>
       <c r="B39">
-        <v>0.2826250128512512</v>
+        <v>0.2754086394770743</v>
       </c>
       <c r="C39">
-        <v>14100.45985728566</v>
+        <v>14852.13268912254</v>
       </c>
       <c r="D39">
-        <v>23758.38985728566</v>
+        <v>24510.06268912254</v>
       </c>
       <c r="E39">
         <v>1254.630000000001</v>
@@ -4473,37 +4473,37 @@
         <v>1991.289795918367</v>
       </c>
       <c r="M39">
-        <v>2975.182249907493</v>
+        <v>2798.218945907493</v>
       </c>
       <c r="N39">
-        <v>-983.8924539891254</v>
+        <v>-806.9291499891251</v>
       </c>
       <c r="O39">
-        <v>-344.3623588961939</v>
+        <v>-282.4252024961938</v>
       </c>
       <c r="P39">
-        <v>-639.5300950929316</v>
+        <v>-524.5039474929313</v>
       </c>
       <c r="Q39">
-        <v>1328.669904907069</v>
+        <v>1443.696052507069</v>
       </c>
       <c r="R39">
         <v>0.5873015873015873</v>
       </c>
       <c r="S39">
-        <v>0.3215873723702923</v>
+        <v>0.3199994781255671</v>
       </c>
       <c r="T39">
-        <v>1.355378519234312</v>
+        <v>1.347244089010769</v>
       </c>
       <c r="U39">
-        <v>0.2824487374989669</v>
+        <v>0.2656487374989668</v>
       </c>
       <c r="V39">
-        <v>0.2342550371806967</v>
+        <v>0.2490696553930306</v>
       </c>
       <c r="W39">
-        <v>0.2162836979945056</v>
+        <v>0.1994836979945055</v>
       </c>
       <c r="X39" t="inlineStr">
         <is>
@@ -4511,7 +4511,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>0.669300106230562</v>
+        <v>0.7116275868372304</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4522,13 +4522,13 @@
         <v>0.38</v>
       </c>
       <c r="B40">
-        <v>0.2849915002262408</v>
+        <v>0.277607126852064</v>
       </c>
       <c r="C40">
-        <v>13580.71163157877</v>
+        <v>14334.9862322655</v>
       </c>
       <c r="D40">
-        <v>23523.33163157877</v>
+        <v>24277.6062322655</v>
       </c>
       <c r="E40">
         <v>1539.32</v>
@@ -4555,37 +4555,37 @@
         <v>1991.289795918367</v>
       </c>
       <c r="M40">
-        <v>3055.592580986073</v>
+        <v>2873.846484986073</v>
       </c>
       <c r="N40">
-        <v>-1064.302785067706</v>
+        <v>-882.5566890677055</v>
       </c>
       <c r="O40">
-        <v>-372.505974773697</v>
+        <v>-308.8948411736969</v>
       </c>
       <c r="P40">
-        <v>-691.7968102940088</v>
+        <v>-573.6618478940086</v>
       </c>
       <c r="Q40">
-        <v>1276.403189705992</v>
+        <v>1394.538152105992</v>
       </c>
       <c r="R40">
         <v>0.6129032258064516</v>
       </c>
       <c r="S40">
-        <v>0.3260355557956195</v>
+        <v>0.3244220503533988</v>
       </c>
       <c r="T40">
-        <v>1.377239463092929</v>
+        <v>1.36897383238191</v>
       </c>
       <c r="U40">
-        <v>0.2824487374989669</v>
+        <v>0.2656487374989668</v>
       </c>
       <c r="V40">
-        <v>0.2280904309390994</v>
+        <v>0.2425151907774246</v>
       </c>
       <c r="W40">
-        <v>0.2180248832446229</v>
+        <v>0.2012248832446229</v>
       </c>
       <c r="X40" t="inlineStr">
         <is>
@@ -4593,7 +4593,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>0.6516869455402842</v>
+        <v>0.6929005450783561</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4604,13 +4604,13 @@
         <v>0.39</v>
       </c>
       <c r="B41">
-        <v>0.3102879300883669</v>
+        <v>0.2798056142270536</v>
       </c>
       <c r="C41">
-        <v>11046.17866693781</v>
+        <v>13822.20764143017</v>
       </c>
       <c r="D41">
-        <v>21273.48866693781</v>
+        <v>24049.51764143017</v>
       </c>
       <c r="E41">
         <v>1824.01</v>
@@ -4637,45 +4637,45 @@
         <v>1991.289795918367</v>
       </c>
       <c r="M41">
-        <v>3715.574814064655</v>
+        <v>2949.474024064654</v>
       </c>
       <c r="N41">
-        <v>-1724.285018146287</v>
+        <v>-958.1842281462864</v>
       </c>
       <c r="O41">
-        <v>-603.4997563512005</v>
+        <v>-335.3644798512002</v>
       </c>
       <c r="P41">
-        <v>-1120.785261795087</v>
+        <v>-622.8197482950861</v>
       </c>
       <c r="Q41">
-        <v>847.4147382049136</v>
+        <v>1345.380251704914</v>
       </c>
       <c r="R41">
         <v>0.639344262295082</v>
       </c>
       <c r="S41">
-        <v>0.3348458804597058</v>
+        <v>0.3289896249493561</v>
       </c>
       <c r="T41">
-        <v>1.420538489783497</v>
+        <v>1.391416026355384</v>
       </c>
       <c r="U41">
-        <v>0.3346487374989669</v>
+        <v>0.2656487374989668</v>
       </c>
       <c r="V41">
-        <v>0.1875756682204976</v>
+        <v>0.2362968525523624</v>
       </c>
       <c r="W41">
-        <v>0.2718767769434523</v>
+        <v>0.2028767769434522</v>
       </c>
       <c r="X41" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y41">
-        <v>0.535930480629993</v>
+        <v>0.6751338644353213</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4686,13 +4686,13 @@
         <v>0.4</v>
       </c>
       <c r="B42">
-        <v>0.3131764174633566</v>
+        <v>0.2820041016020433</v>
       </c>
       <c r="C42">
-        <v>10531.66958259445</v>
+        <v>13313.67495389566</v>
       </c>
       <c r="D42">
-        <v>21043.66958259445</v>
+        <v>23825.67495389566</v>
       </c>
       <c r="E42">
         <v>2108.700000000001</v>
@@ -4719,45 +4719,45 @@
         <v>1991.289795918367</v>
       </c>
       <c r="M42">
-        <v>3810.845963143236</v>
+        <v>3025.101563143235</v>
       </c>
       <c r="N42">
-        <v>-1819.556167224868</v>
+        <v>-1033.811767224867</v>
       </c>
       <c r="O42">
-        <v>-636.8446585287038</v>
+        <v>-361.8341185287035</v>
       </c>
       <c r="P42">
-        <v>-1182.711508696164</v>
+        <v>-671.9776486961637</v>
       </c>
       <c r="Q42">
-        <v>785.4884913038359</v>
+        <v>1296.222351303837</v>
       </c>
       <c r="R42">
         <v>0.6666666666666667</v>
       </c>
       <c r="S42">
-        <v>0.3396633118007009</v>
+        <v>0.3337094520318454</v>
       </c>
       <c r="T42">
-        <v>1.444214131279888</v>
+        <v>1.414606293461307</v>
       </c>
       <c r="U42">
-        <v>0.3346487374989669</v>
+        <v>0.2656487374989668</v>
       </c>
       <c r="V42">
-        <v>0.1828862765149851</v>
+        <v>0.2303894312385534</v>
       </c>
       <c r="W42">
-        <v>0.2734460759573402</v>
+        <v>0.2044460759573401</v>
       </c>
       <c r="X42" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y42">
-        <v>0.5225322186142431</v>
+        <v>0.6582555178244383</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4768,13 +4768,13 @@
         <v>0.41</v>
       </c>
       <c r="B43">
-        <v>0.3160649048383463</v>
+        <v>0.3093049579280098</v>
       </c>
       <c r="C43">
-        <v>10022.07293424832</v>
+        <v>10560.48745806033</v>
       </c>
       <c r="D43">
-        <v>20818.76293424832</v>
+        <v>21357.17745806033</v>
       </c>
       <c r="E43">
         <v>2393.390000000001</v>
@@ -4801,37 +4801,37 @@
         <v>1991.289795918367</v>
       </c>
       <c r="M43">
-        <v>3906.117112221817</v>
+        <v>3731.032762221816</v>
       </c>
       <c r="N43">
-        <v>-1914.827316303449</v>
+        <v>-1739.742966303449</v>
       </c>
       <c r="O43">
-        <v>-670.1895607062072</v>
+        <v>-608.9100382062071</v>
       </c>
       <c r="P43">
-        <v>-1244.637755597242</v>
+        <v>-1130.832928097242</v>
       </c>
       <c r="Q43">
-        <v>723.5622444027583</v>
+        <v>837.3670719027582</v>
       </c>
       <c r="R43">
         <v>0.6949152542372882</v>
       </c>
       <c r="S43">
-        <v>0.3446440458990178</v>
+        <v>0.3436102375764136</v>
       </c>
       <c r="T43">
-        <v>1.468692336894801</v>
+        <v>1.463252537767339</v>
       </c>
       <c r="U43">
-        <v>0.3346487374989669</v>
+        <v>0.3196487374989669</v>
       </c>
       <c r="V43">
-        <v>0.1784256356243757</v>
+        <v>0.1867985281792049</v>
       </c>
       <c r="W43">
-        <v>0.2749388237998189</v>
+        <v>0.2599388237998189</v>
       </c>
       <c r="X43" t="inlineStr">
         <is>
@@ -4839,7 +4839,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>0.5097875303553592</v>
+        <v>0.5337100805120139</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4850,13 +4850,13 @@
         <v>0.42</v>
       </c>
       <c r="B44">
-        <v>0.3189533922133359</v>
+        <v>0.3120434453029994</v>
       </c>
       <c r="C44">
-        <v>9517.232880788564</v>
+        <v>10056.12496708971</v>
       </c>
       <c r="D44">
-        <v>20598.61288078857</v>
+        <v>21137.50496708971</v>
       </c>
       <c r="E44">
         <v>2678.08</v>
@@ -4883,37 +4883,37 @@
         <v>1991.289795918367</v>
       </c>
       <c r="M44">
-        <v>4001.388261300397</v>
+        <v>3822.033561300397</v>
       </c>
       <c r="N44">
-        <v>-2010.09846538203</v>
+        <v>-1830.743765382029</v>
       </c>
       <c r="O44">
-        <v>-703.5344628837104</v>
+        <v>-640.7603178837102</v>
       </c>
       <c r="P44">
-        <v>-1306.564002498319</v>
+        <v>-1189.983447498319</v>
       </c>
       <c r="Q44">
-        <v>661.635997501681</v>
+        <v>778.2165525016812</v>
       </c>
       <c r="R44">
         <v>0.7241379310344827</v>
       </c>
       <c r="S44">
-        <v>0.3497965294490009</v>
+        <v>0.3487448968449725</v>
       </c>
       <c r="T44">
-        <v>1.494014618565401</v>
+        <v>1.488481029797811</v>
       </c>
       <c r="U44">
-        <v>0.3346487374989669</v>
+        <v>0.3196487374989669</v>
       </c>
       <c r="V44">
-        <v>0.1741774062047477</v>
+        <v>0.1823509441749381</v>
       </c>
       <c r="W44">
-        <v>0.2763604884117034</v>
+        <v>0.2613604884117033</v>
       </c>
       <c r="X44" t="inlineStr">
         <is>
@@ -4921,7 +4921,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>0.497649732013565</v>
+        <v>0.5210026976426804</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4932,13 +4932,13 @@
         <v>0.43</v>
       </c>
       <c r="B45">
-        <v>0.3218418795883256</v>
+        <v>0.3147819326779892</v>
       </c>
       <c r="C45">
-        <v>9017.00010395633</v>
+        <v>9556.235418499748</v>
       </c>
       <c r="D45">
-        <v>20383.07010395633</v>
+        <v>20922.30541849975</v>
       </c>
       <c r="E45">
         <v>2962.77</v>
@@ -4965,37 +4965,37 @@
         <v>1991.289795918367</v>
       </c>
       <c r="M45">
-        <v>4096.659410378978</v>
+        <v>3913.034360378978</v>
       </c>
       <c r="N45">
-        <v>-2105.369614460611</v>
+        <v>-1921.74456446061</v>
       </c>
       <c r="O45">
-        <v>-736.8793650612138</v>
+        <v>-672.6105975612136</v>
       </c>
       <c r="P45">
-        <v>-1368.490249399397</v>
+        <v>-1249.133966899397</v>
       </c>
       <c r="Q45">
-        <v>599.709750600603</v>
+        <v>719.0660331006034</v>
       </c>
       <c r="R45">
         <v>0.7543859649122806</v>
       </c>
       <c r="S45">
-        <v>0.3551298018954746</v>
+        <v>0.3540597195966387</v>
       </c>
       <c r="T45">
-        <v>1.52022540134725</v>
+        <v>1.514594732074965</v>
       </c>
       <c r="U45">
-        <v>0.3346487374989669</v>
+        <v>0.3196487374989669</v>
       </c>
       <c r="V45">
-        <v>0.1701267688511489</v>
+        <v>0.1781102245429628</v>
       </c>
       <c r="W45">
-        <v>0.2777160290881514</v>
+        <v>0.2627160290881513</v>
       </c>
       <c r="X45" t="inlineStr">
         <is>
@@ -5003,7 +5003,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>0.4860764824318541</v>
+        <v>0.5088863558370366</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5014,13 +5014,13 @@
         <v>0.44</v>
       </c>
       <c r="B46">
-        <v>0.3247303669633153</v>
+        <v>0.3175204200529788</v>
       </c>
       <c r="C46">
-        <v>8521.23147060498</v>
+        <v>9060.683572956201</v>
       </c>
       <c r="D46">
-        <v>20171.99147060498</v>
+        <v>20711.4435729562</v>
       </c>
       <c r="E46">
         <v>3247.460000000001</v>
@@ -5047,37 +5047,37 @@
         <v>1991.289795918367</v>
       </c>
       <c r="M46">
-        <v>4191.930559457559</v>
+        <v>4004.035159457559</v>
       </c>
       <c r="N46">
-        <v>-2200.640763539192</v>
+        <v>-2012.745363539192</v>
       </c>
       <c r="O46">
-        <v>-770.2242672387169</v>
+        <v>-704.460877238717</v>
       </c>
       <c r="P46">
-        <v>-1430.416496300475</v>
+        <v>-1308.284486300475</v>
       </c>
       <c r="Q46">
-        <v>537.7835036995257</v>
+        <v>659.9155136995255</v>
       </c>
       <c r="R46">
         <v>0.7857142857142857</v>
       </c>
       <c r="S46">
-        <v>0.3606535483578938</v>
+        <v>0.3595643574465786</v>
       </c>
       <c r="T46">
-        <v>1.547372283514166</v>
+        <v>1.541641066576304</v>
       </c>
       <c r="U46">
-        <v>0.3346487374989669</v>
+        <v>0.3196487374989669</v>
       </c>
       <c r="V46">
-        <v>0.1662602513772592</v>
+        <v>0.1740622648942591</v>
       </c>
       <c r="W46">
-        <v>0.2790099542793062</v>
+        <v>0.2640099542793062</v>
       </c>
       <c r="X46" t="inlineStr">
         <is>
@@ -5085,7 +5085,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>0.475029289649312</v>
+        <v>0.4973207568407403</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5096,13 +5096,13 @@
         <v>0.45</v>
       </c>
       <c r="B47">
-        <v>0.327618854338305</v>
+        <v>0.3202589074279685</v>
       </c>
       <c r="C47">
-        <v>8029.789715730201</v>
+        <v>8569.339588671728</v>
       </c>
       <c r="D47">
-        <v>19965.2397157302</v>
+        <v>20504.78958867173</v>
       </c>
       <c r="E47">
         <v>3532.150000000001</v>
@@ -5129,37 +5129,37 @@
         <v>1991.289795918367</v>
       </c>
       <c r="M47">
-        <v>4287.20170853614</v>
+        <v>4095.03595853614</v>
       </c>
       <c r="N47">
-        <v>-2295.911912617773</v>
+        <v>-2103.746162617773</v>
       </c>
       <c r="O47">
-        <v>-803.5691694162205</v>
+        <v>-736.3111569162204</v>
       </c>
       <c r="P47">
-        <v>-1492.342743201552</v>
+        <v>-1367.435005701552</v>
       </c>
       <c r="Q47">
-        <v>475.8572567984479</v>
+        <v>600.7649942984478</v>
       </c>
       <c r="R47">
         <v>0.8181818181818181</v>
       </c>
       <c r="S47">
-        <v>0.3663781583280373</v>
+        <v>0.3652691639456074</v>
       </c>
       <c r="T47">
-        <v>1.575506325032605</v>
+        <v>1.569670904150419</v>
       </c>
       <c r="U47">
-        <v>0.3346487374989669</v>
+        <v>0.3196487374989669</v>
       </c>
       <c r="V47">
-        <v>0.1625655791244312</v>
+        <v>0.1701942145632755</v>
       </c>
       <c r="W47">
-        <v>0.2802463716841876</v>
+        <v>0.2652463716841876</v>
       </c>
       <c r="X47" t="inlineStr">
         <is>
@@ -5167,7 +5167,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>0.4644730832126606</v>
+        <v>0.4862691844665016</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5178,13 +5178,13 @@
         <v>0.46</v>
       </c>
       <c r="B48">
-        <v>0.3305073417132947</v>
+        <v>0.3229973948029581</v>
       </c>
       <c r="C48">
-        <v>7542.543144794976</v>
+        <v>8082.078754788852</v>
       </c>
       <c r="D48">
-        <v>19762.68314479498</v>
+        <v>20302.21875478885</v>
       </c>
       <c r="E48">
         <v>3816.84</v>
@@ -5211,37 +5211,37 @@
         <v>1991.289795918367</v>
       </c>
       <c r="M48">
-        <v>4382.472857614721</v>
+        <v>4186.036757614721</v>
       </c>
       <c r="N48">
-        <v>-2391.183061696353</v>
+        <v>-2194.746961696354</v>
       </c>
       <c r="O48">
-        <v>-836.9140715937236</v>
+        <v>-768.1614365937237</v>
       </c>
       <c r="P48">
-        <v>-1554.26899010263</v>
+        <v>-1426.58552510263</v>
       </c>
       <c r="Q48">
-        <v>413.9310098973706</v>
+        <v>541.6144748973704</v>
       </c>
       <c r="R48">
         <v>0.8518518518518519</v>
       </c>
       <c r="S48">
-        <v>0.3723147908896676</v>
+        <v>0.3711852595742297</v>
       </c>
       <c r="T48">
-        <v>1.604682368088765</v>
+        <v>1.598738883856908</v>
       </c>
       <c r="U48">
-        <v>0.3346487374989669</v>
+        <v>0.3196487374989669</v>
       </c>
       <c r="V48">
-        <v>0.1590315447956392</v>
+        <v>0.1664943403336391</v>
       </c>
       <c r="W48">
-        <v>0.2814290318105959</v>
+        <v>0.2664290318105959</v>
       </c>
       <c r="X48" t="inlineStr">
         <is>
@@ -5249,7 +5249,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>0.454375842273255</v>
+        <v>0.475698115238969</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5260,13 +5260,13 @@
         <v>0.47</v>
       </c>
       <c r="B49">
-        <v>0.3333958290882843</v>
+        <v>0.3257358821779478</v>
       </c>
       <c r="C49">
-        <v>7059.365353992773</v>
+        <v>7598.781240411947</v>
       </c>
       <c r="D49">
-        <v>19564.19535399277</v>
+        <v>20103.61124041195</v>
       </c>
       <c r="E49">
         <v>4101.530000000001</v>
@@ -5293,37 +5293,37 @@
         <v>1991.289795918367</v>
       </c>
       <c r="M49">
-        <v>4477.744006693301</v>
+        <v>4277.037556693302</v>
       </c>
       <c r="N49">
-        <v>-2486.454210774934</v>
+        <v>-2285.747760774934</v>
       </c>
       <c r="O49">
-        <v>-870.2589737712268</v>
+        <v>-800.011716271227</v>
       </c>
       <c r="P49">
-        <v>-1616.195237003707</v>
+        <v>-1485.736044503707</v>
       </c>
       <c r="Q49">
-        <v>352.0047629962933</v>
+        <v>482.463955496293</v>
       </c>
       <c r="R49">
         <v>0.8867924528301887</v>
       </c>
       <c r="S49">
-        <v>0.3784754473215481</v>
+        <v>0.3773246040944982</v>
       </c>
       <c r="T49">
-        <v>1.63495939390176</v>
+        <v>1.628903768457982</v>
       </c>
       <c r="U49">
-        <v>0.3346487374989669</v>
+        <v>0.3196487374989669</v>
       </c>
       <c r="V49">
-        <v>0.1556478949063703</v>
+        <v>0.162951907560583</v>
       </c>
       <c r="W49">
-        <v>0.2825613659741782</v>
+        <v>0.2675613659741782</v>
       </c>
       <c r="X49" t="inlineStr">
         <is>
@@ -5331,7 +5331,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>0.4447082711610582</v>
+        <v>0.4655768787445228</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5342,13 +5342,13 @@
         <v>0.48</v>
       </c>
       <c r="B50">
-        <v>0.3362843164632739</v>
+        <v>0.3284743695529374</v>
       </c>
       <c r="C50">
-        <v>6580.134967200556</v>
+        <v>7119.331858227295</v>
       </c>
       <c r="D50">
-        <v>19369.65496720056</v>
+        <v>19908.8518582273</v>
       </c>
       <c r="E50">
         <v>4386.219999999999</v>
@@ -5375,37 +5375,37 @@
         <v>1991.289795918367</v>
       </c>
       <c r="M50">
-        <v>4573.015155771882</v>
+        <v>4368.038355771882</v>
       </c>
       <c r="N50">
-        <v>-2581.725359853514</v>
+        <v>-2376.748559853515</v>
       </c>
       <c r="O50">
-        <v>-903.60387594873</v>
+        <v>-831.8619959487302</v>
       </c>
       <c r="P50">
-        <v>-1678.121483904784</v>
+        <v>-1544.886563904785</v>
       </c>
       <c r="Q50">
-        <v>290.0785160952159</v>
+        <v>423.3134360952154</v>
       </c>
       <c r="R50">
         <v>0.923076923076923</v>
       </c>
       <c r="S50">
-        <v>0.3848730520777318</v>
+        <v>0.3837000772501616</v>
       </c>
       <c r="T50">
-        <v>1.666400920707563</v>
+        <v>1.660228840928327</v>
       </c>
       <c r="U50">
-        <v>0.3346487374989669</v>
+        <v>0.3196487374989669</v>
       </c>
       <c r="V50">
-        <v>0.1524052304291543</v>
+        <v>0.1595570761530708</v>
       </c>
       <c r="W50">
-        <v>0.2836465195476113</v>
+        <v>0.2686465195476113</v>
       </c>
       <c r="X50" t="inlineStr">
         <is>
@@ -5413,7 +5413,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>0.4354435155118694</v>
+        <v>0.4558773604373453</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5424,13 +5424,13 @@
         <v>0.49</v>
       </c>
       <c r="B51">
-        <v>0.3391728038382636</v>
+        <v>0.3312128569279271</v>
       </c>
       <c r="C51">
-        <v>6104.735388471128</v>
+        <v>6643.619841731159</v>
       </c>
       <c r="D51">
-        <v>19178.94538847113</v>
+        <v>19717.82984173116</v>
       </c>
       <c r="E51">
         <v>4670.91</v>
@@ -5457,37 +5457,37 @@
         <v>1991.289795918367</v>
       </c>
       <c r="M51">
-        <v>4668.286304850463</v>
+        <v>4459.039154850463</v>
       </c>
       <c r="N51">
-        <v>-2676.996508932096</v>
+        <v>-2467.749358932096</v>
       </c>
       <c r="O51">
-        <v>-936.9487781262335</v>
+        <v>-863.7122756262335</v>
       </c>
       <c r="P51">
-        <v>-1740.047730805862</v>
+        <v>-1604.037083305862</v>
       </c>
       <c r="Q51">
-        <v>228.1522691941379</v>
+        <v>364.1629166941379</v>
       </c>
       <c r="R51">
         <v>0.9607843137254901</v>
       </c>
       <c r="S51">
-        <v>0.3915215432949422</v>
+        <v>0.3903255689609491</v>
       </c>
       <c r="T51">
-        <v>1.699075448564574</v>
+        <v>1.692782347613196</v>
       </c>
       <c r="U51">
-        <v>0.3346487374989669</v>
+        <v>0.3196487374989669</v>
       </c>
       <c r="V51">
-        <v>0.1492949196040695</v>
+        <v>0.1563008092928041</v>
       </c>
       <c r="W51">
-        <v>0.2846873811384553</v>
+        <v>0.2696873811384553</v>
       </c>
       <c r="X51" t="inlineStr">
         <is>
@@ -5495,7 +5495,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>0.4265569131544843</v>
+        <v>0.4465737408365832</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5506,13 +5506,13 @@
         <v>0.5</v>
       </c>
       <c r="B52">
-        <v>0.3420612912132532</v>
+        <v>0.3339513443029168</v>
       </c>
       <c r="C52">
-        <v>5633.054569004482</v>
+        <v>6171.538635160865</v>
       </c>
       <c r="D52">
-        <v>18991.95456900448</v>
+        <v>19530.43863516087</v>
       </c>
       <c r="E52">
         <v>4955.6</v>
@@ -5539,37 +5539,37 @@
         <v>1991.289795918367</v>
       </c>
       <c r="M52">
-        <v>4763.557453929045</v>
+        <v>4550.039953929044</v>
       </c>
       <c r="N52">
-        <v>-2772.267658010677</v>
+        <v>-2558.750158010676</v>
       </c>
       <c r="O52">
-        <v>-970.293680303737</v>
+        <v>-895.5625553037366</v>
       </c>
       <c r="P52">
-        <v>-1801.97397770694</v>
+        <v>-1663.18760270694</v>
       </c>
       <c r="Q52">
-        <v>166.2260222930599</v>
+        <v>305.0123972930605</v>
       </c>
       <c r="R52">
         <v>1</v>
       </c>
       <c r="S52">
-        <v>0.398435974160841</v>
+        <v>0.3972160803401681</v>
       </c>
       <c r="T52">
-        <v>1.733056957535866</v>
+        <v>1.72663799456546</v>
       </c>
       <c r="U52">
-        <v>0.3346487374989669</v>
+        <v>0.3196487374989669</v>
       </c>
       <c r="V52">
-        <v>0.1463090212119881</v>
+        <v>0.153174793106948</v>
       </c>
       <c r="W52">
-        <v>0.2856866082656655</v>
+        <v>0.2706866082656655</v>
       </c>
       <c r="X52" t="inlineStr">
         <is>
@@ -5577,7 +5577,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>0.4180257748913946</v>
+        <v>0.4376422660198515</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5588,13 +5588,13 @@
         <v>0.51</v>
       </c>
       <c r="B53">
-        <v>0.3449497785882429</v>
+        <v>0.3366898316779066</v>
       </c>
       <c r="C53">
-        <v>5164.984787619267</v>
+        <v>5702.985695291516</v>
       </c>
       <c r="D53">
-        <v>18808.57478761927</v>
+        <v>19346.57569529152</v>
       </c>
       <c r="E53">
         <v>5240.290000000001</v>
@@ -5621,37 +5621,37 @@
         <v>1991.289795918367</v>
       </c>
       <c r="M53">
-        <v>4858.828603007625</v>
+        <v>4641.040753007625</v>
       </c>
       <c r="N53">
-        <v>-2867.538807089258</v>
+        <v>-2649.750957089258</v>
       </c>
       <c r="O53">
-        <v>-1003.63858248124</v>
+        <v>-927.4128349812403</v>
       </c>
       <c r="P53">
-        <v>-1863.900224608018</v>
+        <v>-1722.338122108018</v>
       </c>
       <c r="Q53">
-        <v>104.2997753919826</v>
+        <v>245.8618778919827</v>
       </c>
       <c r="R53">
         <v>1.040816326530612</v>
       </c>
       <c r="S53">
-        <v>0.4056326266947358</v>
+        <v>0.4043878370818043</v>
       </c>
       <c r="T53">
-        <v>1.768425466873332</v>
+        <v>1.761875504658633</v>
       </c>
       <c r="U53">
-        <v>0.3346487374989669</v>
+        <v>0.3196487374989669</v>
       </c>
       <c r="V53">
-        <v>0.1434402168744981</v>
+        <v>0.1501713657911255</v>
       </c>
       <c r="W53">
-        <v>0.2866466500153381</v>
+        <v>0.2716466500153381</v>
       </c>
       <c r="X53" t="inlineStr">
         <is>
@@ -5659,7 +5659,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>0.4098291910699947</v>
+        <v>0.4290610451175014</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5670,13 +5670,13 @@
         <v>0.52</v>
       </c>
       <c r="B54">
-        <v>0.3478382659632326</v>
+        <v>0.3394283190528962</v>
       </c>
       <c r="C54">
-        <v>4700.422443820946</v>
+        <v>5237.862304323891</v>
       </c>
       <c r="D54">
-        <v>18628.70244382095</v>
+        <v>19166.14230432389</v>
       </c>
       <c r="E54">
         <v>5524.980000000001</v>
@@ -5703,37 +5703,37 @@
         <v>1991.289795918367</v>
       </c>
       <c r="M54">
-        <v>4954.099752086207</v>
+        <v>4732.041552086206</v>
       </c>
       <c r="N54">
-        <v>-2962.809956167839</v>
+        <v>-2740.751756167839</v>
       </c>
       <c r="O54">
-        <v>-1036.983484658744</v>
+        <v>-959.2631146587435</v>
       </c>
       <c r="P54">
-        <v>-1925.826471509095</v>
+        <v>-1781.488641509095</v>
       </c>
       <c r="Q54">
-        <v>42.37352849090485</v>
+        <v>186.711358490905</v>
       </c>
       <c r="R54">
         <v>1.083333333333333</v>
       </c>
       <c r="S54">
-        <v>0.4131291397508761</v>
+        <v>0.4118584170210084</v>
       </c>
       <c r="T54">
-        <v>1.80526766409986</v>
+        <v>1.798581244339021</v>
       </c>
       <c r="U54">
-        <v>0.3346487374989669</v>
+        <v>0.3196487374989669</v>
       </c>
       <c r="V54">
-        <v>0.1406817511653732</v>
+        <v>0.1472834549105269</v>
       </c>
       <c r="W54">
-        <v>0.287569767082331</v>
+        <v>0.2725697670823309</v>
       </c>
       <c r="X54" t="inlineStr">
         <is>
@@ -5741,7 +5741,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>0.4019478604724948</v>
+        <v>0.4208098711729341</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5752,13 +5752,13 @@
         <v>0.53</v>
       </c>
       <c r="B55">
-        <v>0.3507267533382223</v>
+        <v>0.3421668064278858</v>
       </c>
       <c r="C55">
-        <v>4239.267862631068</v>
+        <v>4776.073393146004</v>
       </c>
       <c r="D55">
-        <v>18452.23786263107</v>
+        <v>18989.04339314601</v>
       </c>
       <c r="E55">
         <v>5809.670000000002</v>
@@ -5785,37 +5785,37 @@
         <v>1991.289795918367</v>
       </c>
       <c r="M55">
-        <v>5049.370901164787</v>
+        <v>4823.042351164787</v>
       </c>
       <c r="N55">
-        <v>-3058.08110524642</v>
+        <v>-2831.752555246419</v>
       </c>
       <c r="O55">
-        <v>-1070.328386836247</v>
+        <v>-991.1133943362468</v>
       </c>
       <c r="P55">
-        <v>-1987.752718410173</v>
+        <v>-1840.639160910173</v>
       </c>
       <c r="Q55">
-        <v>-19.55271841017247</v>
+        <v>127.5608390898276</v>
       </c>
       <c r="R55">
         <v>1.127659574468085</v>
       </c>
       <c r="S55">
-        <v>0.4209446533625969</v>
+        <v>0.4196468939789023</v>
       </c>
       <c r="T55">
-        <v>1.843677614399857</v>
+        <v>1.836848930388788</v>
       </c>
       <c r="U55">
-        <v>0.3346487374989669</v>
+        <v>0.3196487374989669</v>
       </c>
       <c r="V55">
-        <v>0.1380273785018756</v>
+        <v>0.1445045217990076</v>
       </c>
       <c r="W55">
-        <v>0.2884580495430222</v>
+        <v>0.2734580495430222</v>
       </c>
       <c r="X55" t="inlineStr">
         <is>
@@ -5823,7 +5823,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>0.3943639385767873</v>
+        <v>0.4128700622828787</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5834,13 +5834,13 @@
         <v>0.54</v>
       </c>
       <c r="B56">
-        <v>0.3536152407132119</v>
+        <v>0.3449052938028755</v>
       </c>
       <c r="C56">
-        <v>3781.425110405353</v>
+        <v>4317.527374303585</v>
       </c>
       <c r="D56">
-        <v>18279.08511040535</v>
+        <v>18815.18737430359</v>
       </c>
       <c r="E56">
         <v>6094.360000000001</v>
@@ -5867,37 +5867,37 @@
         <v>1991.289795918367</v>
       </c>
       <c r="M56">
-        <v>5144.642050243368</v>
+        <v>4914.043150243368</v>
       </c>
       <c r="N56">
-        <v>-3153.352254325</v>
+        <v>-2922.753354325</v>
       </c>
       <c r="O56">
-        <v>-1103.67328901375</v>
+        <v>-1022.96367401375</v>
       </c>
       <c r="P56">
-        <v>-2049.67896531125</v>
+        <v>-1899.78968031125</v>
       </c>
       <c r="Q56">
-        <v>-81.47896531124979</v>
+        <v>68.41031968874995</v>
       </c>
       <c r="R56">
         <v>1.173913043478261</v>
       </c>
       <c r="S56">
-        <v>0.4290999719139577</v>
+        <v>0.427774000369748</v>
       </c>
       <c r="T56">
-        <v>1.883757562538985</v>
+        <v>1.876780428875501</v>
       </c>
       <c r="U56">
-        <v>0.3346487374989669</v>
+        <v>0.3196487374989669</v>
       </c>
       <c r="V56">
-        <v>0.135471315937026</v>
+        <v>0.141828512136063</v>
       </c>
       <c r="W56">
-        <v>0.2893134326533175</v>
+        <v>0.2743134326533175</v>
       </c>
       <c r="X56" t="inlineStr">
         <is>
@@ -5905,7 +5905,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>0.3870609026772173</v>
+        <v>0.4052243203887513</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5916,13 +5916,13 @@
         <v>0.55</v>
       </c>
       <c r="B57">
-        <v>0.3565037280882016</v>
+        <v>0.3476437811778652</v>
       </c>
       <c r="C57">
-        <v>3326.801820925222</v>
+        <v>3862.135984062799</v>
       </c>
       <c r="D57">
-        <v>18109.15182092522</v>
+        <v>18644.4859840628</v>
       </c>
       <c r="E57">
         <v>6379.050000000001</v>
@@ -5949,37 +5949,37 @@
         <v>1991.289795918367</v>
       </c>
       <c r="M57">
-        <v>5239.913199321949</v>
+        <v>5005.043949321949</v>
       </c>
       <c r="N57">
-        <v>-3248.623403403582</v>
+        <v>-3013.754153403582</v>
       </c>
       <c r="O57">
-        <v>-1137.018191191253</v>
+        <v>-1054.813953691254</v>
       </c>
       <c r="P57">
-        <v>-2111.605212212328</v>
+        <v>-1958.940199712328</v>
       </c>
       <c r="Q57">
-        <v>-143.405212212328</v>
+        <v>9.259800287672078</v>
       </c>
       <c r="R57">
         <v>1.222222222222223</v>
       </c>
       <c r="S57">
-        <v>0.4376177490676012</v>
+        <v>0.4362623114890758</v>
       </c>
       <c r="T57">
-        <v>1.925618841706518</v>
+        <v>1.91848666062829</v>
       </c>
       <c r="U57">
-        <v>0.3346487374989669</v>
+        <v>0.3196487374989669</v>
       </c>
       <c r="V57">
-        <v>0.1330082011018074</v>
+        <v>0.1392498119154073</v>
       </c>
       <c r="W57">
-        <v>0.2901377109232384</v>
+        <v>0.2751377109232384</v>
       </c>
       <c r="X57" t="inlineStr">
         <is>
@@ -5987,7 +5987,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>0.3800234317194496</v>
+        <v>0.3978566054725922</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -5998,13 +5998,13 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="B58">
-        <v>0.3593922154631913</v>
+        <v>0.3503822685528548</v>
       </c>
       <c r="C58">
-        <v>2875.309031100694</v>
+        <v>3409.81413299309</v>
       </c>
       <c r="D58">
-        <v>17942.3490311007</v>
+        <v>18476.85413299309</v>
       </c>
       <c r="E58">
         <v>6663.740000000002</v>
@@ -6031,37 +6031,37 @@
         <v>1991.289795918367</v>
       </c>
       <c r="M58">
-        <v>5335.18434840053</v>
+        <v>5096.04474840053</v>
       </c>
       <c r="N58">
-        <v>-3343.894552482163</v>
+        <v>-3104.754952482162</v>
       </c>
       <c r="O58">
-        <v>-1170.363093368757</v>
+        <v>-1086.664233368757</v>
       </c>
       <c r="P58">
-        <v>-2173.531459113406</v>
+        <v>-2018.090719113406</v>
       </c>
       <c r="Q58">
-        <v>-205.3314591134058</v>
+        <v>-49.89071911340534</v>
       </c>
       <c r="R58">
         <v>1.272727272727273</v>
       </c>
       <c r="S58">
-        <v>0.4465226979100467</v>
+        <v>0.4451364549320092</v>
       </c>
       <c r="T58">
-        <v>1.969382906290757</v>
+        <v>1.962088630188023</v>
       </c>
       <c r="U58">
-        <v>0.3346487374989669</v>
+        <v>0.3196487374989669</v>
       </c>
       <c r="V58">
-        <v>0.1306330546535608</v>
+        <v>0.1367632081312035</v>
       </c>
       <c r="W58">
-        <v>0.2909325506835193</v>
+        <v>0.2759325506835192</v>
       </c>
       <c r="X58" t="inlineStr">
         <is>
@@ -6069,7 +6069,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>0.3732372990101737</v>
+        <v>0.3907520232320102</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6080,13 +6080,13 @@
         <v>0.5700000000000001</v>
       </c>
       <c r="B59">
-        <v>0.362280702838181</v>
+        <v>0.3531207559278445</v>
       </c>
       <c r="C59">
-        <v>2426.861025670292</v>
+        <v>2960.479764538493</v>
       </c>
       <c r="D59">
-        <v>17778.5910256703</v>
+        <v>18312.2097645385</v>
       </c>
       <c r="E59">
         <v>6948.430000000002</v>
@@ -6113,37 +6113,37 @@
         <v>1991.289795918367</v>
       </c>
       <c r="M59">
-        <v>5430.455497479111</v>
+        <v>5187.045547479111</v>
       </c>
       <c r="N59">
-        <v>-3439.165701560743</v>
+        <v>-3195.755751560743</v>
       </c>
       <c r="O59">
-        <v>-1203.70799554626</v>
+        <v>-1118.51451304626</v>
       </c>
       <c r="P59">
-        <v>-2235.457706014483</v>
+        <v>-2077.241238514483</v>
       </c>
       <c r="Q59">
-        <v>-267.2577060144831</v>
+        <v>-109.0412385144832</v>
       </c>
       <c r="R59">
         <v>1.325581395348838</v>
       </c>
       <c r="S59">
-        <v>0.4558418304195826</v>
+        <v>0.4544233492327537</v>
       </c>
       <c r="T59">
-        <v>2.015182508762635</v>
+        <v>2.007718598331931</v>
       </c>
       <c r="U59">
-        <v>0.3346487374989669</v>
+        <v>0.3196487374989669</v>
       </c>
       <c r="V59">
-        <v>0.1283412466771825</v>
+        <v>0.134363853602586</v>
       </c>
       <c r="W59">
-        <v>0.2916995013294043</v>
+        <v>0.2766995013294043</v>
       </c>
       <c r="X59" t="inlineStr">
         <is>
@@ -6151,7 +6151,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>0.3666892762205215</v>
+        <v>0.3838967245788171</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6162,13 +6162,13 @@
         <v>0.58</v>
       </c>
       <c r="B60">
-        <v>0.3651691902131706</v>
+        <v>0.3558592433028341</v>
       </c>
       <c r="C60">
-        <v>1981.375190328523</v>
+        <v>2514.053721083823</v>
       </c>
       <c r="D60">
-        <v>17617.79519032852</v>
+        <v>18150.47372108382</v>
       </c>
       <c r="E60">
         <v>7233.120000000001</v>
@@ -6195,37 +6195,37 @@
         <v>1991.289795918367</v>
       </c>
       <c r="M60">
-        <v>5525.726646557691</v>
+        <v>5278.046346557691</v>
       </c>
       <c r="N60">
-        <v>-3534.436850639324</v>
+        <v>-3286.756550639324</v>
       </c>
       <c r="O60">
-        <v>-1237.052897723763</v>
+        <v>-1150.364792723763</v>
       </c>
       <c r="P60">
-        <v>-2297.383952915561</v>
+        <v>-2136.39175791556</v>
       </c>
       <c r="Q60">
-        <v>-329.1839529155604</v>
+        <v>-168.1917579155602</v>
       </c>
       <c r="R60">
         <v>1.380952380952381</v>
       </c>
       <c r="S60">
-        <v>0.4656047311438583</v>
+        <v>0.4641524765954382</v>
       </c>
       <c r="T60">
-        <v>2.063163044685554</v>
+        <v>2.055521422101739</v>
       </c>
       <c r="U60">
-        <v>0.3346487374989669</v>
+        <v>0.3196487374989669</v>
       </c>
       <c r="V60">
-        <v>0.1261284665620587</v>
+        <v>0.1320472354370241</v>
       </c>
       <c r="W60">
-        <v>0.2924400054012933</v>
+        <v>0.2774400054012933</v>
       </c>
       <c r="X60" t="inlineStr">
         <is>
@@ -6233,7 +6233,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>0.3603670473201678</v>
+        <v>0.3772778155343547</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6244,13 +6244,13 @@
         <v>0.59</v>
       </c>
       <c r="B61">
-        <v>0.3680576775881603</v>
+        <v>0.3585977306778237</v>
       </c>
       <c r="C61">
-        <v>1538.771872752102</v>
+        <v>2070.459617056087</v>
       </c>
       <c r="D61">
-        <v>17459.8818727521</v>
+        <v>17991.56961705609</v>
       </c>
       <c r="E61">
         <v>7517.809999999999</v>
@@ -6277,37 +6277,37 @@
         <v>1991.289795918367</v>
       </c>
       <c r="M61">
-        <v>5620.997795636272</v>
+        <v>5369.047145636272</v>
       </c>
       <c r="N61">
-        <v>-3629.707999717904</v>
+        <v>-3377.757349717905</v>
       </c>
       <c r="O61">
-        <v>-1270.397799901266</v>
+        <v>-1182.215072401267</v>
       </c>
       <c r="P61">
-        <v>-2359.310199816638</v>
+        <v>-2195.542277316638</v>
       </c>
       <c r="Q61">
-        <v>-391.1101998166378</v>
+        <v>-227.342277316638</v>
       </c>
       <c r="R61">
         <v>1.439024390243902</v>
       </c>
       <c r="S61">
-        <v>0.4758438709278549</v>
+        <v>0.4743561955367903</v>
       </c>
       <c r="T61">
-        <v>2.113484094555934</v>
+        <v>2.105656090933488</v>
       </c>
       <c r="U61">
-        <v>0.3346487374989669</v>
+        <v>0.3196487374989669</v>
       </c>
       <c r="V61">
-        <v>0.1239906959423628</v>
+        <v>0.1298091467008034</v>
       </c>
       <c r="W61">
-        <v>0.2931554076402369</v>
+        <v>0.2781554076402369</v>
       </c>
       <c r="X61" t="inlineStr">
         <is>
@@ -6315,7 +6315,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>0.3542591312638937</v>
+        <v>0.3708832762880098</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6326,13 +6326,13 @@
         <v>0.6</v>
       </c>
       <c r="B62">
-        <v>0.37094616496315</v>
+        <v>0.3613362180528135</v>
       </c>
       <c r="C62">
-        <v>1098.974251033822</v>
+        <v>1629.62371863403</v>
       </c>
       <c r="D62">
-        <v>17304.77425103382</v>
+        <v>17835.42371863403</v>
       </c>
       <c r="E62">
         <v>7802.499999999998</v>
@@ -6359,37 +6359,37 @@
         <v>1991.289795918367</v>
       </c>
       <c r="M62">
-        <v>5716.268944714852</v>
+        <v>5460.047944714852</v>
       </c>
       <c r="N62">
-        <v>-3724.979148796485</v>
+        <v>-3468.758148796484</v>
       </c>
       <c r="O62">
-        <v>-1303.74270207877</v>
+        <v>-1214.065352078769</v>
       </c>
       <c r="P62">
-        <v>-2421.236446717715</v>
+        <v>-2254.692796717715</v>
       </c>
       <c r="Q62">
-        <v>-453.0364467177151</v>
+        <v>-286.492796717715</v>
       </c>
       <c r="R62">
         <v>1.5</v>
       </c>
       <c r="S62">
-        <v>0.4865949677010513</v>
+        <v>0.48507010042521</v>
       </c>
       <c r="T62">
-        <v>2.166321196919832</v>
+        <v>2.158297493206825</v>
       </c>
       <c r="U62">
-        <v>0.3346487374989669</v>
+        <v>0.3196487374989669</v>
       </c>
       <c r="V62">
-        <v>0.1219241843433234</v>
+        <v>0.1276456609224567</v>
       </c>
       <c r="W62">
-        <v>0.2938469631378824</v>
+        <v>0.2788469631378824</v>
       </c>
       <c r="X62" t="inlineStr">
         <is>
@@ -6397,7 +6397,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>0.3483548124094955</v>
+        <v>0.3647018883498763</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6408,13 +6408,13 @@
         <v>0.61</v>
       </c>
       <c r="B63">
-        <v>0.3738346523381396</v>
+        <v>0.3640747054278032</v>
       </c>
       <c r="C63">
-        <v>661.9082090672746</v>
+        <v>1191.474829667586</v>
       </c>
       <c r="D63">
-        <v>17152.39820906728</v>
+        <v>17681.96482966759</v>
       </c>
       <c r="E63">
         <v>8087.190000000001</v>
@@ -6441,37 +6441,37 @@
         <v>1991.289795918367</v>
       </c>
       <c r="M63">
-        <v>5811.540093793434</v>
+        <v>5551.048743793433</v>
       </c>
       <c r="N63">
-        <v>-3820.250297875066</v>
+        <v>-3559.758947875066</v>
       </c>
       <c r="O63">
-        <v>-1337.087604256273</v>
+        <v>-1245.915631756273</v>
       </c>
       <c r="P63">
-        <v>-2483.162693618793</v>
+        <v>-2313.843316118793</v>
       </c>
       <c r="Q63">
-        <v>-514.9626936187929</v>
+        <v>-345.6433161187929</v>
       </c>
       <c r="R63">
         <v>1.564102564102564</v>
       </c>
       <c r="S63">
-        <v>0.497897402770309</v>
+        <v>0.4963334363335489</v>
       </c>
       <c r="T63">
-        <v>2.221867894276751</v>
+        <v>2.213638454571103</v>
       </c>
       <c r="U63">
-        <v>0.3346487374989669</v>
+        <v>0.3196487374989669</v>
       </c>
       <c r="V63">
-        <v>0.1199254272229411</v>
+        <v>0.1255531091040558</v>
       </c>
       <c r="W63">
-        <v>0.2945158446847854</v>
+        <v>0.2795158446847854</v>
       </c>
       <c r="X63" t="inlineStr">
         <is>
@@ -6479,7 +6479,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>0.3426440777798316</v>
+        <v>0.3587231688687307</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6490,13 +6490,13 @@
         <v>0.62</v>
       </c>
       <c r="B64">
-        <v>0.3767231397131293</v>
+        <v>0.3668131928027928</v>
       </c>
       <c r="C64">
-        <v>227.5022184579902</v>
+        <v>755.9441834365716</v>
       </c>
       <c r="D64">
-        <v>17002.68221845799</v>
+        <v>17531.12418343657</v>
       </c>
       <c r="E64">
         <v>8371.879999999999</v>
@@ -6523,37 +6523,37 @@
         <v>1991.289795918367</v>
       </c>
       <c r="M64">
-        <v>5906.811242872014</v>
+        <v>5642.049542872014</v>
       </c>
       <c r="N64">
-        <v>-3915.521446953647</v>
+        <v>-3650.759746953647</v>
       </c>
       <c r="O64">
-        <v>-1370.432506433776</v>
+        <v>-1277.765911433776</v>
       </c>
       <c r="P64">
-        <v>-2545.08894051987</v>
+        <v>-2372.993835519871</v>
       </c>
       <c r="Q64">
-        <v>-576.8889405198702</v>
+        <v>-404.7938355198703</v>
       </c>
       <c r="R64">
         <v>1.631578947368421</v>
       </c>
       <c r="S64">
-        <v>0.5097947028432119</v>
+        <v>0.508189579394958</v>
       </c>
       <c r="T64">
-        <v>2.280338102020876</v>
+        <v>2.271892098112448</v>
       </c>
       <c r="U64">
-        <v>0.3346487374989669</v>
+        <v>0.3196487374989669</v>
       </c>
       <c r="V64">
-        <v>0.1179911461387001</v>
+        <v>0.1235280589572161</v>
       </c>
       <c r="W64">
-        <v>0.2951631494075948</v>
+        <v>0.2801631494075948</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
@@ -6561,7 +6561,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>0.337117560396286</v>
+        <v>0.3529373113063319</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6572,13 +6572,13 @@
         <v>0.63</v>
       </c>
       <c r="B65">
-        <v>0.379611627088119</v>
+        <v>0.3695516801777825</v>
       </c>
       <c r="C65">
-        <v>-204.3127734345617</v>
+        <v>322.9653399026756</v>
       </c>
       <c r="D65">
-        <v>16855.55722656544</v>
+        <v>17382.83533990268</v>
       </c>
       <c r="E65">
         <v>8656.570000000002</v>
@@ -6605,37 +6605,37 @@
         <v>1991.289795918367</v>
       </c>
       <c r="M65">
-        <v>6002.082391950597</v>
+        <v>5733.050341950596</v>
       </c>
       <c r="N65">
-        <v>-4010.792596032229</v>
+        <v>-3741.760546032228</v>
       </c>
       <c r="O65">
-        <v>-1403.77740861128</v>
+        <v>-1309.61619111128</v>
       </c>
       <c r="P65">
-        <v>-2607.015187420949</v>
+        <v>-2432.144354920948</v>
       </c>
       <c r="Q65">
-        <v>-638.8151874209484</v>
+        <v>-463.9443549209482</v>
       </c>
       <c r="R65">
         <v>1.702702702702703</v>
       </c>
       <c r="S65">
-        <v>0.5223351002173527</v>
+        <v>0.5206865950542812</v>
       </c>
       <c r="T65">
-        <v>2.341968861534954</v>
+        <v>2.333294587250622</v>
       </c>
       <c r="U65">
-        <v>0.3346487374989669</v>
+        <v>0.3196487374989669</v>
       </c>
       <c r="V65">
-        <v>0.1161182708031651</v>
+        <v>0.1215672961166254</v>
       </c>
       <c r="W65">
-        <v>0.2957899047741245</v>
+        <v>0.2807899047741245</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
@@ -6643,7 +6643,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>0.3317664880090433</v>
+        <v>0.3473351317617869</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6654,13 +6654,13 @@
         <v>0.64</v>
       </c>
       <c r="B66">
-        <v>0.3825001144631086</v>
+        <v>0.3722901675527722</v>
       </c>
       <c r="C66">
-        <v>-633.6034496920802</v>
+        <v>-107.5259118674985</v>
       </c>
       <c r="D66">
-        <v>16710.95655030792</v>
+        <v>17237.0340881325</v>
       </c>
       <c r="E66">
         <v>8941.26</v>
@@ -6687,37 +6687,37 @@
         <v>1991.289795918367</v>
       </c>
       <c r="M66">
-        <v>6097.353541029177</v>
+        <v>5824.051141029177</v>
       </c>
       <c r="N66">
-        <v>-4106.06374511081</v>
+        <v>-3832.761345110809</v>
       </c>
       <c r="O66">
-        <v>-1437.122310788783</v>
+        <v>-1341.466470788783</v>
       </c>
       <c r="P66">
-        <v>-2668.941434322026</v>
+        <v>-2491.294874322026</v>
       </c>
       <c r="Q66">
-        <v>-700.7414343220257</v>
+        <v>-523.0948743220256</v>
       </c>
       <c r="R66">
         <v>1.777777777777778</v>
       </c>
       <c r="S66">
-        <v>0.5355721863345014</v>
+        <v>0.5338778893613446</v>
       </c>
       <c r="T66">
-        <v>2.407023552133147</v>
+        <v>2.398108325785362</v>
       </c>
       <c r="U66">
-        <v>0.3346487374989669</v>
+        <v>0.3196487374989669</v>
       </c>
       <c r="V66">
-        <v>0.1143039228218657</v>
+        <v>0.1196678071148031</v>
       </c>
       <c r="W66">
-        <v>0.2963970740354502</v>
+        <v>0.2813970740354502</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
@@ -6725,7 +6725,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>0.326582636633902</v>
+        <v>0.3419080203280089</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6736,13 +6736,13 @@
         <v>0.65</v>
       </c>
       <c r="B67">
-        <v>0.3853886018380983</v>
+        <v>0.3750286549277618</v>
       </c>
       <c r="C67">
-        <v>-1060.43422461296</v>
+        <v>-535.5916464097245</v>
       </c>
       <c r="D67">
-        <v>16568.81577538704</v>
+        <v>17093.65835359028</v>
       </c>
       <c r="E67">
         <v>9225.950000000003</v>
@@ -6769,37 +6769,37 @@
         <v>1991.289795918367</v>
       </c>
       <c r="M67">
-        <v>6192.624690107758</v>
+        <v>5915.051940107758</v>
       </c>
       <c r="N67">
-        <v>-4201.334894189391</v>
+        <v>-3923.762144189391</v>
       </c>
       <c r="O67">
-        <v>-1470.467212966287</v>
+        <v>-1373.316750466287</v>
       </c>
       <c r="P67">
-        <v>-2730.867681223104</v>
+        <v>-2550.445393723104</v>
       </c>
       <c r="Q67">
-        <v>-762.667681223104</v>
+        <v>-582.2453937231035</v>
       </c>
       <c r="R67">
         <v>1.857142857142857</v>
       </c>
       <c r="S67">
-        <v>0.5495656773726301</v>
+        <v>0.5478229719145259</v>
       </c>
       <c r="T67">
-        <v>2.475795653622666</v>
+        <v>2.466625706522087</v>
       </c>
       <c r="U67">
-        <v>0.3346487374989669</v>
+        <v>0.3196487374989669</v>
       </c>
       <c r="V67">
-        <v>0.1125454009322985</v>
+        <v>0.1178267639284215</v>
       </c>
       <c r="W67">
-        <v>0.2969855611656582</v>
+        <v>0.2819855611656581</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
@@ -6807,7 +6807,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>0.3215582883779958</v>
+        <v>0.3366478969383472</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6818,13 +6818,13 @@
         <v>0.66</v>
       </c>
       <c r="B68">
-        <v>0.3882770892130879</v>
+        <v>0.3777671423027514</v>
       </c>
       <c r="C68">
-        <v>-1484.867339388024</v>
+        <v>-961.2918899807628</v>
       </c>
       <c r="D68">
-        <v>16429.07266061198</v>
+        <v>16952.64811001924</v>
       </c>
       <c r="E68">
         <v>9510.640000000001</v>
@@ -6851,37 +6851,37 @@
         <v>1991.289795918367</v>
       </c>
       <c r="M68">
-        <v>6287.895839186339</v>
+        <v>6006.052739186339</v>
       </c>
       <c r="N68">
-        <v>-4296.606043267971</v>
+        <v>-4014.762943267971</v>
       </c>
       <c r="O68">
-        <v>-1503.81211514379</v>
+        <v>-1405.16703014379</v>
       </c>
       <c r="P68">
-        <v>-2792.793928124182</v>
+        <v>-2609.595913124182</v>
       </c>
       <c r="Q68">
-        <v>-824.5939281241813</v>
+        <v>-641.3959131241813</v>
       </c>
       <c r="R68">
         <v>1.941176470588236</v>
       </c>
       <c r="S68">
-        <v>0.5643823149424132</v>
+        <v>0.5625883534414235</v>
       </c>
       <c r="T68">
-        <v>2.548613172846861</v>
+        <v>2.539173521419795</v>
       </c>
       <c r="U68">
-        <v>0.3346487374989669</v>
+        <v>0.3196487374989669</v>
       </c>
       <c r="V68">
-        <v>0.1108401675848395</v>
+        <v>0.116041509929506</v>
       </c>
       <c r="W68">
-        <v>0.2975562153525265</v>
+        <v>0.2825562153525265</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
@@ -6889,7 +6889,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>0.3166861930995414</v>
+        <v>0.3315471712271602</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6900,13 +6900,13 @@
         <v>0.67</v>
       </c>
       <c r="B69">
-        <v>0.3911655765880777</v>
+        <v>0.3805056296777412</v>
       </c>
       <c r="C69">
-        <v>-1906.96295297518</v>
+        <v>-1384.684704351199</v>
       </c>
       <c r="D69">
-        <v>16291.66704702482</v>
+        <v>16813.9452956488</v>
       </c>
       <c r="E69">
         <v>9795.33</v>
@@ -6933,37 +6933,37 @@
         <v>1991.289795918367</v>
       </c>
       <c r="M69">
-        <v>6383.166988264919</v>
+        <v>6097.053538264919</v>
       </c>
       <c r="N69">
-        <v>-4391.877192346552</v>
+        <v>-4105.763742346551</v>
       </c>
       <c r="O69">
-        <v>-1537.157017321293</v>
+        <v>-1437.017309821293</v>
       </c>
       <c r="P69">
-        <v>-2854.720175025259</v>
+        <v>-2668.746432525259</v>
       </c>
       <c r="Q69">
-        <v>-886.5201750252586</v>
+        <v>-700.5464325252583</v>
       </c>
       <c r="R69">
         <v>2.030303030303031</v>
       </c>
       <c r="S69">
-        <v>0.5800969305467288</v>
+        <v>0.5782486065760124</v>
       </c>
       <c r="T69">
-        <v>2.625843875054342</v>
+        <v>2.616118173584032</v>
       </c>
       <c r="U69">
-        <v>0.3346487374989669</v>
+        <v>0.3196487374989669</v>
       </c>
       <c r="V69">
-        <v>0.1091858367253642</v>
+        <v>0.1143095470947373</v>
       </c>
       <c r="W69">
-        <v>0.2981098350860554</v>
+        <v>0.2831098350860554</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
@@ -6971,7 +6971,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>0.3119595335010408</v>
+        <v>0.3265987059849638</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6982,13 +6982,13 @@
         <v>0.68</v>
       </c>
       <c r="B70">
-        <v>0.3940540639630673</v>
+        <v>0.3832441170527308</v>
       </c>
       <c r="C70">
-        <v>-2326.779228451629</v>
+        <v>-1805.826266518176</v>
       </c>
       <c r="D70">
-        <v>16156.54077154837</v>
+        <v>16677.49373348183</v>
       </c>
       <c r="E70">
         <v>10080.02</v>
@@ -7015,37 +7015,37 @@
         <v>1991.289795918367</v>
       </c>
       <c r="M70">
-        <v>6478.438137343501</v>
+        <v>6188.0543373435</v>
       </c>
       <c r="N70">
-        <v>-4487.148341425133</v>
+        <v>-4196.764541425133</v>
       </c>
       <c r="O70">
-        <v>-1570.501919498796</v>
+        <v>-1468.867589498796</v>
       </c>
       <c r="P70">
-        <v>-2916.646421926337</v>
+        <v>-2727.896951926336</v>
       </c>
       <c r="Q70">
-        <v>-948.4464219263368</v>
+        <v>-759.6969519263362</v>
       </c>
       <c r="R70">
         <v>2.125</v>
       </c>
       <c r="S70">
-        <v>0.5967937096263142</v>
+        <v>0.5948876255315126</v>
       </c>
       <c r="T70">
-        <v>2.707901496149791</v>
+        <v>2.697871866508532</v>
       </c>
       <c r="U70">
-        <v>0.3346487374989669</v>
+        <v>0.3196487374989669</v>
       </c>
       <c r="V70">
-        <v>0.1075801626558736</v>
+        <v>0.1126285243433441</v>
       </c>
       <c r="W70">
-        <v>0.2986471718862453</v>
+        <v>0.2836471718862453</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
@@ -7053,7 +7053,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>0.307371893302496</v>
+        <v>0.321795783838126</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7064,13 +7064,13 @@
         <v>0.6900000000000001</v>
       </c>
       <c r="B71">
-        <v>0.396942551338057</v>
+        <v>0.3859826044277205</v>
       </c>
       <c r="C71">
-        <v>-2744.372415104146</v>
+        <v>-2224.770944568045</v>
       </c>
       <c r="D71">
-        <v>16023.63758489585</v>
+        <v>16543.23905543196</v>
       </c>
       <c r="E71">
         <v>10364.71</v>
@@ -7097,37 +7097,37 @@
         <v>1991.289795918367</v>
       </c>
       <c r="M71">
-        <v>6573.709286422081</v>
+        <v>6279.055136422081</v>
       </c>
       <c r="N71">
-        <v>-4582.419490503714</v>
+        <v>-4287.765340503714</v>
       </c>
       <c r="O71">
-        <v>-1603.8468216763</v>
+        <v>-1500.7178691763</v>
       </c>
       <c r="P71">
-        <v>-2978.572668827414</v>
+        <v>-2787.047471327414</v>
       </c>
       <c r="Q71">
-        <v>-1010.372668827414</v>
+        <v>-818.8474713274136</v>
       </c>
       <c r="R71">
         <v>2.225806451612904</v>
       </c>
       <c r="S71">
-        <v>0.6145677002594211</v>
+        <v>0.6126001295809164</v>
       </c>
       <c r="T71">
-        <v>2.795253157315913</v>
+        <v>2.784899991234615</v>
       </c>
       <c r="U71">
-        <v>0.3346487374989669</v>
+        <v>0.3196487374989669</v>
       </c>
       <c r="V71">
-        <v>0.1060210298637595</v>
+        <v>0.1109962268890928</v>
       </c>
       <c r="W71">
-        <v>0.2991689337067195</v>
+        <v>0.2841689337067195</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
@@ -7135,7 +7135,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>0.30291722818217</v>
+        <v>0.3171320768259793</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7146,13 +7146,13 @@
         <v>0.7000000000000001</v>
       </c>
       <c r="B72">
-        <v>0.3998310387130466</v>
+        <v>0.3887210918027101</v>
       </c>
       <c r="C72">
-        <v>-3159.796926500752</v>
+        <v>-2641.571369904028</v>
       </c>
       <c r="D72">
-        <v>15892.90307349925</v>
+        <v>16411.12863009598</v>
       </c>
       <c r="E72">
         <v>10649.4</v>
@@ -7179,37 +7179,37 @@
         <v>1991.289795918367</v>
       </c>
       <c r="M72">
-        <v>6668.980435500663</v>
+        <v>6370.055935500663</v>
       </c>
       <c r="N72">
-        <v>-4677.690639582295</v>
+        <v>-4378.766139582295</v>
       </c>
       <c r="O72">
-        <v>-1637.191723853803</v>
+        <v>-1532.568148853803</v>
       </c>
       <c r="P72">
-        <v>-3040.498915728492</v>
+        <v>-2846.197990728492</v>
       </c>
       <c r="Q72">
-        <v>-1072.298915728491</v>
+        <v>-877.9979907284919</v>
       </c>
       <c r="R72">
         <v>2.333333333333334</v>
       </c>
       <c r="S72">
-        <v>0.6335266236014018</v>
+        <v>0.6314934672336134</v>
       </c>
       <c r="T72">
-        <v>2.888428262559777</v>
+        <v>2.877729990942434</v>
       </c>
       <c r="U72">
-        <v>0.3346487374989669</v>
+        <v>0.3196487374989669</v>
       </c>
       <c r="V72">
-        <v>0.1045064437228486</v>
+        <v>0.1094105665049628</v>
       </c>
       <c r="W72">
-        <v>0.2996757880466088</v>
+        <v>0.2846757880466088</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
@@ -7217,7 +7217,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>0.298589839208139</v>
+        <v>0.3126016185856082</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7228,13 +7228,13 @@
         <v>0.71</v>
       </c>
       <c r="B73">
-        <v>0.4027195260880363</v>
+        <v>0.3914595791776998</v>
       </c>
       <c r="C73">
-        <v>-3573.105414771442</v>
+        <v>-3056.278506040569</v>
       </c>
       <c r="D73">
-        <v>15764.28458522856</v>
+        <v>16281.11149395943</v>
       </c>
       <c r="E73">
         <v>10934.09</v>
@@ -7261,37 +7261,37 @@
         <v>1991.289795918367</v>
       </c>
       <c r="M73">
-        <v>6764.251584579242</v>
+        <v>6461.056734579242</v>
       </c>
       <c r="N73">
-        <v>-4772.961788660875</v>
+        <v>-4469.766938660875</v>
       </c>
       <c r="O73">
-        <v>-1670.536626031306</v>
+        <v>-1564.418428531306</v>
       </c>
       <c r="P73">
-        <v>-3102.425162629569</v>
+        <v>-2905.348510129569</v>
       </c>
       <c r="Q73">
-        <v>-1134.225162629569</v>
+        <v>-937.1485101295689</v>
       </c>
       <c r="R73">
         <v>2.448275862068965</v>
       </c>
       <c r="S73">
-        <v>0.6537930588980017</v>
+        <v>0.6516897936899448</v>
       </c>
       <c r="T73">
-        <v>2.988029237130803</v>
+        <v>2.976962059595621</v>
       </c>
       <c r="U73">
-        <v>0.3346487374989669</v>
+        <v>0.3196487374989669</v>
       </c>
       <c r="V73">
-        <v>0.1030345219802733</v>
+        <v>0.1078695726105268</v>
       </c>
       <c r="W73">
-        <v>0.3001683647994589</v>
+        <v>0.2851683647994588</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
@@ -7299,7 +7299,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>0.2943843485150667</v>
+        <v>0.3081987788872194</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7310,13 +7310,13 @@
         <v>0.72</v>
       </c>
       <c r="B74">
-        <v>0.405608013463026</v>
+        <v>0.3941980665526895</v>
       </c>
       <c r="C74">
-        <v>-3984.348841311115</v>
+        <v>-3468.941714153269</v>
       </c>
       <c r="D74">
-        <v>15637.73115868889</v>
+        <v>16153.13828584673</v>
       </c>
       <c r="E74">
         <v>11218.78</v>
@@ -7343,37 +7343,37 @@
         <v>1991.289795918367</v>
       </c>
       <c r="M74">
-        <v>6859.522733657824</v>
+        <v>6552.057533657824</v>
       </c>
       <c r="N74">
-        <v>-4868.232937739456</v>
+        <v>-4560.767737739457</v>
       </c>
       <c r="O74">
-        <v>-1703.88152820881</v>
+        <v>-1596.26870820881</v>
       </c>
       <c r="P74">
-        <v>-3164.351409530646</v>
+        <v>-2964.499029530647</v>
       </c>
       <c r="Q74">
-        <v>-1196.151409530646</v>
+        <v>-996.2990295306467</v>
       </c>
       <c r="R74">
         <v>2.571428571428571</v>
       </c>
       <c r="S74">
-        <v>0.6755070967157875</v>
+        <v>0.6733287148931572</v>
       </c>
       <c r="T74">
-        <v>3.094744567028331</v>
+        <v>3.083282133152608</v>
       </c>
       <c r="U74">
-        <v>0.3346487374989669</v>
+        <v>0.3196487374989669</v>
       </c>
       <c r="V74">
-        <v>0.1016034869527695</v>
+        <v>0.1063713841020472</v>
       </c>
       <c r="W74">
-        <v>0.3006472588647298</v>
+        <v>0.2856472588647298</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
@@ -7381,7 +7381,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>0.2902956770079129</v>
+        <v>0.3039182402915634</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7392,13 +7392,13 @@
         <v>0.73</v>
       </c>
       <c r="B75">
-        <v>0.4084965008380156</v>
+        <v>0.3969365539276791</v>
       </c>
       <c r="C75">
-        <v>-4393.576544103915</v>
+        <v>-3879.608815561409</v>
       </c>
       <c r="D75">
-        <v>15513.19345589609</v>
+        <v>16027.16118443859</v>
       </c>
       <c r="E75">
         <v>11503.47</v>
@@ -7425,37 +7425,37 @@
         <v>1991.289795918367</v>
       </c>
       <c r="M75">
-        <v>6954.793882736404</v>
+        <v>6643.058332736404</v>
       </c>
       <c r="N75">
-        <v>-4963.504086818037</v>
+        <v>-4651.768536818036</v>
       </c>
       <c r="O75">
-        <v>-1737.226430386313</v>
+        <v>-1628.118987886313</v>
       </c>
       <c r="P75">
-        <v>-3226.277656431724</v>
+        <v>-3023.649548931724</v>
       </c>
       <c r="Q75">
-        <v>-1258.077656431723</v>
+        <v>-1055.449548931724</v>
       </c>
       <c r="R75">
         <v>2.703703703703703</v>
       </c>
       <c r="S75">
-        <v>0.6988295817793351</v>
+        <v>0.6965705191484592</v>
       </c>
       <c r="T75">
-        <v>3.209364736177529</v>
+        <v>3.197477767713815</v>
       </c>
       <c r="U75">
-        <v>0.3346487374989669</v>
+        <v>0.3196487374989669</v>
       </c>
       <c r="V75">
-        <v>0.1002116583643754</v>
+        <v>0.104914241854074</v>
       </c>
       <c r="W75">
-        <v>0.3011130325446509</v>
+        <v>0.2861130325446509</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
@@ -7463,7 +7463,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>0.2863190238982155</v>
+        <v>0.2997549767259257</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7474,13 +7474,13 @@
         <v>0.74</v>
       </c>
       <c r="B76">
-        <v>0.4113849882130053</v>
+        <v>0.3996750413026688</v>
       </c>
       <c r="C76">
-        <v>-4800.83630185617</v>
+        <v>-4288.326151309488</v>
       </c>
       <c r="D76">
-        <v>15390.62369814383</v>
+        <v>15903.13384869051</v>
       </c>
       <c r="E76">
         <v>11788.16</v>
@@ -7507,37 +7507,37 @@
         <v>1991.289795918367</v>
       </c>
       <c r="M76">
-        <v>7050.065031814986</v>
+        <v>6734.059131814985</v>
       </c>
       <c r="N76">
-        <v>-5058.775235896618</v>
+        <v>-4742.769335896618</v>
       </c>
       <c r="O76">
-        <v>-1770.571332563816</v>
+        <v>-1659.969267563816</v>
       </c>
       <c r="P76">
-        <v>-3288.203903332802</v>
+        <v>-3082.800068332802</v>
       </c>
       <c r="Q76">
-        <v>-1320.003903332802</v>
+        <v>-1114.600068332802</v>
       </c>
       <c r="R76">
         <v>2.846153846153846</v>
       </c>
       <c r="S76">
-        <v>0.7239461041554633</v>
+        <v>0.7216001545003231</v>
       </c>
       <c r="T76">
-        <v>3.332801841415126</v>
+        <v>3.320457681856654</v>
       </c>
       <c r="U76">
-        <v>0.3346487374989669</v>
+        <v>0.3196487374989669</v>
       </c>
       <c r="V76">
-        <v>0.09885744676485682</v>
+        <v>0.1034964818290189</v>
       </c>
       <c r="W76">
-        <v>0.3015662177467362</v>
+        <v>0.2865662177467362</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
@@ -7545,7 +7545,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>0.2824498478995909</v>
+        <v>0.2957042337971969</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7556,13 +7556,13 @@
         <v>0.75</v>
       </c>
       <c r="B77">
-        <v>0.414273475587995</v>
+        <v>0.4024135286776585</v>
       </c>
       <c r="C77">
-        <v>-5206.174395112719</v>
+        <v>-4695.138639003369</v>
       </c>
       <c r="D77">
-        <v>15269.97560488728</v>
+        <v>15781.01136099663</v>
       </c>
       <c r="E77">
         <v>12072.85</v>
@@ -7589,37 +7589,37 @@
         <v>1991.289795918367</v>
       </c>
       <c r="M77">
-        <v>7145.336180893566</v>
+        <v>6825.059930893566</v>
       </c>
       <c r="N77">
-        <v>-5154.046384975199</v>
+        <v>-4833.770134975199</v>
       </c>
       <c r="O77">
-        <v>-1803.916234741319</v>
+        <v>-1691.819547241319</v>
       </c>
       <c r="P77">
-        <v>-3350.130150233879</v>
+        <v>-3141.950587733879</v>
       </c>
       <c r="Q77">
-        <v>-1381.930150233879</v>
+        <v>-1173.750587733879</v>
       </c>
       <c r="R77">
         <v>3</v>
       </c>
       <c r="S77">
-        <v>0.751071948321682</v>
+        <v>0.7486321606803361</v>
       </c>
       <c r="T77">
-        <v>3.466113915071731</v>
+        <v>3.453275989130921</v>
       </c>
       <c r="U77">
-        <v>0.3346487374989669</v>
+        <v>0.3196487374989669</v>
       </c>
       <c r="V77">
-        <v>0.09753934747465874</v>
+        <v>0.1021165287379653</v>
       </c>
       <c r="W77">
-        <v>0.3020073180100993</v>
+        <v>0.2870073180100993</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
@@ -7627,7 +7627,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>0.2786838499275964</v>
+        <v>0.291761510679901</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7638,13 +7638,13 @@
         <v>0.76</v>
       </c>
       <c r="B78">
-        <v>0.4171619629629846</v>
+        <v>0.4051520160526482</v>
       </c>
       <c r="C78">
-        <v>-5609.635664521138</v>
+        <v>-5100.08982704781</v>
       </c>
       <c r="D78">
-        <v>15151.20433547886</v>
+        <v>15660.75017295219</v>
       </c>
       <c r="E78">
         <v>12357.54</v>
@@ -7671,37 +7671,37 @@
         <v>1991.289795918367</v>
       </c>
       <c r="M78">
-        <v>7240.607329972147</v>
+        <v>6916.060729972147</v>
       </c>
       <c r="N78">
-        <v>-5249.317534053779</v>
+        <v>-4924.770934053779</v>
       </c>
       <c r="O78">
-        <v>-1837.261136918823</v>
+        <v>-1723.669826918823</v>
       </c>
       <c r="P78">
-        <v>-3412.056397134957</v>
+        <v>-3201.101107134957</v>
       </c>
       <c r="Q78">
-        <v>-1443.856397134956</v>
+        <v>-1232.901107134956</v>
       </c>
       <c r="R78">
         <v>3.166666666666667</v>
       </c>
       <c r="S78">
-        <v>0.7804582795017521</v>
+        <v>0.7779168340420168</v>
       </c>
       <c r="T78">
-        <v>3.61053532819972</v>
+        <v>3.597162488678043</v>
       </c>
       <c r="U78">
-        <v>0.3346487374989669</v>
+        <v>0.3196487374989669</v>
       </c>
       <c r="V78">
-        <v>0.09625593500788691</v>
+        <v>0.1007728902019395</v>
       </c>
       <c r="W78">
-        <v>0.3024368103717949</v>
+        <v>0.2874368103717949</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
@@ -7709,7 +7709,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>0.2750169571653912</v>
+        <v>0.2879225434341128</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7720,13 +7720,13 @@
         <v>0.77</v>
       </c>
       <c r="B79">
-        <v>0.4200504503379743</v>
+        <v>0.4078905034276379</v>
       </c>
       <c r="C79">
-        <v>-6011.263566397809</v>
+        <v>-5503.221946422727</v>
       </c>
       <c r="D79">
-        <v>15034.26643360219</v>
+        <v>15542.30805357728</v>
       </c>
       <c r="E79">
         <v>12642.23</v>
@@ -7753,37 +7753,37 @@
         <v>1991.289795918367</v>
       </c>
       <c r="M79">
-        <v>7335.878479050729</v>
+        <v>7007.061529050728</v>
       </c>
       <c r="N79">
-        <v>-5344.588683132361</v>
+        <v>-5015.771733132361</v>
       </c>
       <c r="O79">
-        <v>-1870.606039096326</v>
+        <v>-1755.520106596326</v>
       </c>
       <c r="P79">
-        <v>-3473.982644036035</v>
+        <v>-3260.251626536035</v>
       </c>
       <c r="Q79">
-        <v>-1505.782644036035</v>
+        <v>-1292.051626536034</v>
       </c>
       <c r="R79">
         <v>3.347826086956522</v>
       </c>
       <c r="S79">
-        <v>0.8123999438279152</v>
+        <v>0.8097480007394959</v>
       </c>
       <c r="T79">
-        <v>3.767515125077969</v>
+        <v>3.753560857751002</v>
       </c>
       <c r="U79">
-        <v>0.3346487374989669</v>
+        <v>0.3196487374989669</v>
       </c>
       <c r="V79">
-        <v>0.09500585792986239</v>
+        <v>0.09946415136814805</v>
       </c>
       <c r="W79">
-        <v>0.3028551470877323</v>
+        <v>0.2878551470877322</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
@@ -7791,7 +7791,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>0.2714453083710354</v>
+        <v>0.2841832896232801</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7802,13 +7802,13 @@
         <v>0.78</v>
       </c>
       <c r="B80">
-        <v>0.422938937712964</v>
+        <v>0.4106289908026275</v>
       </c>
       <c r="C80">
-        <v>-6411.100225740474</v>
+        <v>-5904.575960127562</v>
       </c>
       <c r="D80">
-        <v>14919.11977425953</v>
+        <v>15425.64403987244</v>
       </c>
       <c r="E80">
         <v>12926.92</v>
@@ -7835,37 +7835,37 @@
         <v>1991.289795918367</v>
       </c>
       <c r="M80">
-        <v>7431.149628129309</v>
+        <v>7098.062328129308</v>
       </c>
       <c r="N80">
-        <v>-5439.859832210942</v>
+        <v>-5106.772532210941</v>
       </c>
       <c r="O80">
-        <v>-1903.95094127383</v>
+        <v>-1787.370386273829</v>
       </c>
       <c r="P80">
-        <v>-3535.908890937112</v>
+        <v>-3319.402145937112</v>
       </c>
       <c r="Q80">
-        <v>-1567.708890937112</v>
+        <v>-1351.202145937111</v>
       </c>
       <c r="R80">
         <v>3.545454545454546</v>
       </c>
       <c r="S80">
-        <v>0.8472453958200933</v>
+        <v>0.8444729098640184</v>
       </c>
       <c r="T80">
-        <v>3.938765812581513</v>
+        <v>3.924177260376047</v>
       </c>
       <c r="U80">
-        <v>0.3346487374989669</v>
+        <v>0.3196487374989669</v>
       </c>
       <c r="V80">
-        <v>0.09378783411024878</v>
+        <v>0.0981889699403513</v>
       </c>
       <c r="W80">
-        <v>0.3032627572212096</v>
+        <v>0.2882627572212096</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
@@ -7873,7 +7873,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>0.2679652403149965</v>
+        <v>0.2805399141152894</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7884,13 +7884,13 @@
         <v>0.79</v>
       </c>
       <c r="B81">
-        <v>0.4258274250879537</v>
+        <v>0.4133674781776172</v>
       </c>
       <c r="C81">
-        <v>-6809.186486823302</v>
+        <v>-6304.191610415544</v>
       </c>
       <c r="D81">
-        <v>14805.7235131767</v>
+        <v>15310.71838958446</v>
       </c>
       <c r="E81">
         <v>13211.61</v>
@@ -7917,37 +7917,37 @@
         <v>1991.289795918367</v>
       </c>
       <c r="M81">
-        <v>7526.420777207891</v>
+        <v>7189.06312720789</v>
       </c>
       <c r="N81">
-        <v>-5535.130981289523</v>
+        <v>-5197.773331289523</v>
       </c>
       <c r="O81">
-        <v>-1937.295843451333</v>
+        <v>-1819.220665951333</v>
       </c>
       <c r="P81">
-        <v>-3597.83513783819</v>
+        <v>-3378.55266533819</v>
       </c>
       <c r="Q81">
-        <v>-1629.63513783819</v>
+        <v>-1410.35266533819</v>
       </c>
       <c r="R81">
         <v>3.761904761904763</v>
       </c>
       <c r="S81">
-        <v>0.885409462287717</v>
+        <v>0.8825049531908766</v>
       </c>
       <c r="T81">
-        <v>4.12632608937111</v>
+        <v>4.111042844203479</v>
       </c>
       <c r="U81">
-        <v>0.3346487374989669</v>
+        <v>0.3196487374989669</v>
       </c>
       <c r="V81">
-        <v>0.09260064633670131</v>
+        <v>0.09694607158667594</v>
       </c>
       <c r="W81">
-        <v>0.3036600481108015</v>
+        <v>0.2886600481108015</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
@@ -7955,7 +7955,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>0.2645732752477181</v>
+        <v>0.2769887759619313</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7966,13 +7966,13 @@
         <v>0.8</v>
       </c>
       <c r="B82">
-        <v>0.4287159124629434</v>
+        <v>0.4161059655526068</v>
       </c>
       <c r="C82">
-        <v>-7205.561961501864</v>
+        <v>-6702.107463931916</v>
       </c>
       <c r="D82">
-        <v>14694.03803849814</v>
+        <v>15197.49253606808</v>
       </c>
       <c r="E82">
         <v>13496.3</v>
@@ -7999,37 +7999,37 @@
         <v>1991.289795918367</v>
       </c>
       <c r="M82">
-        <v>7621.691926286471</v>
+        <v>7280.063926286471</v>
       </c>
       <c r="N82">
-        <v>-5630.402130368104</v>
+        <v>-5288.774130368103</v>
       </c>
       <c r="O82">
-        <v>-1970.640745628836</v>
+        <v>-1851.070945628836</v>
       </c>
       <c r="P82">
-        <v>-3659.761384739268</v>
+        <v>-3437.703184739267</v>
       </c>
       <c r="Q82">
-        <v>-1691.561384739267</v>
+        <v>-1469.503184739267</v>
       </c>
       <c r="R82">
         <v>4.000000000000001</v>
       </c>
       <c r="S82">
-        <v>0.9273899354021028</v>
+        <v>0.9243402008504205</v>
       </c>
       <c r="T82">
-        <v>4.332642393839666</v>
+        <v>4.316594986413652</v>
       </c>
       <c r="U82">
-        <v>0.3346487374989669</v>
+        <v>0.3196487374989669</v>
       </c>
       <c r="V82">
-        <v>0.09144313825749256</v>
+        <v>0.0957342456918425</v>
       </c>
       <c r="W82">
-        <v>0.3040474067281536</v>
+        <v>0.2890474067281535</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
@@ -8037,7 +8037,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>0.2612661093071216</v>
+        <v>0.2735264162624071</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8048,13 +8048,13 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="B83">
-        <v>0.431604399837933</v>
+        <v>0.4188444529275965</v>
       </c>
       <c r="C83">
-        <v>-7600.265075348285</v>
+        <v>-7098.360954864193</v>
       </c>
       <c r="D83">
-        <v>14584.02492465172</v>
+        <v>15085.92904513581</v>
       </c>
       <c r="E83">
         <v>13780.99</v>
@@ -8081,37 +8081,37 @@
         <v>1991.289795918367</v>
       </c>
       <c r="M83">
-        <v>7716.963075365053</v>
+        <v>7371.064725365052</v>
       </c>
       <c r="N83">
-        <v>-5725.673279446685</v>
+        <v>-5379.774929446685</v>
       </c>
       <c r="O83">
-        <v>-2003.98564780634</v>
+        <v>-1882.921225306339</v>
       </c>
       <c r="P83">
-        <v>-3721.687631640345</v>
+        <v>-3496.853704140345</v>
       </c>
       <c r="Q83">
-        <v>-1753.487631640345</v>
+        <v>-1528.653704140345</v>
       </c>
       <c r="R83">
         <v>4.263157894736843</v>
       </c>
       <c r="S83">
-        <v>0.9737894056864238</v>
+        <v>0.9705791587899162</v>
       </c>
       <c r="T83">
-        <v>4.560676204041752</v>
+        <v>4.543784196224897</v>
       </c>
       <c r="U83">
-        <v>0.3346487374989669</v>
+        <v>0.3196487374989669</v>
       </c>
       <c r="V83">
-        <v>0.09031421062468399</v>
+        <v>0.09455234142404197</v>
       </c>
       <c r="W83">
-        <v>0.3044252009352006</v>
+        <v>0.2894252009352006</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
@@ -8119,7 +8119,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>0.2580406017848115</v>
+        <v>0.2701495469258343</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8130,13 +8130,13 @@
         <v>0.8200000000000001</v>
       </c>
       <c r="B84">
-        <v>0.4344928872129227</v>
+        <v>0.4215829403025862</v>
       </c>
       <c r="C84">
-        <v>-7993.333111729266</v>
+        <v>-7492.988426205568</v>
       </c>
       <c r="D84">
-        <v>14475.64688827074</v>
+        <v>14975.99157379443</v>
       </c>
       <c r="E84">
         <v>14065.68</v>
@@ -8163,37 +8163,37 @@
         <v>1991.289795918367</v>
       </c>
       <c r="M84">
-        <v>7812.234224443633</v>
+        <v>7462.065524443633</v>
       </c>
       <c r="N84">
-        <v>-5820.944428525266</v>
+        <v>-5470.775728525266</v>
       </c>
       <c r="O84">
-        <v>-2037.330549983843</v>
+        <v>-1914.771504983843</v>
       </c>
       <c r="P84">
-        <v>-3783.613878541423</v>
+        <v>-3556.004223541423</v>
       </c>
       <c r="Q84">
-        <v>-1815.413878541422</v>
+        <v>-1587.804223541423</v>
       </c>
       <c r="R84">
         <v>4.555555555555557</v>
       </c>
       <c r="S84">
-        <v>1.025344372669003</v>
+        <v>1.021955778722689</v>
       </c>
       <c r="T84">
-        <v>4.814047104266295</v>
+        <v>4.796216651570725</v>
       </c>
       <c r="U84">
-        <v>0.3346487374989669</v>
+        <v>0.3196487374989669</v>
       </c>
       <c r="V84">
-        <v>0.08921281781218784</v>
+        <v>0.09339926408960243</v>
       </c>
       <c r="W84">
-        <v>0.3047937806493929</v>
+        <v>0.2897937806493929</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
@@ -8201,7 +8201,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>0.2548937651776796</v>
+        <v>0.2668550402560069</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8212,13 +8212,13 @@
         <v>0.8300000000000001</v>
       </c>
       <c r="B85">
-        <v>0.4373813745879124</v>
+        <v>0.424321427677576</v>
       </c>
       <c r="C85">
-        <v>-8384.802253933311</v>
+        <v>-7886.025169227267</v>
       </c>
       <c r="D85">
-        <v>14368.86774606669</v>
+        <v>14867.64483077273</v>
       </c>
       <c r="E85">
         <v>14350.37</v>
@@ -8245,37 +8245,37 @@
         <v>1991.289795918367</v>
       </c>
       <c r="M85">
-        <v>7907.505373522214</v>
+        <v>7553.066323522214</v>
       </c>
       <c r="N85">
-        <v>-5916.215577603846</v>
+        <v>-5561.776527603846</v>
       </c>
       <c r="O85">
-        <v>-2070.675452161346</v>
+        <v>-1946.621784661346</v>
       </c>
       <c r="P85">
-        <v>-3845.5401254425</v>
+        <v>-3615.1547429425</v>
       </c>
       <c r="Q85">
-        <v>-1877.3401254425</v>
+        <v>-1646.9547429425</v>
       </c>
       <c r="R85">
         <v>4.882352941176473</v>
       </c>
       <c r="S85">
-        <v>1.082964629884827</v>
+        <v>1.079376706882848</v>
       </c>
       <c r="T85">
-        <v>5.097226345693724</v>
+        <v>5.078347042839592</v>
       </c>
       <c r="U85">
-        <v>0.3346487374989669</v>
+        <v>0.3196487374989669</v>
       </c>
       <c r="V85">
-        <v>0.08813796458553499</v>
+        <v>0.09227397175117348</v>
       </c>
       <c r="W85">
-        <v>0.305153478924689</v>
+        <v>0.290153478924689</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -8283,7 +8283,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>0.2518227559586714</v>
+        <v>0.2636399192890672</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8294,13 +8294,13 @@
         <v>0.84</v>
       </c>
       <c r="B86">
-        <v>0.440269861962902</v>
+        <v>0.4270599150525656</v>
       </c>
       <c r="C86">
-        <v>-8774.707625447072</v>
+        <v>-8277.505461249668</v>
       </c>
       <c r="D86">
-        <v>14263.65237455293</v>
+        <v>14760.85453875033</v>
       </c>
       <c r="E86">
         <v>14635.06</v>
@@ -8327,37 +8327,37 @@
         <v>1991.289795918367</v>
       </c>
       <c r="M86">
-        <v>8002.776522600794</v>
+        <v>7644.067122600793</v>
       </c>
       <c r="N86">
-        <v>-6011.486726682427</v>
+        <v>-5652.777326682426</v>
       </c>
       <c r="O86">
-        <v>-2104.020354338849</v>
+        <v>-1978.472064338849</v>
       </c>
       <c r="P86">
-        <v>-3907.466372343577</v>
+        <v>-3674.305262343577</v>
       </c>
       <c r="Q86">
-        <v>-1939.266372343577</v>
+        <v>-1706.105262343577</v>
       </c>
       <c r="R86">
         <v>5.249999999999999</v>
       </c>
       <c r="S86">
-        <v>1.147787419252628</v>
+        <v>1.143975251063025</v>
       </c>
       <c r="T86">
-        <v>5.41580299229958</v>
+        <v>5.395743733017063</v>
       </c>
       <c r="U86">
-        <v>0.3346487374989669</v>
+        <v>0.3196487374989669</v>
       </c>
       <c r="V86">
-        <v>0.08708870310237386</v>
+        <v>0.09117547208746905</v>
       </c>
       <c r="W86">
-        <v>0.3055046129553352</v>
+        <v>0.2905046129553351</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -8365,7 +8365,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>0.2488248660067826</v>
+        <v>0.2605013488213401</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8376,13 +8376,13 @@
         <v>0.85</v>
       </c>
       <c r="B87">
-        <v>0.4431583493378917</v>
+        <v>0.4297984024275552</v>
       </c>
       <c r="C87">
-        <v>-9163.08332847505</v>
+        <v>-8667.46260179735</v>
       </c>
       <c r="D87">
-        <v>14159.96667152495</v>
+        <v>14655.58739820265</v>
       </c>
       <c r="E87">
         <v>14919.75</v>
@@ -8409,37 +8409,37 @@
         <v>1991.289795918367</v>
       </c>
       <c r="M87">
-        <v>8098.047671679375</v>
+        <v>7735.067921679374</v>
       </c>
       <c r="N87">
-        <v>-6106.757875761007</v>
+        <v>-5743.778125761007</v>
       </c>
       <c r="O87">
-        <v>-2137.365256516352</v>
+        <v>-2010.322344016352</v>
       </c>
       <c r="P87">
-        <v>-3969.392619244655</v>
+        <v>-3733.455781744655</v>
       </c>
       <c r="Q87">
-        <v>-2001.192619244654</v>
+        <v>-1765.255781744655</v>
       </c>
       <c r="R87">
         <v>5.666666666666666</v>
       </c>
       <c r="S87">
-        <v>1.221253247202803</v>
+        <v>1.217186934467227</v>
       </c>
       <c r="T87">
-        <v>5.776856525119552</v>
+        <v>5.755459981884868</v>
       </c>
       <c r="U87">
-        <v>0.3346487374989669</v>
+        <v>0.3196487374989669</v>
       </c>
       <c r="V87">
-        <v>0.08606413012469888</v>
+        <v>0.09010281947467531</v>
       </c>
       <c r="W87">
-        <v>0.3058474850087896</v>
+        <v>0.2908474850087896</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8447,7 +8447,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.2458975146419968</v>
+        <v>0.2574366270705009</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8458,13 +8458,13 @@
         <v>0.86</v>
       </c>
       <c r="B88">
-        <v>0.4460468367128814</v>
+        <v>0.4325368898025449</v>
       </c>
       <c r="C88">
-        <v>-9549.962480791368</v>
+        <v>-9055.928947217948</v>
       </c>
       <c r="D88">
-        <v>14057.77751920863</v>
+        <v>14551.81105278205</v>
       </c>
       <c r="E88">
         <v>15204.44</v>
@@ -8491,37 +8491,37 @@
         <v>1991.289795918367</v>
       </c>
       <c r="M88">
-        <v>8193.318820757957</v>
+        <v>7826.068720757956</v>
       </c>
       <c r="N88">
-        <v>-6202.02902483959</v>
+        <v>-5834.778924839588</v>
       </c>
       <c r="O88">
-        <v>-2170.710158693856</v>
+        <v>-2042.172623693856</v>
       </c>
       <c r="P88">
-        <v>-4031.318866145733</v>
+        <v>-3792.606301145733</v>
       </c>
       <c r="Q88">
-        <v>-2063.118866145733</v>
+        <v>-1824.406301145732</v>
       </c>
       <c r="R88">
         <v>6.142857142857142</v>
       </c>
       <c r="S88">
-        <v>1.305214193431575</v>
+        <v>1.300857429786314</v>
       </c>
       <c r="T88">
-        <v>6.189489134056663</v>
+        <v>6.166564266305215</v>
       </c>
       <c r="U88">
-        <v>0.3346487374989669</v>
+        <v>0.3196487374989669</v>
       </c>
       <c r="V88">
-        <v>0.08506338442557447</v>
+        <v>0.0890551122714814</v>
       </c>
       <c r="W88">
-        <v>0.3061823832935591</v>
+        <v>0.2911823832935591</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8529,7 +8529,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.2430382412159271</v>
+        <v>0.2544431779185183</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8540,13 +8540,13 @@
         <v>0.87</v>
       </c>
       <c r="B89">
-        <v>0.448935324087871</v>
+        <v>0.4352753771775345</v>
       </c>
       <c r="C89">
-        <v>-9935.377251007229</v>
+        <v>-9442.935943840594</v>
       </c>
       <c r="D89">
-        <v>13957.05274899277</v>
+        <v>14449.4940561594</v>
       </c>
       <c r="E89">
         <v>15489.13</v>
@@ -8573,37 +8573,37 @@
         <v>1991.289795918367</v>
       </c>
       <c r="M89">
-        <v>8288.589969836537</v>
+        <v>7917.069519836537</v>
       </c>
       <c r="N89">
-        <v>-6297.30017391817</v>
+        <v>-5925.779723918169</v>
       </c>
       <c r="O89">
-        <v>-2204.055060871359</v>
+        <v>-2074.022903371359</v>
       </c>
       <c r="P89">
-        <v>-4093.245113046811</v>
+        <v>-3851.75682054681</v>
       </c>
       <c r="Q89">
-        <v>-2125.04511304681</v>
+        <v>-1883.55682054681</v>
       </c>
       <c r="R89">
         <v>6.692307692307692</v>
       </c>
       <c r="S89">
-        <v>1.402092208310927</v>
+        <v>1.397400309000646</v>
       </c>
       <c r="T89">
-        <v>6.665603682830253</v>
+        <v>6.640915363713308</v>
       </c>
       <c r="U89">
-        <v>0.3346487374989669</v>
+        <v>0.3196487374989669</v>
       </c>
       <c r="V89">
-        <v>0.0840856443747058</v>
+        <v>0.08803149029134943</v>
       </c>
       <c r="W89">
-        <v>0.3065095827671845</v>
+        <v>0.2915095827671845</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8611,7 +8611,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.2402446982134452</v>
+        <v>0.2515185436895698</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8622,13 +8622,13 @@
         <v>0.88</v>
       </c>
       <c r="B90">
-        <v>0.4518238114628607</v>
+        <v>0.4380138645525242</v>
       </c>
       <c r="C90">
-        <v>-10319.35889233309</v>
+        <v>-9828.514159745269</v>
       </c>
       <c r="D90">
-        <v>13857.76110766691</v>
+        <v>14348.60584025473</v>
       </c>
       <c r="E90">
         <v>15773.82</v>
@@ -8655,37 +8655,37 @@
         <v>1991.289795918367</v>
       </c>
       <c r="M90">
-        <v>8383.861118915118</v>
+        <v>8008.070318915118</v>
       </c>
       <c r="N90">
-        <v>-6392.57132299675</v>
+        <v>-6016.780522996751</v>
       </c>
       <c r="O90">
-        <v>-2237.399963048862</v>
+        <v>-2105.873183048863</v>
       </c>
       <c r="P90">
-        <v>-4155.171359947888</v>
+        <v>-3910.907339947888</v>
       </c>
       <c r="Q90">
-        <v>-2186.971359947888</v>
+        <v>-1942.707339947888</v>
       </c>
       <c r="R90">
         <v>7.333333333333334</v>
       </c>
       <c r="S90">
-        <v>1.515116559003504</v>
+        <v>1.510033668084034</v>
       </c>
       <c r="T90">
-        <v>7.221070656399441</v>
+        <v>7.194324977356086</v>
       </c>
       <c r="U90">
-        <v>0.3346487374989669</v>
+        <v>0.3196487374989669</v>
       </c>
       <c r="V90">
-        <v>0.0831301256886296</v>
+        <v>0.08703113244712954</v>
       </c>
       <c r="W90">
-        <v>0.3068293458891366</v>
+        <v>0.2918293458891366</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8693,7 +8693,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.237514644824656</v>
+        <v>0.2486603784203701</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8704,13 +8704,13 @@
         <v>0.89</v>
       </c>
       <c r="B91">
-        <v>0.4547122988378504</v>
+        <v>0.4407523519275138</v>
       </c>
       <c r="C91">
-        <v>-10701.93777490982</v>
+        <v>-10212.69331521041</v>
       </c>
       <c r="D91">
-        <v>13759.87222509018</v>
+        <v>14249.11668478959</v>
       </c>
       <c r="E91">
         <v>16058.51</v>
@@ -8737,37 +8737,37 @@
         <v>1991.289795918367</v>
       </c>
       <c r="M91">
-        <v>8479.132267993698</v>
+        <v>8099.071117993699</v>
       </c>
       <c r="N91">
-        <v>-6487.842472075331</v>
+        <v>-6107.781322075331</v>
       </c>
       <c r="O91">
-        <v>-2270.744865226366</v>
+        <v>-2137.723462726366</v>
       </c>
       <c r="P91">
-        <v>-4217.097606848965</v>
+        <v>-3970.057859348965</v>
       </c>
       <c r="Q91">
-        <v>-2248.897606848965</v>
+        <v>-2001.857859348965</v>
       </c>
       <c r="R91">
         <v>8.090909090909092</v>
       </c>
       <c r="S91">
-        <v>1.648690791640187</v>
+        <v>1.643145819728037</v>
       </c>
       <c r="T91">
-        <v>7.877531625163027</v>
+        <v>7.848354520752093</v>
       </c>
       <c r="U91">
-        <v>0.3346487374989669</v>
+        <v>0.3196487374989669</v>
       </c>
       <c r="V91">
-        <v>0.08219607933257758</v>
+        <v>0.08605325455446518</v>
       </c>
       <c r="W91">
-        <v>0.3071419233229549</v>
+        <v>0.2921419233229549</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8775,7 +8775,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.2348459409502217</v>
+        <v>0.2458664415841862</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8786,13 +8786,13 @@
         <v>0.9</v>
       </c>
       <c r="B92">
-        <v>0.4576007862128401</v>
+        <v>0.4434908393025035</v>
       </c>
       <c r="C92">
-        <v>-11083.1434167792</v>
+        <v>-10595.50231190264</v>
       </c>
       <c r="D92">
-        <v>13663.35658322081</v>
+        <v>14150.99768809736</v>
       </c>
       <c r="E92">
         <v>16343.2</v>
@@ -8819,37 +8819,37 @@
         <v>1991.289795918367</v>
       </c>
       <c r="M92">
-        <v>8574.403417072281</v>
+        <v>8190.07191707228</v>
       </c>
       <c r="N92">
-        <v>-6583.113621153913</v>
+        <v>-6198.782121153913</v>
       </c>
       <c r="O92">
-        <v>-2304.08976740387</v>
+        <v>-2169.573742403869</v>
       </c>
       <c r="P92">
-        <v>-4279.023853750044</v>
+        <v>-4029.208378750044</v>
       </c>
       <c r="Q92">
-        <v>-2310.823853750043</v>
+        <v>-2061.008378750043</v>
       </c>
       <c r="R92">
         <v>9.000000000000002</v>
       </c>
       <c r="S92">
-        <v>1.808979870804206</v>
+        <v>1.802880401700841</v>
       </c>
       <c r="T92">
-        <v>8.665284787679331</v>
+        <v>8.633189972827305</v>
       </c>
       <c r="U92">
-        <v>0.3346487374989669</v>
+        <v>0.3196487374989669</v>
       </c>
       <c r="V92">
-        <v>0.0812827895622156</v>
+        <v>0.08509710728163777</v>
       </c>
       <c r="W92">
-        <v>0.3074475545915772</v>
+        <v>0.2924475545915772</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -8857,7 +8857,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.2322365416063303</v>
+        <v>0.2431345922332507</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8868,13 +8868,13 @@
         <v>0.91</v>
       </c>
       <c r="B93">
-        <v>0.4604892735878297</v>
+        <v>0.4462293266774932</v>
       </c>
       <c r="C93">
-        <v>-11463.00451356006</v>
+        <v>-10976.96926086865</v>
       </c>
       <c r="D93">
-        <v>13568.18548643994</v>
+        <v>14054.22073913135</v>
       </c>
       <c r="E93">
         <v>16627.89</v>
@@ -8901,37 +8901,37 @@
         <v>1991.289795918367</v>
       </c>
       <c r="M93">
-        <v>8669.674566150861</v>
+        <v>8281.07271615086</v>
       </c>
       <c r="N93">
-        <v>-6678.384770232494</v>
+        <v>-6289.782920232493</v>
       </c>
       <c r="O93">
-        <v>-2337.434669581373</v>
+        <v>-2201.424022081372</v>
       </c>
       <c r="P93">
-        <v>-4340.950100651121</v>
+        <v>-4088.358898151121</v>
       </c>
       <c r="Q93">
-        <v>-2372.750100651121</v>
+        <v>-2120.15889815112</v>
       </c>
       <c r="R93">
         <v>10.11111111111111</v>
       </c>
       <c r="S93">
-        <v>2.004888745338006</v>
+        <v>1.998111557445379</v>
       </c>
       <c r="T93">
-        <v>9.628094208532589</v>
+        <v>9.592433303141449</v>
       </c>
       <c r="U93">
-        <v>0.3346487374989669</v>
+        <v>0.3196487374989669</v>
       </c>
       <c r="V93">
-        <v>0.08038957209449896</v>
+        <v>0.08416197423458682</v>
       </c>
       <c r="W93">
-        <v>0.3077464686894607</v>
+        <v>0.2927464686894606</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -8939,7 +8939,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.2296844916985684</v>
+        <v>0.2404627835273909</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8950,13 +8950,13 @@
         <v>0.92</v>
       </c>
       <c r="B94">
-        <v>0.4633777609628194</v>
+        <v>0.4489678140524829</v>
       </c>
       <c r="C94">
-        <v>-11841.54896689286</v>
+        <v>-11357.12150938638</v>
       </c>
       <c r="D94">
-        <v>13474.33103310714</v>
+        <v>13958.75849061362</v>
       </c>
       <c r="E94">
         <v>16912.58</v>
@@ -8983,37 +8983,37 @@
         <v>1991.289795918367</v>
       </c>
       <c r="M94">
-        <v>8764.945715229442</v>
+        <v>8372.073515229442</v>
       </c>
       <c r="N94">
-        <v>-6773.655919311074</v>
+        <v>-6380.783719311074</v>
       </c>
       <c r="O94">
-        <v>-2370.779571758876</v>
+        <v>-2233.274301758876</v>
       </c>
       <c r="P94">
-        <v>-4402.876347552198</v>
+        <v>-4147.509417552199</v>
       </c>
       <c r="Q94">
-        <v>-2434.676347552198</v>
+        <v>-2179.309417552199</v>
       </c>
       <c r="R94">
         <v>11.50000000000001</v>
       </c>
       <c r="S94">
-        <v>2.249774838505258</v>
+        <v>2.242150502126051</v>
       </c>
       <c r="T94">
-        <v>10.83160598459917</v>
+        <v>10.79148746603413</v>
       </c>
       <c r="U94">
-        <v>0.3346487374989669</v>
+        <v>0.3196487374989669</v>
       </c>
       <c r="V94">
-        <v>0.07951577239781962</v>
+        <v>0.08324717016681955</v>
       </c>
       <c r="W94">
-        <v>0.3080388846547814</v>
+        <v>0.2930388846547813</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9021,7 +9021,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.2271879211366274</v>
+        <v>0.2378490576194845</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9032,13 +9032,13 @@
         <v>0.93</v>
       </c>
       <c r="B95">
-        <v>0.4662662483378091</v>
+        <v>0.4517063014274726</v>
       </c>
       <c r="C95">
-        <v>-12218.80391171167</v>
+        <v>-11735.98566672921</v>
       </c>
       <c r="D95">
-        <v>13381.76608828833</v>
+        <v>13864.58433327079</v>
       </c>
       <c r="E95">
         <v>17197.27</v>
@@ -9065,37 +9065,37 @@
         <v>1991.289795918367</v>
       </c>
       <c r="M95">
-        <v>8860.216864308022</v>
+        <v>8463.074314308024</v>
       </c>
       <c r="N95">
-        <v>-6868.927068389655</v>
+        <v>-6471.784518389656</v>
       </c>
       <c r="O95">
-        <v>-2404.124473936379</v>
+        <v>-2265.12458143638</v>
       </c>
       <c r="P95">
-        <v>-4464.802594453276</v>
+        <v>-4206.659936953276</v>
       </c>
       <c r="Q95">
-        <v>-2496.602594453275</v>
+        <v>-2238.459936953276</v>
       </c>
       <c r="R95">
         <v>13.2857142857143</v>
       </c>
       <c r="S95">
-        <v>2.564628386863152</v>
+        <v>2.555914859572631</v>
       </c>
       <c r="T95">
-        <v>12.37897826811334</v>
+        <v>12.33312853261044</v>
       </c>
       <c r="U95">
-        <v>0.3346487374989669</v>
+        <v>0.3196487374989669</v>
       </c>
       <c r="V95">
-        <v>0.07866076409246672</v>
+        <v>0.08235203930481075</v>
       </c>
       <c r="W95">
-        <v>0.3083250121047189</v>
+        <v>0.2933250121047188</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9103,7 +9103,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.2247450402641906</v>
+        <v>0.2352915408708879</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9114,13 +9114,13 @@
         <v>0.9400000000000001</v>
       </c>
       <c r="B96">
-        <v>0.4691547357127987</v>
+        <v>0.4544447888024623</v>
       </c>
       <c r="C96">
-        <v>-12594.79574239984</v>
+        <v>-12113.58762889422</v>
       </c>
       <c r="D96">
-        <v>13290.46425760016</v>
+        <v>13771.67237110578</v>
       </c>
       <c r="E96">
         <v>17481.96</v>
@@ -9147,37 +9147,37 @@
         <v>1991.289795918367</v>
       </c>
       <c r="M96">
-        <v>8955.488013386603</v>
+        <v>8554.075113386603</v>
       </c>
       <c r="N96">
-        <v>-6964.198217468235</v>
+        <v>-6562.785317468236</v>
       </c>
       <c r="O96">
-        <v>-2437.469376113882</v>
+        <v>-2296.974861113883</v>
       </c>
       <c r="P96">
-        <v>-4526.728841354353</v>
+        <v>-4265.810456354353</v>
       </c>
       <c r="Q96">
-        <v>-2558.528841354353</v>
+        <v>-2297.610456354353</v>
       </c>
       <c r="R96">
         <v>15.66666666666668</v>
       </c>
       <c r="S96">
-        <v>2.984433118007011</v>
+        <v>2.97426733616807</v>
       </c>
       <c r="T96">
-        <v>14.44214131279889</v>
+        <v>14.38864995471218</v>
       </c>
       <c r="U96">
-        <v>0.3346487374989669</v>
+        <v>0.3196487374989669</v>
       </c>
       <c r="V96">
-        <v>0.07782394745318516</v>
+        <v>0.08147595378029149</v>
       </c>
       <c r="W96">
-        <v>0.3086050517365725</v>
+        <v>0.2936050517365725</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9185,7 +9185,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.2223541355805291</v>
+        <v>0.2327884393722615</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9196,13 +9196,13 @@
         <v>0.9500000000000001</v>
       </c>
       <c r="B97">
-        <v>0.4720432230877883</v>
+        <v>0.4571832761774519</v>
       </c>
       <c r="C97">
-        <v>-12969.55013788214</v>
+        <v>-12489.95260234282</v>
       </c>
       <c r="D97">
-        <v>13200.39986211786</v>
+        <v>13679.99739765718</v>
       </c>
       <c r="E97">
         <v>17766.65</v>
@@ -9229,37 +9229,37 @@
         <v>1991.289795918367</v>
       </c>
       <c r="M97">
-        <v>9050.759162465185</v>
+        <v>8645.075912465185</v>
       </c>
       <c r="N97">
-        <v>-7059.469366546818</v>
+        <v>-6653.786116546818</v>
       </c>
       <c r="O97">
-        <v>-2470.814278291386</v>
+        <v>-2328.825140791386</v>
       </c>
       <c r="P97">
-        <v>-4588.655088255431</v>
+        <v>-4324.960975755432</v>
       </c>
       <c r="Q97">
-        <v>-2620.455088255431</v>
+        <v>-2356.760975755431</v>
       </c>
       <c r="R97">
         <v>19.00000000000003</v>
       </c>
       <c r="S97">
-        <v>3.572159741608415</v>
+        <v>3.559960803401686</v>
       </c>
       <c r="T97">
-        <v>17.33056957535868</v>
+        <v>17.26637994565463</v>
       </c>
       <c r="U97">
-        <v>0.3346487374989669</v>
+        <v>0.3196487374989669</v>
       </c>
       <c r="V97">
-        <v>0.07700474800630952</v>
+        <v>0.08061831216155158</v>
       </c>
       <c r="W97">
-        <v>0.3088791957972293</v>
+        <v>0.2938791957972293</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9267,7 +9267,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.2200135657323129</v>
+        <v>0.2303380347472902</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9278,13 +9278,13 @@
         <v>0.96</v>
       </c>
       <c r="B98">
-        <v>0.474931710462778</v>
+        <v>0.4599217635524415</v>
       </c>
       <c r="C98">
-        <v>-13343.09208570353</v>
+        <v>-12865.10512679942</v>
       </c>
       <c r="D98">
-        <v>13111.54791429647</v>
+        <v>13589.53487320058</v>
       </c>
       <c r="E98">
         <v>18051.34</v>
@@ -9311,37 +9311,37 @@
         <v>1991.289795918367</v>
       </c>
       <c r="M98">
-        <v>9146.030311543764</v>
+        <v>8736.076711543765</v>
       </c>
       <c r="N98">
-        <v>-7154.740515625396</v>
+        <v>-6744.786915625397</v>
       </c>
       <c r="O98">
-        <v>-2504.159180468889</v>
+        <v>-2360.675420468889</v>
       </c>
       <c r="P98">
-        <v>-4650.581335156508</v>
+        <v>-4384.111495156509</v>
       </c>
       <c r="Q98">
-        <v>-2682.381335156507</v>
+        <v>-2415.911495156508</v>
       </c>
       <c r="R98">
         <v>23.99999999999998</v>
       </c>
       <c r="S98">
-        <v>4.453749677010509</v>
+        <v>4.438501004252097</v>
       </c>
       <c r="T98">
-        <v>21.6632119691983</v>
+        <v>21.58297493206824</v>
       </c>
       <c r="U98">
-        <v>0.3346487374989669</v>
+        <v>0.3196487374989669</v>
       </c>
       <c r="V98">
-        <v>0.07620261521457715</v>
+        <v>0.07977853807653541</v>
       </c>
       <c r="W98">
-        <v>0.3091476285232891</v>
+        <v>0.2941476285232891</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9349,7 +9349,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.2177217577559347</v>
+        <v>0.2279386802186726</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9360,13 +9360,13 @@
         <v>0.97</v>
       </c>
       <c r="B99">
-        <v>0.4778201978377677</v>
+        <v>0.4626602509274312</v>
       </c>
       <c r="C99">
-        <v>-13715.445905142</v>
+        <v>-13239.06909715147</v>
       </c>
       <c r="D99">
-        <v>13023.884094858</v>
+        <v>13500.26090284853</v>
       </c>
       <c r="E99">
         <v>18336.03</v>
@@ -9393,37 +9393,37 @@
         <v>1991.289795918367</v>
       </c>
       <c r="M99">
-        <v>9241.301460622346</v>
+        <v>8827.077510622346</v>
       </c>
       <c r="N99">
-        <v>-7250.011664703979</v>
+        <v>-6835.787714703979</v>
       </c>
       <c r="O99">
-        <v>-2537.504082646392</v>
+        <v>-2392.525700146392</v>
       </c>
       <c r="P99">
-        <v>-4712.507582057586</v>
+        <v>-4443.262014557587</v>
       </c>
       <c r="Q99">
-        <v>-2744.307582057585</v>
+        <v>-2475.062014557586</v>
       </c>
       <c r="R99">
         <v>32.33333333333331</v>
       </c>
       <c r="S99">
-        <v>5.923066236014012</v>
+        <v>5.90273467233613</v>
       </c>
       <c r="T99">
-        <v>28.88428262559774</v>
+        <v>28.77729990942432</v>
       </c>
       <c r="U99">
-        <v>0.3346487374989669</v>
+        <v>0.3196487374989669</v>
       </c>
       <c r="V99">
-        <v>0.07541702124329283</v>
+        <v>0.0789560789211072</v>
       </c>
       <c r="W99">
-        <v>0.3094105265539662</v>
+        <v>0.2944105265539662</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9431,7 +9431,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.2154772035522653</v>
+        <v>0.2255887969174492</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9442,13 +9442,13 @@
         <v>0.98</v>
       </c>
       <c r="B100">
-        <v>0.4807086852127574</v>
+        <v>0.4653987383024208</v>
       </c>
       <c r="C100">
-        <v>-14086.63526940031</v>
+        <v>-13611.86778449187</v>
       </c>
       <c r="D100">
-        <v>12937.38473059968</v>
+        <v>13412.15221550812</v>
       </c>
       <c r="E100">
         <v>18620.72</v>
@@ -9475,37 +9475,37 @@
         <v>1991.289795918367</v>
       </c>
       <c r="M100">
-        <v>9336.572609700926</v>
+        <v>8918.078309700926</v>
       </c>
       <c r="N100">
-        <v>-7345.282813782559</v>
+        <v>-6926.788513782559</v>
       </c>
       <c r="O100">
-        <v>-2570.848984823896</v>
+        <v>-2424.375979823895</v>
       </c>
       <c r="P100">
-        <v>-4774.433828958663</v>
+        <v>-4502.412533958664</v>
       </c>
       <c r="Q100">
-        <v>-2806.233828958663</v>
+        <v>-2534.212533958663</v>
       </c>
       <c r="R100">
         <v>48.99999999999996</v>
       </c>
       <c r="S100">
-        <v>8.861699354021018</v>
+        <v>8.831202008504194</v>
       </c>
       <c r="T100">
-        <v>43.32642393839661</v>
+        <v>43.16594986413647</v>
       </c>
       <c r="U100">
-        <v>0.3346487374989669</v>
+        <v>0.3196487374989669</v>
       </c>
       <c r="V100">
-        <v>0.07464745980203474</v>
+        <v>0.07815040464640205</v>
       </c>
       <c r="W100">
-        <v>0.3096680593187111</v>
+        <v>0.294668059318711</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9513,7 +9513,7 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.2132784565772421</v>
+        <v>0.2232868704182915</v>
       </c>
       <c r="Z100">
         <v>0</v>
@@ -9524,13 +9524,13 @@
         <v>0.99</v>
       </c>
       <c r="B101">
-        <v>0.4835971725877471</v>
+        <v>0.4681372256774106</v>
       </c>
       <c r="C101">
-        <v>-14456.68322691941</v>
+        <v>-13983.52385634287</v>
       </c>
       <c r="D101">
-        <v>12852.0267730806</v>
+        <v>13325.18614365713</v>
       </c>
       <c r="E101">
         <v>18905.41</v>
@@ -9557,37 +9557,37 @@
         <v>1991.289795918367</v>
       </c>
       <c r="M101">
-        <v>9431.843758779509</v>
+        <v>9009.079108779508</v>
       </c>
       <c r="N101">
-        <v>-7440.553962861141</v>
+        <v>-7017.78931286114</v>
       </c>
       <c r="O101">
-        <v>-2604.193887001399</v>
+        <v>-2456.226259501399</v>
       </c>
       <c r="P101">
-        <v>-4836.360075859742</v>
+        <v>-4561.563053359741</v>
       </c>
       <c r="Q101">
-        <v>-2868.160075859742</v>
+        <v>-2593.363053359741</v>
       </c>
       <c r="R101">
         <v>98.99999999999991</v>
       </c>
       <c r="S101">
-        <v>17.67759870804204</v>
+        <v>17.61660401700839</v>
       </c>
       <c r="T101">
-        <v>86.65284787679322</v>
+        <v>86.33189972827296</v>
       </c>
       <c r="U101">
-        <v>0.3346487374989669</v>
+        <v>0.3196487374989669</v>
       </c>
       <c r="V101">
-        <v>0.07389344505655963</v>
+        <v>0.07736100661967071</v>
       </c>
       <c r="W101">
-        <v>0.30992038940134</v>
+        <v>0.2949203894013399</v>
       </c>
       <c r="X101" t="inlineStr">
         <is>
@@ -9595,7 +9595,7 @@
         </is>
       </c>
       <c r="Y101">
-        <v>0.2111241287330275</v>
+        <v>0.2210314474847734</v>
       </c>
       <c r="Z101">
         <v>0</v>

--- a/research/traditional_assets/database/data/argentina/argentina_oil_gas_integrated.xlsx
+++ b/research/traditional_assets/database/data/argentina/argentina_oil_gas_integrated.xlsx
@@ -1266,7 +1266,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1403,22 +1403,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.236081180389216</v>
+        <v>0.2360566630515971</v>
       </c>
       <c r="C2">
-        <v>30451.42108769686</v>
+        <v>30170.54236231577</v>
       </c>
       <c r="D2">
-        <v>29575.82108769687</v>
+        <v>29579.63236231577</v>
       </c>
       <c r="E2">
-        <v>-9278.9</v>
+        <v>-8994.209999999999</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>284.69</v>
       </c>
       <c r="G2">
         <v>875.6</v>
@@ -1439,28 +1439,28 @@
         <v>1991.289795918367</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>48.15495407858088</v>
       </c>
       <c r="N2">
-        <v>1991.289795918367</v>
+        <v>1943.134841839787</v>
       </c>
       <c r="O2">
-        <v>696.9514285714286</v>
+        <v>680.0971946439253</v>
       </c>
       <c r="P2">
-        <v>1294.338367346939</v>
+        <v>1263.037647195861</v>
       </c>
       <c r="Q2">
-        <v>3262.538367346939</v>
+        <v>3231.237647195861</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.236081180389216</v>
+        <v>0.2373305012705594</v>
       </c>
       <c r="T2">
-        <v>0.9349222590860211</v>
+        <v>0.9410606375547678</v>
       </c>
       <c r="U2">
         <v>0.1691487374989669</v>
@@ -1477,7 +1477,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>41.35171207242589</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1485,22 +1485,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.2360566630515971</v>
+        <v>0.2360321457139781</v>
       </c>
       <c r="C3">
-        <v>30170.54236231577</v>
+        <v>29889.66461933757</v>
       </c>
       <c r="D3">
-        <v>29579.63236231577</v>
+        <v>29583.44461933757</v>
       </c>
       <c r="E3">
-        <v>-8994.209999999999</v>
+        <v>-8709.52</v>
       </c>
       <c r="F3">
-        <v>284.69</v>
+        <v>569.38</v>
       </c>
       <c r="G3">
         <v>875.6</v>
@@ -1521,28 +1521,28 @@
         <v>1991.289795918367</v>
       </c>
       <c r="M3">
-        <v>48.15495407858088</v>
+        <v>96.30990815716176</v>
       </c>
       <c r="N3">
-        <v>1943.134841839787</v>
+        <v>1894.979887761206</v>
       </c>
       <c r="O3">
-        <v>680.0971946439253</v>
+        <v>663.242960716422</v>
       </c>
       <c r="P3">
-        <v>1263.037647195861</v>
+        <v>1231.736927044784</v>
       </c>
       <c r="Q3">
-        <v>3231.237647195861</v>
+        <v>3199.936927044784</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.2373305012705594</v>
+        <v>0.2386053184964199</v>
       </c>
       <c r="T3">
-        <v>0.9410606375547678</v>
+        <v>0.9473242890534888</v>
       </c>
       <c r="U3">
         <v>0.1691487374989669</v>
@@ -1559,7 +1559,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>41.35171207242589</v>
+        <v>20.67585603621295</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1567,22 +1567,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.2360321457139781</v>
+        <v>0.2360076283763591</v>
       </c>
       <c r="C4">
-        <v>29889.66461933757</v>
+        <v>29608.78785914218</v>
       </c>
       <c r="D4">
-        <v>29583.44461933757</v>
+        <v>29587.25785914218</v>
       </c>
       <c r="E4">
-        <v>-8709.52</v>
+        <v>-8424.83</v>
       </c>
       <c r="F4">
-        <v>569.38</v>
+        <v>854.0699999999999</v>
       </c>
       <c r="G4">
         <v>875.6</v>
@@ -1603,28 +1603,28 @@
         <v>1991.289795918367</v>
       </c>
       <c r="M4">
-        <v>96.30990815716176</v>
+        <v>144.4648622357426</v>
       </c>
       <c r="N4">
-        <v>1894.979887761206</v>
+        <v>1846.824933682625</v>
       </c>
       <c r="O4">
-        <v>663.242960716422</v>
+        <v>646.3887267889186</v>
       </c>
       <c r="P4">
-        <v>1231.736927044784</v>
+        <v>1200.436206893706</v>
       </c>
       <c r="Q4">
-        <v>3199.936927044784</v>
+        <v>3168.636206893706</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.2386053184964199</v>
+        <v>0.2399064206135353</v>
       </c>
       <c r="T4">
-        <v>0.9473242890534888</v>
+        <v>0.9537170880057916</v>
       </c>
       <c r="U4">
         <v>0.1691487374989669</v>
@@ -1641,7 +1641,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>20.67585603621295</v>
+        <v>13.78390402414196</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1649,22 +1649,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.2360076283763591</v>
+        <v>0.2359831110387402</v>
       </c>
       <c r="C5">
-        <v>29608.78785914218</v>
+        <v>29327.91208210967</v>
       </c>
       <c r="D5">
-        <v>29587.25785914218</v>
+        <v>29591.07208210967</v>
       </c>
       <c r="E5">
-        <v>-8424.83</v>
+        <v>-8140.139999999999</v>
       </c>
       <c r="F5">
-        <v>854.0699999999999</v>
+        <v>1138.76</v>
       </c>
       <c r="G5">
         <v>875.6</v>
@@ -1685,28 +1685,28 @@
         <v>1991.289795918367</v>
       </c>
       <c r="M5">
-        <v>144.4648622357426</v>
+        <v>192.6198163143235</v>
       </c>
       <c r="N5">
-        <v>1846.824933682625</v>
+        <v>1798.669979604044</v>
       </c>
       <c r="O5">
-        <v>646.3887267889186</v>
+        <v>629.5344928614153</v>
       </c>
       <c r="P5">
-        <v>1200.436206893706</v>
+        <v>1169.135486742628</v>
       </c>
       <c r="Q5">
-        <v>3168.636206893706</v>
+        <v>3137.335486742629</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.2399064206135353</v>
+        <v>0.2412346290247573</v>
       </c>
       <c r="T5">
-        <v>0.9537170880057916</v>
+        <v>0.9602430702696009</v>
       </c>
       <c r="U5">
         <v>0.1691487374989669</v>
@@ -1723,7 +1723,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>13.78390402414196</v>
+        <v>10.33792801810647</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1731,22 +1731,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.2359831110387402</v>
+        <v>0.2360073437011212</v>
       </c>
       <c r="C6">
-        <v>29327.91208210967</v>
+        <v>29039.45214113207</v>
       </c>
       <c r="D6">
-        <v>29591.07208210967</v>
+        <v>29587.30214113207</v>
       </c>
       <c r="E6">
-        <v>-8140.139999999999</v>
+        <v>-7855.45</v>
       </c>
       <c r="F6">
-        <v>1138.76</v>
+        <v>1423.45</v>
       </c>
       <c r="G6">
         <v>875.6</v>
@@ -1767,45 +1767,45 @@
         <v>1991.289795918367</v>
       </c>
       <c r="M6">
-        <v>192.6198163143235</v>
+        <v>242.9099453929044</v>
       </c>
       <c r="N6">
-        <v>1798.669979604044</v>
+        <v>1748.379850525463</v>
       </c>
       <c r="O6">
-        <v>629.5344928614153</v>
+        <v>611.9329476839121</v>
       </c>
       <c r="P6">
-        <v>1169.135486742628</v>
+        <v>1136.446902841551</v>
       </c>
       <c r="Q6">
-        <v>3137.335486742629</v>
+        <v>3104.646902841551</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.2412346290247573</v>
+        <v>0.2425907997183208</v>
       </c>
       <c r="T6">
-        <v>0.9602430702696009</v>
+        <v>0.9669064416337008</v>
       </c>
       <c r="U6">
-        <v>0.1691487374989669</v>
+        <v>0.1706487374989669</v>
       </c>
       <c r="V6">
         <v>0.35</v>
       </c>
       <c r="W6">
-        <v>0.1099466793743285</v>
+        <v>0.1109216793743285</v>
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y6">
-        <v>10.33792801810647</v>
+        <v>8.197646221102541</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1813,22 +1813,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.2360073437011212</v>
+        <v>0.2359925763635022</v>
       </c>
       <c r="C7">
-        <v>29039.45214113207</v>
+        <v>28757.05942154284</v>
       </c>
       <c r="D7">
-        <v>29587.30214113207</v>
+        <v>29589.59942154284</v>
       </c>
       <c r="E7">
-        <v>-7855.45</v>
+        <v>-7570.759999999999</v>
       </c>
       <c r="F7">
-        <v>1423.45</v>
+        <v>1708.14</v>
       </c>
       <c r="G7">
         <v>875.6</v>
@@ -1849,28 +1849,28 @@
         <v>1991.289795918367</v>
       </c>
       <c r="M7">
-        <v>242.9099453929044</v>
+        <v>291.4919344714853</v>
       </c>
       <c r="N7">
-        <v>1748.379850525463</v>
+        <v>1699.797861446882</v>
       </c>
       <c r="O7">
-        <v>611.9329476839121</v>
+        <v>594.9292515064087</v>
       </c>
       <c r="P7">
-        <v>1136.446902841551</v>
+        <v>1104.868609940473</v>
       </c>
       <c r="Q7">
-        <v>3104.646902841551</v>
+        <v>3073.068609940474</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.2425907997183208</v>
+        <v>0.2439758251074921</v>
       </c>
       <c r="T7">
-        <v>0.9669064416337008</v>
+        <v>0.9737115868566114</v>
       </c>
       <c r="U7">
         <v>0.1706487374989669</v>
@@ -1887,7 +1887,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>8.197646221102541</v>
+        <v>6.831371850918785</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1895,22 +1895,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.2359925763635022</v>
+        <v>0.2360551590258833</v>
       </c>
       <c r="C8">
-        <v>28757.05942154284</v>
+        <v>28462.63619843304</v>
       </c>
       <c r="D8">
-        <v>29589.59942154284</v>
+        <v>29579.86619843304</v>
       </c>
       <c r="E8">
-        <v>-7570.76</v>
+        <v>-7286.07</v>
       </c>
       <c r="F8">
-        <v>1708.14</v>
+        <v>1992.83</v>
       </c>
       <c r="G8">
         <v>875.6</v>
@@ -1931,45 +1931,45 @@
         <v>1991.289795918367</v>
       </c>
       <c r="M8">
-        <v>291.4919344714853</v>
+        <v>343.4617345500661</v>
       </c>
       <c r="N8">
-        <v>1699.797861446882</v>
+        <v>1647.828061368301</v>
       </c>
       <c r="O8">
-        <v>594.9292515064087</v>
+        <v>576.7398214789055</v>
       </c>
       <c r="P8">
-        <v>1104.868609940473</v>
+        <v>1071.088239889396</v>
       </c>
       <c r="Q8">
-        <v>3073.068609940474</v>
+        <v>3039.288239889396</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.2439758251074921</v>
+        <v>0.2453906359889035</v>
       </c>
       <c r="T8">
-        <v>0.9737115868566114</v>
+        <v>0.9806630792886167</v>
       </c>
       <c r="U8">
-        <v>0.1706487374989669</v>
+        <v>0.1723487374989669</v>
       </c>
       <c r="V8">
         <v>0.35</v>
       </c>
       <c r="W8">
-        <v>0.1109216793743285</v>
+        <v>0.1120266793743285</v>
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y8">
-        <v>6.831371850918785</v>
+        <v>5.79770494237721</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1977,22 +1977,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.2360551590258833</v>
+        <v>0.2360930416882643</v>
       </c>
       <c r="C9">
-        <v>28462.63619843304</v>
+        <v>28172.05757489468</v>
       </c>
       <c r="D9">
-        <v>29579.86619843304</v>
+        <v>29573.97757489468</v>
       </c>
       <c r="E9">
-        <v>-7286.07</v>
+        <v>-7001.379999999999</v>
       </c>
       <c r="F9">
-        <v>1992.83</v>
+        <v>2277.52</v>
       </c>
       <c r="G9">
         <v>875.6</v>
@@ -2013,45 +2013,45 @@
         <v>1991.289795918367</v>
       </c>
       <c r="M9">
-        <v>343.4617345500662</v>
+        <v>394.349712628647</v>
       </c>
       <c r="N9">
-        <v>1647.828061368301</v>
+        <v>1596.94008328972</v>
       </c>
       <c r="O9">
-        <v>576.7398214789054</v>
+        <v>558.9290291514021</v>
       </c>
       <c r="P9">
-        <v>1071.088239889396</v>
+        <v>1038.011054138318</v>
       </c>
       <c r="Q9">
-        <v>3039.288239889396</v>
+        <v>3006.211054138319</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.2453906359889035</v>
+        <v>0.2468362036286065</v>
       </c>
       <c r="T9">
-        <v>0.9806630792886167</v>
+        <v>0.9877656911213178</v>
       </c>
       <c r="U9">
-        <v>0.1723487374989669</v>
+        <v>0.1731487374989669</v>
       </c>
       <c r="V9">
         <v>0.35</v>
       </c>
       <c r="W9">
-        <v>0.1120266793743285</v>
+        <v>0.1125466793743285</v>
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y9">
-        <v>5.797704942377208</v>
+        <v>5.049553054432003</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2059,22 +2059,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.2360930416882643</v>
+        <v>0.2360945243506453</v>
       </c>
       <c r="C10">
-        <v>28172.05757489468</v>
+        <v>27887.13715195342</v>
       </c>
       <c r="D10">
-        <v>29573.97757489468</v>
+        <v>29573.74715195342</v>
       </c>
       <c r="E10">
-        <v>-7001.379999999999</v>
+        <v>-6716.69</v>
       </c>
       <c r="F10">
-        <v>2277.52</v>
+        <v>2562.21</v>
       </c>
       <c r="G10">
         <v>875.6</v>
@@ -2095,28 +2095,28 @@
         <v>1991.289795918367</v>
       </c>
       <c r="M10">
-        <v>394.349712628647</v>
+        <v>443.6434267072279</v>
       </c>
       <c r="N10">
-        <v>1596.94008328972</v>
+        <v>1547.646369211139</v>
       </c>
       <c r="O10">
-        <v>558.9290291514021</v>
+        <v>541.6762292238988</v>
       </c>
       <c r="P10">
-        <v>1038.011054138318</v>
+        <v>1005.970139987241</v>
       </c>
       <c r="Q10">
-        <v>3006.211054138319</v>
+        <v>2974.170139987241</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.2468362036286065</v>
+        <v>0.2483135419856657</v>
       </c>
       <c r="T10">
-        <v>0.9877656911213178</v>
+        <v>0.9950244043129796</v>
       </c>
       <c r="U10">
         <v>0.1731487374989669</v>
@@ -2133,7 +2133,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>5.049553054432003</v>
+        <v>4.488491603939559</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2141,22 +2141,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.2360945243506453</v>
+        <v>0.2361610070130263</v>
       </c>
       <c r="C11">
-        <v>27887.13715195342</v>
+        <v>27592.11866358232</v>
       </c>
       <c r="D11">
-        <v>29573.74715195342</v>
+        <v>29563.41866358232</v>
       </c>
       <c r="E11">
-        <v>-6716.69</v>
+        <v>-6432</v>
       </c>
       <c r="F11">
-        <v>2562.21</v>
+        <v>2846.9</v>
       </c>
       <c r="G11">
         <v>875.6</v>
@@ -2177,45 +2177,45 @@
         <v>1991.289795918367</v>
       </c>
       <c r="M11">
-        <v>443.6434267072279</v>
+        <v>495.7840407858087</v>
       </c>
       <c r="N11">
-        <v>1547.646369211139</v>
+        <v>1495.505755132559</v>
       </c>
       <c r="O11">
-        <v>541.6762292238988</v>
+        <v>523.4270142963956</v>
       </c>
       <c r="P11">
-        <v>1005.970139987241</v>
+        <v>972.0787408361632</v>
       </c>
       <c r="Q11">
-        <v>2974.170139987241</v>
+        <v>2940.278740836164</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.2483135419856657</v>
+        <v>0.2498237100839928</v>
       </c>
       <c r="T11">
-        <v>0.9950244043129796</v>
+        <v>1.002444422242234</v>
       </c>
       <c r="U11">
-        <v>0.1731487374989669</v>
+        <v>0.1741487374989669</v>
       </c>
       <c r="V11">
         <v>0.35</v>
       </c>
       <c r="W11">
-        <v>0.1125466793743285</v>
+        <v>0.1131966793743285</v>
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y11">
-        <v>4.488491603939559</v>
+        <v>4.016445936343996</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2223,22 +2223,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.2361610070130264</v>
+        <v>0.2361689896754074</v>
       </c>
       <c r="C12">
-        <v>27592.11866358231</v>
+        <v>27306.18899324302</v>
       </c>
       <c r="D12">
-        <v>29563.41866358231</v>
+        <v>29562.17899324303</v>
       </c>
       <c r="E12">
-        <v>-6432</v>
+        <v>-6147.309999999999</v>
       </c>
       <c r="F12">
-        <v>2846.9</v>
+        <v>3131.59</v>
       </c>
       <c r="G12">
         <v>875.6</v>
@@ -2259,28 +2259,28 @@
         <v>1991.289795918367</v>
       </c>
       <c r="M12">
-        <v>495.7840407858088</v>
+        <v>545.3624448643897</v>
       </c>
       <c r="N12">
-        <v>1495.505755132559</v>
+        <v>1445.927351053978</v>
       </c>
       <c r="O12">
-        <v>523.4270142963954</v>
+        <v>506.0745728688922</v>
       </c>
       <c r="P12">
-        <v>972.0787408361631</v>
+        <v>939.8527781850856</v>
       </c>
       <c r="Q12">
-        <v>2940.278740836163</v>
+        <v>2908.052778185086</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.2498237100839928</v>
+        <v>0.2513678145440801</v>
       </c>
       <c r="T12">
-        <v>1.002444422242234</v>
+        <v>1.010031182147426</v>
       </c>
       <c r="U12">
         <v>0.1741487374989669</v>
@@ -2297,7 +2297,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>4.016445936343995</v>
+        <v>3.651314487585451</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2305,22 +2305,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.2361689896754074</v>
+        <v>0.2361769723377884</v>
       </c>
       <c r="C13">
-        <v>27306.18899324302</v>
+        <v>27020.25942686453</v>
       </c>
       <c r="D13">
-        <v>29562.17899324303</v>
+        <v>29560.93942686453</v>
       </c>
       <c r="E13">
-        <v>-6147.309999999999</v>
+        <v>-5862.62</v>
       </c>
       <c r="F13">
-        <v>3131.59</v>
+        <v>3416.28</v>
       </c>
       <c r="G13">
         <v>875.6</v>
@@ -2341,28 +2341,28 @@
         <v>1991.289795918367</v>
       </c>
       <c r="M13">
-        <v>545.3624448643897</v>
+        <v>594.9408489429704</v>
       </c>
       <c r="N13">
-        <v>1445.927351053978</v>
+        <v>1396.348946975397</v>
       </c>
       <c r="O13">
-        <v>506.0745728688922</v>
+        <v>488.7221314413889</v>
       </c>
       <c r="P13">
-        <v>939.8527781850856</v>
+        <v>907.6268155340081</v>
       </c>
       <c r="Q13">
-        <v>2908.052778185086</v>
+        <v>2875.826815534008</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.2513678145440801</v>
+        <v>0.2529470122873511</v>
       </c>
       <c r="T13">
-        <v>1.010031182147426</v>
+        <v>1.0177903684141</v>
       </c>
       <c r="U13">
         <v>0.1741487374989669</v>
@@ -2379,7 +2379,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>3.651314487585451</v>
+        <v>3.347038280286664</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2387,22 +2387,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.2361769723377884</v>
+        <v>0.2361849550001694</v>
       </c>
       <c r="C14">
-        <v>27020.25942686453</v>
+        <v>26734.32996443374</v>
       </c>
       <c r="D14">
-        <v>29560.93942686453</v>
+        <v>29559.69996443374</v>
       </c>
       <c r="E14">
-        <v>-5862.62</v>
+        <v>-5577.929999999999</v>
       </c>
       <c r="F14">
-        <v>3416.28</v>
+        <v>3700.97</v>
       </c>
       <c r="G14">
         <v>875.6</v>
@@ -2423,28 +2423,28 @@
         <v>1991.289795918367</v>
       </c>
       <c r="M14">
-        <v>594.9408489429704</v>
+        <v>644.5192530215514</v>
       </c>
       <c r="N14">
-        <v>1396.348946975397</v>
+        <v>1346.770542896816</v>
       </c>
       <c r="O14">
-        <v>488.7221314413889</v>
+        <v>471.3696900138856</v>
       </c>
       <c r="P14">
-        <v>907.6268155340081</v>
+        <v>875.4008528829305</v>
       </c>
       <c r="Q14">
-        <v>2875.826815534008</v>
+        <v>2843.600852882931</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.2529470122873511</v>
+        <v>0.2545625134270192</v>
       </c>
       <c r="T14">
-        <v>1.0177903684141</v>
+        <v>1.025727926778859</v>
       </c>
       <c r="U14">
         <v>0.1741487374989669</v>
@@ -2461,7 +2461,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>3.347038280286664</v>
+        <v>3.089573797187689</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2469,22 +2469,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.2361849550001694</v>
+        <v>0.2364204376625505</v>
       </c>
       <c r="C15">
-        <v>26734.32996443374</v>
+        <v>26413.12343487287</v>
       </c>
       <c r="D15">
-        <v>29559.69996443374</v>
+        <v>29523.18343487287</v>
       </c>
       <c r="E15">
-        <v>-5577.929999999999</v>
+        <v>-5293.24</v>
       </c>
       <c r="F15">
-        <v>3700.97</v>
+        <v>3985.66</v>
       </c>
       <c r="G15">
         <v>875.6</v>
@@ -2505,45 +2505,45 @@
         <v>1991.289795918367</v>
       </c>
       <c r="M15">
-        <v>644.5192530215514</v>
+        <v>704.0618071001323</v>
       </c>
       <c r="N15">
-        <v>1346.770542896816</v>
+        <v>1287.227988818235</v>
       </c>
       <c r="O15">
-        <v>471.3696900138856</v>
+        <v>450.5297960863823</v>
       </c>
       <c r="P15">
-        <v>875.4008528829305</v>
+        <v>836.6981927318529</v>
       </c>
       <c r="Q15">
-        <v>2843.600852882931</v>
+        <v>2804.898192731853</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.2545625134270192</v>
+        <v>0.2562155843606331</v>
       </c>
       <c r="T15">
-        <v>1.025727926778859</v>
+        <v>1.033850079524193</v>
       </c>
       <c r="U15">
-        <v>0.1741487374989669</v>
+        <v>0.1766487374989669</v>
       </c>
       <c r="V15">
         <v>0.35</v>
       </c>
       <c r="W15">
-        <v>0.1131966793743285</v>
+        <v>0.1148216793743285</v>
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y15">
-        <v>3.089573797187689</v>
+        <v>2.828288334684748</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2551,22 +2551,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.2364204376625505</v>
+        <v>0.2364446703249314</v>
       </c>
       <c r="C16">
-        <v>26413.12343487287</v>
+        <v>26124.68077115891</v>
       </c>
       <c r="D16">
-        <v>29523.18343487287</v>
+        <v>29519.43077115891</v>
       </c>
       <c r="E16">
-        <v>-5293.24</v>
+        <v>-5008.549999999999</v>
       </c>
       <c r="F16">
-        <v>3985.66</v>
+        <v>4270.35</v>
       </c>
       <c r="G16">
         <v>875.6</v>
@@ -2587,28 +2587,28 @@
         <v>1991.289795918367</v>
       </c>
       <c r="M16">
-        <v>704.0618071001323</v>
+        <v>754.3519361787132</v>
       </c>
       <c r="N16">
-        <v>1287.227988818235</v>
+        <v>1236.937859739654</v>
       </c>
       <c r="O16">
-        <v>450.5297960863823</v>
+        <v>432.928250908879</v>
       </c>
       <c r="P16">
-        <v>836.6981927318529</v>
+        <v>804.0096088307753</v>
       </c>
       <c r="Q16">
-        <v>2804.898192731853</v>
+        <v>2772.209608830775</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.2562155843606331</v>
+        <v>0.2579075510809202</v>
       </c>
       <c r="T16">
-        <v>1.033850079524193</v>
+        <v>1.042163341745888</v>
       </c>
       <c r="U16">
         <v>0.1766487374989669</v>
@@ -2625,7 +2625,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>2.828288334684748</v>
+        <v>2.639735779039098</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2633,22 +2633,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.2364446703249314</v>
+        <v>0.2368329029873125</v>
       </c>
       <c r="C17">
-        <v>26124.68077115891</v>
+        <v>25779.99897382428</v>
       </c>
       <c r="D17">
-        <v>29519.43077115891</v>
+        <v>29459.43897382428</v>
       </c>
       <c r="E17">
-        <v>-5008.55</v>
+        <v>-4723.86</v>
       </c>
       <c r="F17">
-        <v>4270.349999999999</v>
+        <v>4555.04</v>
       </c>
       <c r="G17">
         <v>875.6</v>
@@ -2669,45 +2669,45 @@
         <v>1991.289795918367</v>
       </c>
       <c r="M17">
-        <v>754.3519361787131</v>
+        <v>820.5847052572941</v>
       </c>
       <c r="N17">
-        <v>1236.937859739654</v>
+        <v>1170.705090661073</v>
       </c>
       <c r="O17">
-        <v>432.928250908879</v>
+        <v>409.7467817313757</v>
       </c>
       <c r="P17">
-        <v>804.0096088307754</v>
+        <v>760.9583089296978</v>
       </c>
       <c r="Q17">
-        <v>2772.209608830776</v>
+        <v>2729.158308929698</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.2579075510809202</v>
+        <v>0.259639802723119</v>
       </c>
       <c r="T17">
-        <v>1.042163341745888</v>
+        <v>1.050674538782386</v>
       </c>
       <c r="U17">
-        <v>0.1766487374989669</v>
+        <v>0.1801487374989669</v>
       </c>
       <c r="V17">
         <v>0.35</v>
       </c>
       <c r="W17">
-        <v>0.1148216793743285</v>
+        <v>0.1170966793743285</v>
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y17">
-        <v>2.639735779039099</v>
+        <v>2.426671839190568</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2715,22 +2715,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.2368329029873125</v>
+        <v>0.2368798856496936</v>
       </c>
       <c r="C18">
-        <v>25779.99897382428</v>
+        <v>25488.06549620477</v>
       </c>
       <c r="D18">
-        <v>29459.43897382428</v>
+        <v>29452.19549620477</v>
       </c>
       <c r="E18">
-        <v>-4723.86</v>
+        <v>-4439.169999999999</v>
       </c>
       <c r="F18">
-        <v>4555.04</v>
+        <v>4839.73</v>
       </c>
       <c r="G18">
         <v>875.6</v>
@@ -2751,28 +2751,28 @@
         <v>1991.289795918367</v>
       </c>
       <c r="M18">
-        <v>820.5847052572941</v>
+        <v>871.8712493358751</v>
       </c>
       <c r="N18">
-        <v>1170.705090661073</v>
+        <v>1119.418546582492</v>
       </c>
       <c r="O18">
-        <v>409.7467817313757</v>
+        <v>391.7964913038723</v>
       </c>
       <c r="P18">
-        <v>760.9583089296978</v>
+        <v>727.6220552786201</v>
       </c>
       <c r="Q18">
-        <v>2729.158308929698</v>
+        <v>2695.822055278621</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.259639802723119</v>
+        <v>0.2614137953687443</v>
       </c>
       <c r="T18">
-        <v>1.050674538782386</v>
+        <v>1.0593908249041</v>
       </c>
       <c r="U18">
         <v>0.1801487374989669</v>
@@ -2789,7 +2789,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>2.426671839190568</v>
+        <v>2.28392643688524</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2797,22 +2797,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.2368798856496936</v>
+        <v>0.2372544683120746</v>
       </c>
       <c r="C19">
-        <v>25488.06549620477</v>
+        <v>25145.75196879797</v>
       </c>
       <c r="D19">
-        <v>29452.19549620477</v>
+        <v>29394.57196879797</v>
       </c>
       <c r="E19">
-        <v>-4439.169999999999</v>
+        <v>-4154.479999999999</v>
       </c>
       <c r="F19">
-        <v>4839.73</v>
+        <v>5124.420000000001</v>
       </c>
       <c r="G19">
         <v>875.6</v>
@@ -2833,45 +2833,45 @@
         <v>1991.289795918367</v>
       </c>
       <c r="M19">
-        <v>871.8712493358751</v>
+        <v>937.5061694144559</v>
       </c>
       <c r="N19">
-        <v>1119.418546582492</v>
+        <v>1053.783626503911</v>
       </c>
       <c r="O19">
-        <v>391.7964913038723</v>
+        <v>368.824269276369</v>
       </c>
       <c r="P19">
-        <v>727.6220552786201</v>
+        <v>684.9593572275423</v>
       </c>
       <c r="Q19">
-        <v>2695.822055278621</v>
+        <v>2653.159357227542</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.2614137953687443</v>
+        <v>0.2632310561276774</v>
       </c>
       <c r="T19">
-        <v>1.0593908249041</v>
+        <v>1.068319703370246</v>
       </c>
       <c r="U19">
-        <v>0.1801487374989669</v>
+        <v>0.1829487374989669</v>
       </c>
       <c r="V19">
         <v>0.35</v>
       </c>
       <c r="W19">
-        <v>0.1170966793743285</v>
+        <v>0.1189166793743285</v>
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y19">
-        <v>2.28392643688524</v>
+        <v>2.124028471366839</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2879,22 +2879,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.2372544683120746</v>
+        <v>0.2373196509744556</v>
       </c>
       <c r="C20">
-        <v>25145.75196879797</v>
+        <v>24851.05768751024</v>
       </c>
       <c r="D20">
-        <v>29394.57196879797</v>
+        <v>29384.56768751024</v>
       </c>
       <c r="E20">
-        <v>-4154.48</v>
+        <v>-3869.79</v>
       </c>
       <c r="F20">
-        <v>5124.42</v>
+        <v>5409.11</v>
       </c>
       <c r="G20">
         <v>875.6</v>
@@ -2915,28 +2915,28 @@
         <v>1991.289795918367</v>
       </c>
       <c r="M20">
-        <v>937.5061694144558</v>
+        <v>989.5898454930366</v>
       </c>
       <c r="N20">
-        <v>1053.783626503912</v>
+        <v>1001.699950425331</v>
       </c>
       <c r="O20">
-        <v>368.824269276369</v>
+        <v>350.5949826488658</v>
       </c>
       <c r="P20">
-        <v>684.9593572275426</v>
+        <v>651.1049677764651</v>
       </c>
       <c r="Q20">
-        <v>2653.159357227543</v>
+        <v>2619.304967776465</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.2632310561276774</v>
+        <v>0.2650931875226336</v>
       </c>
       <c r="T20">
-        <v>1.068319703370246</v>
+        <v>1.077469047971359</v>
       </c>
       <c r="U20">
         <v>0.1829487374989669</v>
@@ -2953,7 +2953,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>2.124028471366839</v>
+        <v>2.012237499189637</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2961,22 +2961,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.2373196509744556</v>
+        <v>0.2383988336368367</v>
       </c>
       <c r="C21">
-        <v>24851.05768751024</v>
+        <v>24401.71811310151</v>
       </c>
       <c r="D21">
-        <v>29384.56768751024</v>
+        <v>29219.91811310151</v>
       </c>
       <c r="E21">
-        <v>-3869.79</v>
+        <v>-3585.099999999999</v>
       </c>
       <c r="F21">
-        <v>5409.11</v>
+        <v>5693.8</v>
       </c>
       <c r="G21">
         <v>875.6</v>
@@ -2997,45 +2997,45 @@
         <v>1991.289795918367</v>
       </c>
       <c r="M21">
-        <v>989.5898454930366</v>
+        <v>1086.085161571618</v>
       </c>
       <c r="N21">
-        <v>1001.699950425331</v>
+        <v>905.2046343467498</v>
       </c>
       <c r="O21">
-        <v>350.5949826488658</v>
+        <v>316.8216220213624</v>
       </c>
       <c r="P21">
-        <v>651.1049677764651</v>
+        <v>588.3830123253874</v>
       </c>
       <c r="Q21">
-        <v>2619.304967776465</v>
+        <v>2556.583012325388</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.2650931875226336</v>
+        <v>0.2670018722024637</v>
       </c>
       <c r="T21">
-        <v>1.077469047971359</v>
+        <v>1.0868471261875</v>
       </c>
       <c r="U21">
-        <v>0.1829487374989669</v>
+        <v>0.1907487374989669</v>
       </c>
       <c r="V21">
         <v>0.35</v>
       </c>
       <c r="W21">
-        <v>0.1189166793743285</v>
+        <v>0.1239866793743285</v>
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y21">
-        <v>2.012237499189637</v>
+        <v>1.833456405054715</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3043,22 +3043,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.2383988336368367</v>
+        <v>0.2390470662992177</v>
       </c>
       <c r="C22">
-        <v>24401.71811310151</v>
+        <v>24019.01210863765</v>
       </c>
       <c r="D22">
-        <v>29219.91811310151</v>
+        <v>29121.90210863766</v>
       </c>
       <c r="E22">
-        <v>-3585.099999999999</v>
+        <v>-3300.409999999999</v>
       </c>
       <c r="F22">
-        <v>5693.8</v>
+        <v>5978.490000000001</v>
       </c>
       <c r="G22">
         <v>875.6</v>
@@ -3079,45 +3079,45 @@
         <v>1991.289795918367</v>
       </c>
       <c r="M22">
-        <v>1086.085161571618</v>
+        <v>1163.705530650198</v>
       </c>
       <c r="N22">
-        <v>905.2046343467498</v>
+        <v>827.584265268169</v>
       </c>
       <c r="O22">
-        <v>316.8216220213624</v>
+        <v>289.6544928438591</v>
       </c>
       <c r="P22">
-        <v>588.3830123253874</v>
+        <v>537.9297724243099</v>
       </c>
       <c r="Q22">
-        <v>2556.583012325388</v>
+        <v>2506.12977242431</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.2670018722024637</v>
+        <v>0.2689588780134287</v>
       </c>
       <c r="T22">
-        <v>1.0868471261875</v>
+        <v>1.096462624105315</v>
       </c>
       <c r="U22">
-        <v>0.1907487374989669</v>
+        <v>0.1946487374989669</v>
       </c>
       <c r="V22">
         <v>0.35</v>
       </c>
       <c r="W22">
-        <v>0.1239866793743285</v>
+        <v>0.1265216793743285</v>
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y22">
-        <v>1.833456405054715</v>
+        <v>1.711162956152466</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3125,22 +3125,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.2390470662992177</v>
+        <v>0.2391882989615987</v>
       </c>
       <c r="C23">
-        <v>24019.01210863765</v>
+        <v>23713.05420468231</v>
       </c>
       <c r="D23">
-        <v>29121.90210863766</v>
+        <v>29100.63420468231</v>
       </c>
       <c r="E23">
-        <v>-3300.41</v>
+        <v>-3015.719999999999</v>
       </c>
       <c r="F23">
-        <v>5978.49</v>
+        <v>6263.18</v>
       </c>
       <c r="G23">
         <v>875.6</v>
@@ -3161,28 +3161,28 @@
         <v>1991.289795918367</v>
       </c>
       <c r="M23">
-        <v>1163.705530650198</v>
+        <v>1219.120079728779</v>
       </c>
       <c r="N23">
-        <v>827.584265268169</v>
+        <v>772.1697161895881</v>
       </c>
       <c r="O23">
-        <v>289.6544928438591</v>
+        <v>270.2594006663558</v>
       </c>
       <c r="P23">
-        <v>537.9297724243099</v>
+        <v>501.9103155232323</v>
       </c>
       <c r="Q23">
-        <v>2506.12977242431</v>
+        <v>2470.110315523233</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.2689588780134287</v>
+        <v>0.2709660634605723</v>
       </c>
       <c r="T23">
-        <v>1.096462624105315</v>
+        <v>1.106324673251792</v>
       </c>
       <c r="U23">
         <v>0.1946487374989669</v>
@@ -3199,7 +3199,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>1.711162956152466</v>
+        <v>1.633382821781899</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3207,22 +3207,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.2391882989615987</v>
+        <v>0.2393295316239797</v>
       </c>
       <c r="C24">
-        <v>23713.05420468231</v>
+        <v>23407.12734221891</v>
       </c>
       <c r="D24">
-        <v>29100.63420468231</v>
+        <v>29079.39734221891</v>
       </c>
       <c r="E24">
-        <v>-3015.719999999999</v>
+        <v>-2731.03</v>
       </c>
       <c r="F24">
-        <v>6263.18</v>
+        <v>6547.87</v>
       </c>
       <c r="G24">
         <v>875.6</v>
@@ -3243,28 +3243,28 @@
         <v>1991.289795918367</v>
       </c>
       <c r="M24">
-        <v>1219.120079728779</v>
+        <v>1274.53462880736</v>
       </c>
       <c r="N24">
-        <v>772.1697161895881</v>
+        <v>716.7551671110073</v>
       </c>
       <c r="O24">
-        <v>270.2594006663558</v>
+        <v>250.8643084888525</v>
       </c>
       <c r="P24">
-        <v>501.9103155232323</v>
+        <v>465.8908586221547</v>
       </c>
       <c r="Q24">
-        <v>2470.110315523233</v>
+        <v>2434.090858622155</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.2709660634605723</v>
+        <v>0.2730253835946548</v>
       </c>
       <c r="T24">
-        <v>1.106324673251792</v>
+        <v>1.116442879518956</v>
       </c>
       <c r="U24">
         <v>0.1946487374989669</v>
@@ -3281,7 +3281,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>1.633382821781899</v>
+        <v>1.562366177356599</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3289,22 +3289,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.2393295316239797</v>
+        <v>0.2416859642863607</v>
       </c>
       <c r="C25">
-        <v>23407.12734221891</v>
+        <v>22772.62339843177</v>
       </c>
       <c r="D25">
-        <v>29079.39734221891</v>
+        <v>28729.58339843177</v>
       </c>
       <c r="E25">
-        <v>-2731.03</v>
+        <v>-2446.339999999999</v>
       </c>
       <c r="F25">
-        <v>6547.87</v>
+        <v>6832.56</v>
       </c>
       <c r="G25">
         <v>875.6</v>
@@ -3325,45 +3325,45 @@
         <v>1991.289795918367</v>
       </c>
       <c r="M25">
-        <v>1274.53462880736</v>
+        <v>1426.971529885941</v>
       </c>
       <c r="N25">
-        <v>716.7551671110073</v>
+        <v>564.3182660324262</v>
       </c>
       <c r="O25">
-        <v>250.8643084888525</v>
+        <v>197.5113931113492</v>
       </c>
       <c r="P25">
-        <v>465.8908586221547</v>
+        <v>366.8068729210771</v>
       </c>
       <c r="Q25">
-        <v>2434.090858622155</v>
+        <v>2335.006872921078</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.2730253835946548</v>
+        <v>0.2751388963638446</v>
       </c>
       <c r="T25">
-        <v>1.116442879518956</v>
+        <v>1.126827354372099</v>
       </c>
       <c r="U25">
-        <v>0.1946487374989669</v>
+        <v>0.2088487374989669</v>
       </c>
       <c r="V25">
         <v>0.35</v>
       </c>
       <c r="W25">
-        <v>0.1265216793743285</v>
+        <v>0.1357516793743285</v>
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y25">
-        <v>1.562366177356599</v>
+        <v>1.395465679737516</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3371,22 +3371,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.2416859642863607</v>
+        <v>0.2419194969487418</v>
       </c>
       <c r="C26">
-        <v>22772.62339843177</v>
+        <v>22453.72315312461</v>
       </c>
       <c r="D26">
-        <v>28729.58339843177</v>
+        <v>28695.37315312461</v>
       </c>
       <c r="E26">
-        <v>-2446.34</v>
+        <v>-2161.65</v>
       </c>
       <c r="F26">
-        <v>6832.559999999999</v>
+        <v>7117.25</v>
       </c>
       <c r="G26">
         <v>875.6</v>
@@ -3407,28 +3407,28 @@
         <v>1991.289795918367</v>
       </c>
       <c r="M26">
-        <v>1426.971529885941</v>
+        <v>1486.428676964522</v>
       </c>
       <c r="N26">
-        <v>564.3182660324264</v>
+        <v>504.8611189538453</v>
       </c>
       <c r="O26">
-        <v>197.5113931113492</v>
+        <v>176.7013916338458</v>
       </c>
       <c r="P26">
-        <v>366.8068729210772</v>
+        <v>328.1597273199995</v>
       </c>
       <c r="Q26">
-        <v>2335.006872921078</v>
+        <v>2296.35972732</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.2751388963638446</v>
+        <v>0.2773087694735462</v>
       </c>
       <c r="T26">
-        <v>1.126827354372099</v>
+        <v>1.137488748554659</v>
       </c>
       <c r="U26">
         <v>0.2088487374989669</v>
@@ -3445,7 +3445,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>1.395465679737516</v>
+        <v>1.339647052548015</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3453,22 +3453,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.2419194969487418</v>
+        <v>0.2421530296111228</v>
       </c>
       <c r="C27">
-        <v>22453.72315312461</v>
+        <v>22134.90428379297</v>
       </c>
       <c r="D27">
-        <v>28695.37315312461</v>
+        <v>28661.24428379298</v>
       </c>
       <c r="E27">
-        <v>-2161.65</v>
+        <v>-1876.959999999999</v>
       </c>
       <c r="F27">
-        <v>7117.25</v>
+        <v>7401.940000000001</v>
       </c>
       <c r="G27">
         <v>875.6</v>
@@ -3489,28 +3489,28 @@
         <v>1991.289795918367</v>
       </c>
       <c r="M27">
-        <v>1486.428676964522</v>
+        <v>1545.885824043103</v>
       </c>
       <c r="N27">
-        <v>504.8611189538453</v>
+        <v>445.4039718752645</v>
       </c>
       <c r="O27">
-        <v>176.7013916338458</v>
+        <v>155.8913901563425</v>
       </c>
       <c r="P27">
-        <v>328.1597273199995</v>
+        <v>289.5125817189219</v>
       </c>
       <c r="Q27">
-        <v>2296.35972732</v>
+        <v>2257.712581718922</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.2773087694735462</v>
+        <v>0.2795372878024289</v>
       </c>
       <c r="T27">
-        <v>1.137488748554659</v>
+        <v>1.148438288525937</v>
       </c>
       <c r="U27">
         <v>0.2088487374989669</v>
@@ -3527,7 +3527,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>1.339647052548015</v>
+        <v>1.288122165911553</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3535,22 +3535,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.2421530296111228</v>
+        <v>0.2474058622735038</v>
       </c>
       <c r="C28">
-        <v>22134.90428379297</v>
+        <v>21103.44671254971</v>
       </c>
       <c r="D28">
-        <v>28661.24428379298</v>
+        <v>27914.47671254972</v>
       </c>
       <c r="E28">
-        <v>-1876.959999999999</v>
+        <v>-1592.27</v>
       </c>
       <c r="F28">
-        <v>7401.940000000001</v>
+        <v>7686.63</v>
       </c>
       <c r="G28">
         <v>875.6</v>
@@ -3571,45 +3571,45 @@
         <v>1991.289795918367</v>
       </c>
       <c r="M28">
-        <v>1545.885824043103</v>
+        <v>1825.180589121684</v>
       </c>
       <c r="N28">
-        <v>445.4039718752645</v>
+        <v>166.1092067966838</v>
       </c>
       <c r="O28">
-        <v>155.8913901563425</v>
+        <v>58.13822237883932</v>
       </c>
       <c r="P28">
-        <v>289.5125817189219</v>
+        <v>107.9709844178445</v>
       </c>
       <c r="Q28">
-        <v>2257.712581718922</v>
+        <v>2076.170984417845</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.2795372878024289</v>
+        <v>0.2818268614279933</v>
       </c>
       <c r="T28">
-        <v>1.148438288525937</v>
+        <v>1.159687815893688</v>
       </c>
       <c r="U28">
-        <v>0.2088487374989669</v>
+        <v>0.2374487374989669</v>
       </c>
       <c r="V28">
         <v>0.35</v>
       </c>
       <c r="W28">
-        <v>0.1357516793743285</v>
+        <v>0.1543416793743285</v>
       </c>
       <c r="X28" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>Caa/CCC</t>
         </is>
       </c>
       <c r="Y28">
-        <v>1.288122165911553</v>
+        <v>1.091009737768808</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3617,22 +3617,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.2474058622735038</v>
+        <v>0.2478252949358848</v>
       </c>
       <c r="C29">
-        <v>21103.44671254971</v>
+        <v>20760.80236930654</v>
       </c>
       <c r="D29">
-        <v>27914.47671254972</v>
+        <v>27856.52236930654</v>
       </c>
       <c r="E29">
-        <v>-1592.27</v>
+        <v>-1307.579999999999</v>
       </c>
       <c r="F29">
-        <v>7686.63</v>
+        <v>7971.320000000001</v>
       </c>
       <c r="G29">
         <v>875.6</v>
@@ -3653,28 +3653,28 @@
         <v>1991.289795918367</v>
       </c>
       <c r="M29">
-        <v>1825.180589121684</v>
+        <v>1892.779870200265</v>
       </c>
       <c r="N29">
-        <v>166.1092067966838</v>
+        <v>98.50992571810275</v>
       </c>
       <c r="O29">
-        <v>58.13822237883932</v>
+        <v>34.47847400133596</v>
       </c>
       <c r="P29">
-        <v>107.9709844178445</v>
+        <v>64.03145171676678</v>
       </c>
       <c r="Q29">
-        <v>2076.170984417845</v>
+        <v>2032.231451716767</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.2818268614279933</v>
+        <v>0.2841800343209346</v>
       </c>
       <c r="T29">
-        <v>1.159687815893688</v>
+        <v>1.171249830132765</v>
       </c>
       <c r="U29">
         <v>0.2374487374989669</v>
@@ -3691,7 +3691,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>1.091009737768808</v>
+        <v>1.052045104277065</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3699,22 +3699,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.2478252949358848</v>
+        <v>0.2482447275982659</v>
       </c>
       <c r="C30">
-        <v>20760.80236930654</v>
+        <v>20418.39817007472</v>
       </c>
       <c r="D30">
-        <v>27856.52236930654</v>
+        <v>27798.80817007473</v>
       </c>
       <c r="E30">
-        <v>-1307.579999999999</v>
+        <v>-1022.889999999999</v>
       </c>
       <c r="F30">
-        <v>7971.320000000001</v>
+        <v>8256.01</v>
       </c>
       <c r="G30">
         <v>875.6</v>
@@ -3735,28 +3735,28 @@
         <v>1991.289795918367</v>
       </c>
       <c r="M30">
-        <v>1892.779870200265</v>
+        <v>1960.379151278845</v>
       </c>
       <c r="N30">
-        <v>98.50992571810275</v>
+        <v>30.91064463952193</v>
       </c>
       <c r="O30">
-        <v>34.47847400133596</v>
+        <v>10.81872562383268</v>
       </c>
       <c r="P30">
-        <v>64.03145171676678</v>
+        <v>20.09191901568926</v>
       </c>
       <c r="Q30">
-        <v>2032.231451716767</v>
+        <v>1988.291919015689</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.2841800343209346</v>
+        <v>0.2865994937742403</v>
       </c>
       <c r="T30">
-        <v>1.171249830132765</v>
+        <v>1.183137534913789</v>
       </c>
       <c r="U30">
         <v>0.2374487374989669</v>
@@ -3773,7 +3773,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>1.052045104277065</v>
+        <v>1.015767686888201</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3781,22 +3781,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.2482447275982659</v>
+        <v>0.2494766673643309</v>
       </c>
       <c r="C31">
-        <v>20418.39817007473</v>
+        <v>19965.56688184034</v>
       </c>
       <c r="D31">
-        <v>27798.80817007474</v>
+        <v>27630.66688184033</v>
       </c>
       <c r="E31">
-        <v>-1022.889999999999</v>
+        <v>-738.2000000000007</v>
       </c>
       <c r="F31">
-        <v>8256.01</v>
+        <v>8540.699999999999</v>
       </c>
       <c r="G31">
         <v>875.6</v>
@@ -3817,37 +3817,37 @@
         <v>1991.289795918367</v>
       </c>
       <c r="M31">
-        <v>1960.379151278845</v>
+        <v>2027.978432357426</v>
       </c>
       <c r="N31">
-        <v>30.91064463952193</v>
+        <v>-36.68863643905866</v>
       </c>
       <c r="O31">
-        <v>10.81872562383268</v>
+        <v>-12.84102275367053</v>
       </c>
       <c r="P31">
-        <v>20.09191901568926</v>
+        <v>-23.84761368538813</v>
       </c>
       <c r="Q31">
-        <v>1988.291919015689</v>
+        <v>1944.352386314612</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.2865994937742403</v>
+        <v>0.289604443901845</v>
       </c>
       <c r="T31">
-        <v>1.183137534913789</v>
+        <v>1.19790197328859</v>
       </c>
       <c r="U31">
         <v>0.2374487374989669</v>
       </c>
       <c r="V31">
-        <v>0.35</v>
+        <v>0.3436680673971747</v>
       </c>
       <c r="W31">
-        <v>0.1543416793743285</v>
+        <v>0.1558451887767979</v>
       </c>
       <c r="X31" t="inlineStr">
         <is>
@@ -3855,7 +3855,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>1.015767686888201</v>
+        <v>0.9819087639919277</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3863,22 +3863,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.2494766673643309</v>
+        <v>0.2513931547393206</v>
       </c>
       <c r="C32">
-        <v>19965.56688184034</v>
+        <v>19423.31079551448</v>
       </c>
       <c r="D32">
-        <v>27630.66688184033</v>
+        <v>27373.10079551448</v>
       </c>
       <c r="E32">
-        <v>-738.2000000000007</v>
+        <v>-453.5100000000002</v>
       </c>
       <c r="F32">
-        <v>8540.699999999999</v>
+        <v>8825.389999999999</v>
       </c>
       <c r="G32">
         <v>875.6</v>
@@ -3899,37 +3899,37 @@
         <v>1991.289795918367</v>
       </c>
       <c r="M32">
-        <v>2027.978432357426</v>
+        <v>2095.577713436007</v>
       </c>
       <c r="N32">
-        <v>-36.68863643905866</v>
+        <v>-104.2879175176395</v>
       </c>
       <c r="O32">
-        <v>-12.84102275367053</v>
+        <v>-36.50077113117381</v>
       </c>
       <c r="P32">
-        <v>-23.84761368538813</v>
+        <v>-67.78714638646565</v>
       </c>
       <c r="Q32">
-        <v>1944.352386314612</v>
+        <v>1900.412853613535</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.289604443901845</v>
+        <v>0.293137841639553</v>
       </c>
       <c r="T32">
-        <v>1.19790197328859</v>
+        <v>1.215262871452193</v>
       </c>
       <c r="U32">
         <v>0.2374487374989669</v>
       </c>
       <c r="V32">
-        <v>0.3436680673971747</v>
+        <v>0.3325820007069433</v>
       </c>
       <c r="W32">
-        <v>0.1558451887767979</v>
+        <v>0.1584775613162227</v>
       </c>
       <c r="X32" t="inlineStr">
         <is>
@@ -3937,7 +3937,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>0.9819087639919277</v>
+        <v>0.9502342877341237</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3945,22 +3945,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.2513931547393206</v>
+        <v>0.2533096421143102</v>
       </c>
       <c r="C33">
-        <v>19423.31079551448</v>
+        <v>18885.81229199432</v>
       </c>
       <c r="D33">
-        <v>27373.10079551448</v>
+        <v>27120.29229199432</v>
       </c>
       <c r="E33">
-        <v>-453.5100000000002</v>
+        <v>-168.8199999999997</v>
       </c>
       <c r="F33">
-        <v>8825.389999999999</v>
+        <v>9110.08</v>
       </c>
       <c r="G33">
         <v>875.6</v>
@@ -3981,37 +3981,37 @@
         <v>1991.289795918367</v>
       </c>
       <c r="M33">
-        <v>2095.577713436007</v>
+        <v>2163.176994514588</v>
       </c>
       <c r="N33">
-        <v>-104.2879175176395</v>
+        <v>-171.8871985962205</v>
       </c>
       <c r="O33">
-        <v>-36.50077113117381</v>
+        <v>-60.16051950867718</v>
       </c>
       <c r="P33">
-        <v>-67.78714638646565</v>
+        <v>-111.7266790875433</v>
       </c>
       <c r="Q33">
-        <v>1900.412853613535</v>
+        <v>1856.473320912457</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.293137841639553</v>
+        <v>0.2967751628401346</v>
       </c>
       <c r="T33">
-        <v>1.215262871452193</v>
+        <v>1.233134384267666</v>
       </c>
       <c r="U33">
         <v>0.2374487374989669</v>
       </c>
       <c r="V33">
-        <v>0.3325820007069433</v>
+        <v>0.3221888131848513</v>
       </c>
       <c r="W33">
-        <v>0.1584775613162227</v>
+        <v>0.1609454105719334</v>
       </c>
       <c r="X33" t="inlineStr">
         <is>
@@ -4019,7 +4019,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>0.9502342877341237</v>
+        <v>0.9205394662424322</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4027,22 +4027,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.2533096421143102</v>
+        <v>0.2552261294892999</v>
       </c>
       <c r="C34">
-        <v>18885.81229199432</v>
+        <v>18352.94075939195</v>
       </c>
       <c r="D34">
-        <v>27120.29229199432</v>
+        <v>26872.11075939195</v>
       </c>
       <c r="E34">
-        <v>-168.8199999999997</v>
+        <v>115.8700000000008</v>
       </c>
       <c r="F34">
-        <v>9110.08</v>
+        <v>9394.77</v>
       </c>
       <c r="G34">
         <v>875.6</v>
@@ -4063,37 +4063,37 @@
         <v>1991.289795918367</v>
       </c>
       <c r="M34">
-        <v>2163.176994514588</v>
+        <v>2230.776275593169</v>
       </c>
       <c r="N34">
-        <v>-171.8871985962205</v>
+        <v>-239.4864796748016</v>
       </c>
       <c r="O34">
-        <v>-60.16051950867718</v>
+        <v>-83.82026788618055</v>
       </c>
       <c r="P34">
-        <v>-111.7266790875433</v>
+        <v>-155.666211788621</v>
       </c>
       <c r="Q34">
-        <v>1856.473320912457</v>
+        <v>1812.533788211379</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.2967751628401346</v>
+        <v>0.3005210607929725</v>
       </c>
       <c r="T34">
-        <v>1.233134384267666</v>
+        <v>1.251539375077632</v>
       </c>
       <c r="U34">
         <v>0.2374487374989669</v>
       </c>
       <c r="V34">
-        <v>0.3221888131848513</v>
+        <v>0.3124255158156133</v>
       </c>
       <c r="W34">
-        <v>0.1609454105719334</v>
+        <v>0.163263693206086</v>
       </c>
       <c r="X34" t="inlineStr">
         <is>
@@ -4101,7 +4101,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>0.9205394662424322</v>
+        <v>0.8926443309017523</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4109,22 +4109,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.2552261294892999</v>
+        <v>0.2571426168642896</v>
       </c>
       <c r="C35">
-        <v>18352.94075939195</v>
+        <v>17824.57032345427</v>
       </c>
       <c r="D35">
-        <v>26872.11075939195</v>
+        <v>26628.43032345427</v>
       </c>
       <c r="E35">
-        <v>115.8700000000008</v>
+        <v>400.5600000000013</v>
       </c>
       <c r="F35">
-        <v>9394.77</v>
+        <v>9679.460000000001</v>
       </c>
       <c r="G35">
         <v>875.6</v>
@@ -4145,37 +4145,37 @@
         <v>1991.289795918367</v>
       </c>
       <c r="M35">
-        <v>2230.776275593169</v>
+        <v>2298.37555667175</v>
       </c>
       <c r="N35">
-        <v>-239.4864796748016</v>
+        <v>-307.0857607533826</v>
       </c>
       <c r="O35">
-        <v>-83.82026788618055</v>
+        <v>-107.4800162636839</v>
       </c>
       <c r="P35">
-        <v>-155.666211788621</v>
+        <v>-199.6057444896987</v>
       </c>
       <c r="Q35">
-        <v>1812.533788211379</v>
+        <v>1768.594255510302</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.3005210607929725</v>
+        <v>0.3043804708049872</v>
       </c>
       <c r="T35">
-        <v>1.251539375077632</v>
+        <v>1.270502092881838</v>
       </c>
       <c r="U35">
         <v>0.2374487374989669</v>
       </c>
       <c r="V35">
-        <v>0.3124255158156133</v>
+        <v>0.3032365300563306</v>
       </c>
       <c r="W35">
-        <v>0.163263693206086</v>
+        <v>0.1654456062735236</v>
       </c>
       <c r="X35" t="inlineStr">
         <is>
@@ -4183,7 +4183,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>0.8926443309017523</v>
+        <v>0.8663900858752301</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4191,22 +4191,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.2571426168642896</v>
+        <v>0.2590591042392792</v>
       </c>
       <c r="C36">
-        <v>17824.57032345427</v>
+        <v>17300.5796346854</v>
       </c>
       <c r="D36">
-        <v>26628.43032345427</v>
+        <v>26389.1296346854</v>
       </c>
       <c r="E36">
-        <v>400.5600000000013</v>
+        <v>685.2500000000018</v>
       </c>
       <c r="F36">
-        <v>9679.460000000001</v>
+        <v>9964.150000000001</v>
       </c>
       <c r="G36">
         <v>875.6</v>
@@ -4227,37 +4227,37 @@
         <v>1991.289795918367</v>
       </c>
       <c r="M36">
-        <v>2298.37555667175</v>
+        <v>2365.974837750331</v>
       </c>
       <c r="N36">
-        <v>-307.0857607533826</v>
+        <v>-374.6850418319636</v>
       </c>
       <c r="O36">
-        <v>-107.4800162636839</v>
+        <v>-131.1397646411873</v>
       </c>
       <c r="P36">
-        <v>-199.6057444896987</v>
+        <v>-243.5452771907764</v>
       </c>
       <c r="Q36">
-        <v>1768.594255510302</v>
+        <v>1724.654722809224</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.3043804708049872</v>
+        <v>0.3083586318942947</v>
       </c>
       <c r="T36">
-        <v>1.270502092881838</v>
+        <v>1.290048278926174</v>
       </c>
       <c r="U36">
         <v>0.2374487374989669</v>
       </c>
       <c r="V36">
-        <v>0.3032365300563306</v>
+        <v>0.2945726291975782</v>
       </c>
       <c r="W36">
-        <v>0.1654456062735236</v>
+        <v>0.1675028385942506</v>
       </c>
       <c r="X36" t="inlineStr">
         <is>
@@ -4265,7 +4265,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>0.8663900858752301</v>
+        <v>0.8416360834216521</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4273,22 +4273,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.2590591042392792</v>
+        <v>0.2609755916142689</v>
       </c>
       <c r="C37">
-        <v>17300.5796346854</v>
+        <v>16780.85166684515</v>
       </c>
       <c r="D37">
-        <v>26389.1296346854</v>
+        <v>26154.09166684515</v>
       </c>
       <c r="E37">
-        <v>685.2500000000018</v>
+        <v>969.9400000000023</v>
       </c>
       <c r="F37">
-        <v>9964.150000000001</v>
+        <v>10248.84</v>
       </c>
       <c r="G37">
         <v>875.6</v>
@@ -4309,37 +4309,37 @@
         <v>1991.289795918367</v>
       </c>
       <c r="M37">
-        <v>2365.974837750331</v>
+        <v>2433.574118828912</v>
       </c>
       <c r="N37">
-        <v>-374.6850418319636</v>
+        <v>-442.2843229105447</v>
       </c>
       <c r="O37">
-        <v>-131.1397646411873</v>
+        <v>-154.7995130186906</v>
       </c>
       <c r="P37">
-        <v>-243.5452771907764</v>
+        <v>-287.4848098918541</v>
       </c>
       <c r="Q37">
-        <v>1724.654722809224</v>
+        <v>1680.715190108146</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.3083586318942947</v>
+        <v>0.3124611105176431</v>
       </c>
       <c r="T37">
-        <v>1.290048278926174</v>
+        <v>1.310205283284396</v>
       </c>
       <c r="U37">
         <v>0.2374487374989669</v>
       </c>
       <c r="V37">
-        <v>0.2945726291975782</v>
+        <v>0.2863900561643121</v>
       </c>
       <c r="W37">
-        <v>0.1675028385942506</v>
+        <v>0.1694457802304927</v>
       </c>
       <c r="X37" t="inlineStr">
         <is>
@@ -4347,7 +4347,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>0.8416360834216521</v>
+        <v>0.8182573033266062</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4355,22 +4355,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.2609755916142689</v>
+        <v>0.2754086394770743</v>
       </c>
       <c r="C38">
-        <v>16780.85166684515</v>
+        <v>14852.13268912254</v>
       </c>
       <c r="D38">
-        <v>26154.09166684515</v>
+        <v>24510.06268912254</v>
       </c>
       <c r="E38">
-        <v>969.9400000000005</v>
+        <v>1254.630000000001</v>
       </c>
       <c r="F38">
-        <v>10248.84</v>
+        <v>10533.53</v>
       </c>
       <c r="G38">
         <v>875.6</v>
@@ -4391,45 +4391,45 @@
         <v>1991.289795918367</v>
       </c>
       <c r="M38">
-        <v>2433.574118828912</v>
+        <v>2798.218945907493</v>
       </c>
       <c r="N38">
-        <v>-442.2843229105442</v>
+        <v>-806.9291499891251</v>
       </c>
       <c r="O38">
-        <v>-154.7995130186905</v>
+        <v>-282.4252024961938</v>
       </c>
       <c r="P38">
-        <v>-287.4848098918537</v>
+        <v>-524.5039474929313</v>
       </c>
       <c r="Q38">
-        <v>1680.715190108147</v>
+        <v>1443.696052507069</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.3124611105176431</v>
+        <v>0.3199994781255671</v>
       </c>
       <c r="T38">
-        <v>1.310205283284396</v>
+        <v>1.347244089010769</v>
       </c>
       <c r="U38">
-        <v>0.2374487374989669</v>
+        <v>0.2656487374989668</v>
       </c>
       <c r="V38">
-        <v>0.2863900561643122</v>
+        <v>0.2490696553930306</v>
       </c>
       <c r="W38">
-        <v>0.1694457802304927</v>
+        <v>0.1994836979945055</v>
       </c>
       <c r="X38" t="inlineStr">
         <is>
-          <t>Caa/CCC</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y38">
-        <v>0.8182573033266063</v>
+        <v>0.7116275868372304</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4437,22 +4437,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.2754086394770743</v>
+        <v>0.277607126852064</v>
       </c>
       <c r="C39">
-        <v>14852.13268912254</v>
+        <v>14334.9862322655</v>
       </c>
       <c r="D39">
-        <v>24510.06268912254</v>
+        <v>24277.6062322655</v>
       </c>
       <c r="E39">
-        <v>1254.630000000001</v>
+        <v>1539.32</v>
       </c>
       <c r="F39">
-        <v>10533.53</v>
+        <v>10818.22</v>
       </c>
       <c r="G39">
         <v>875.6</v>
@@ -4473,37 +4473,37 @@
         <v>1991.289795918367</v>
       </c>
       <c r="M39">
-        <v>2798.218945907493</v>
+        <v>2873.846484986073</v>
       </c>
       <c r="N39">
-        <v>-806.9291499891251</v>
+        <v>-882.5566890677055</v>
       </c>
       <c r="O39">
-        <v>-282.4252024961938</v>
+        <v>-308.8948411736969</v>
       </c>
       <c r="P39">
-        <v>-524.5039474929313</v>
+        <v>-573.6618478940086</v>
       </c>
       <c r="Q39">
-        <v>1443.696052507069</v>
+        <v>1394.538152105992</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.3199994781255671</v>
+        <v>0.3244220503533988</v>
       </c>
       <c r="T39">
-        <v>1.347244089010769</v>
+        <v>1.36897383238191</v>
       </c>
       <c r="U39">
         <v>0.2656487374989668</v>
       </c>
       <c r="V39">
-        <v>0.2490696553930306</v>
+        <v>0.2425151907774246</v>
       </c>
       <c r="W39">
-        <v>0.1994836979945055</v>
+        <v>0.2012248832446229</v>
       </c>
       <c r="X39" t="inlineStr">
         <is>
@@ -4511,7 +4511,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>0.7116275868372304</v>
+        <v>0.6929005450783561</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4519,22 +4519,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.277607126852064</v>
+        <v>0.2798056142270536</v>
       </c>
       <c r="C40">
-        <v>14334.9862322655</v>
+        <v>13822.20764143017</v>
       </c>
       <c r="D40">
-        <v>24277.6062322655</v>
+        <v>24049.51764143017</v>
       </c>
       <c r="E40">
-        <v>1539.32</v>
+        <v>1824.01</v>
       </c>
       <c r="F40">
-        <v>10818.22</v>
+        <v>11102.91</v>
       </c>
       <c r="G40">
         <v>875.6</v>
@@ -4555,37 +4555,37 @@
         <v>1991.289795918367</v>
       </c>
       <c r="M40">
-        <v>2873.846484986073</v>
+        <v>2949.474024064654</v>
       </c>
       <c r="N40">
-        <v>-882.5566890677055</v>
+        <v>-958.1842281462864</v>
       </c>
       <c r="O40">
-        <v>-308.8948411736969</v>
+        <v>-335.3644798512002</v>
       </c>
       <c r="P40">
-        <v>-573.6618478940086</v>
+        <v>-622.8197482950861</v>
       </c>
       <c r="Q40">
-        <v>1394.538152105992</v>
+        <v>1345.380251704914</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.3244220503533988</v>
+        <v>0.3289896249493561</v>
       </c>
       <c r="T40">
-        <v>1.36897383238191</v>
+        <v>1.391416026355384</v>
       </c>
       <c r="U40">
         <v>0.2656487374989668</v>
       </c>
       <c r="V40">
-        <v>0.2425151907774246</v>
+        <v>0.2362968525523624</v>
       </c>
       <c r="W40">
-        <v>0.2012248832446229</v>
+        <v>0.2028767769434522</v>
       </c>
       <c r="X40" t="inlineStr">
         <is>
@@ -4593,7 +4593,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>0.6929005450783561</v>
+        <v>0.6751338644353213</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4601,22 +4601,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.2798056142270536</v>
+        <v>0.2820041016020433</v>
       </c>
       <c r="C41">
-        <v>13822.20764143017</v>
+        <v>13313.67495389566</v>
       </c>
       <c r="D41">
-        <v>24049.51764143017</v>
+        <v>23825.67495389566</v>
       </c>
       <c r="E41">
-        <v>1824.01</v>
+        <v>2108.700000000001</v>
       </c>
       <c r="F41">
-        <v>11102.91</v>
+        <v>11387.6</v>
       </c>
       <c r="G41">
         <v>875.6</v>
@@ -4637,37 +4637,37 @@
         <v>1991.289795918367</v>
       </c>
       <c r="M41">
-        <v>2949.474024064654</v>
+        <v>3025.101563143235</v>
       </c>
       <c r="N41">
-        <v>-958.1842281462864</v>
+        <v>-1033.811767224867</v>
       </c>
       <c r="O41">
-        <v>-335.3644798512002</v>
+        <v>-361.8341185287035</v>
       </c>
       <c r="P41">
-        <v>-622.8197482950861</v>
+        <v>-671.9776486961637</v>
       </c>
       <c r="Q41">
-        <v>1345.380251704914</v>
+        <v>1296.222351303837</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.3289896249493561</v>
+        <v>0.3337094520318454</v>
       </c>
       <c r="T41">
-        <v>1.391416026355384</v>
+        <v>1.414606293461307</v>
       </c>
       <c r="U41">
         <v>0.2656487374989668</v>
       </c>
       <c r="V41">
-        <v>0.2362968525523624</v>
+        <v>0.2303894312385534</v>
       </c>
       <c r="W41">
-        <v>0.2028767769434522</v>
+        <v>0.2044460759573401</v>
       </c>
       <c r="X41" t="inlineStr">
         <is>
@@ -4675,7 +4675,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>0.6751338644353213</v>
+        <v>0.6582555178244383</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4683,22 +4683,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.2820041016020433</v>
+        <v>0.3093049579280098</v>
       </c>
       <c r="C42">
-        <v>13313.67495389566</v>
+        <v>10560.48745806033</v>
       </c>
       <c r="D42">
-        <v>23825.67495389566</v>
+        <v>21357.17745806033</v>
       </c>
       <c r="E42">
-        <v>2108.700000000001</v>
+        <v>2393.390000000001</v>
       </c>
       <c r="F42">
-        <v>11387.6</v>
+        <v>11672.29</v>
       </c>
       <c r="G42">
         <v>875.6</v>
@@ -4719,45 +4719,45 @@
         <v>1991.289795918367</v>
       </c>
       <c r="M42">
-        <v>3025.101563143235</v>
+        <v>3731.032762221816</v>
       </c>
       <c r="N42">
-        <v>-1033.811767224867</v>
+        <v>-1739.742966303449</v>
       </c>
       <c r="O42">
-        <v>-361.8341185287035</v>
+        <v>-608.9100382062071</v>
       </c>
       <c r="P42">
-        <v>-671.9776486961637</v>
+        <v>-1130.832928097242</v>
       </c>
       <c r="Q42">
-        <v>1296.222351303837</v>
+        <v>837.3670719027582</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.3337094520318454</v>
+        <v>0.3436102375764136</v>
       </c>
       <c r="T42">
-        <v>1.414606293461307</v>
+        <v>1.463252537767339</v>
       </c>
       <c r="U42">
-        <v>0.2656487374989668</v>
+        <v>0.3196487374989669</v>
       </c>
       <c r="V42">
-        <v>0.2303894312385534</v>
+        <v>0.1867985281792049</v>
       </c>
       <c r="W42">
-        <v>0.2044460759573401</v>
+        <v>0.2599388237998189</v>
       </c>
       <c r="X42" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y42">
-        <v>0.6582555178244383</v>
+        <v>0.5337100805120139</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4765,22 +4765,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.3093049579280098</v>
+        <v>0.3120434453029994</v>
       </c>
       <c r="C43">
-        <v>10560.48745806033</v>
+        <v>10056.12496708971</v>
       </c>
       <c r="D43">
-        <v>21357.17745806033</v>
+        <v>21137.50496708971</v>
       </c>
       <c r="E43">
-        <v>2393.390000000001</v>
+        <v>2678.080000000002</v>
       </c>
       <c r="F43">
-        <v>11672.29</v>
+        <v>11956.98</v>
       </c>
       <c r="G43">
         <v>875.6</v>
@@ -4801,37 +4801,37 @@
         <v>1991.289795918367</v>
       </c>
       <c r="M43">
-        <v>3731.032762221816</v>
+        <v>3822.033561300398</v>
       </c>
       <c r="N43">
-        <v>-1739.742966303449</v>
+        <v>-1830.74376538203</v>
       </c>
       <c r="O43">
-        <v>-608.9100382062071</v>
+        <v>-640.7603178837105</v>
       </c>
       <c r="P43">
-        <v>-1130.832928097242</v>
+        <v>-1189.98344749832</v>
       </c>
       <c r="Q43">
-        <v>837.3670719027582</v>
+        <v>778.2165525016806</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.3436102375764136</v>
+        <v>0.3487448968449725</v>
       </c>
       <c r="T43">
-        <v>1.463252537767339</v>
+        <v>1.488481029797811</v>
       </c>
       <c r="U43">
         <v>0.3196487374989669</v>
       </c>
       <c r="V43">
-        <v>0.1867985281792049</v>
+        <v>0.1823509441749381</v>
       </c>
       <c r="W43">
-        <v>0.2599388237998189</v>
+        <v>0.2613604884117033</v>
       </c>
       <c r="X43" t="inlineStr">
         <is>
@@ -4839,7 +4839,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>0.5337100805120139</v>
+        <v>0.5210026976426803</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4847,22 +4847,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.3120434453029994</v>
+        <v>0.3147819326779892</v>
       </c>
       <c r="C44">
-        <v>10056.12496708971</v>
+        <v>9556.235418499748</v>
       </c>
       <c r="D44">
-        <v>21137.50496708971</v>
+        <v>20922.30541849975</v>
       </c>
       <c r="E44">
-        <v>2678.08</v>
+        <v>2962.77</v>
       </c>
       <c r="F44">
-        <v>11956.98</v>
+        <v>12241.67</v>
       </c>
       <c r="G44">
         <v>875.6</v>
@@ -4883,37 +4883,37 @@
         <v>1991.289795918367</v>
       </c>
       <c r="M44">
-        <v>3822.033561300397</v>
+        <v>3913.034360378978</v>
       </c>
       <c r="N44">
-        <v>-1830.743765382029</v>
+        <v>-1921.74456446061</v>
       </c>
       <c r="O44">
-        <v>-640.7603178837102</v>
+        <v>-672.6105975612136</v>
       </c>
       <c r="P44">
-        <v>-1189.983447498319</v>
+        <v>-1249.133966899397</v>
       </c>
       <c r="Q44">
-        <v>778.2165525016812</v>
+        <v>719.0660331006034</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.3487448968449725</v>
+        <v>0.3540597195966387</v>
       </c>
       <c r="T44">
-        <v>1.488481029797811</v>
+        <v>1.514594732074965</v>
       </c>
       <c r="U44">
         <v>0.3196487374989669</v>
       </c>
       <c r="V44">
-        <v>0.1823509441749381</v>
+        <v>0.1781102245429628</v>
       </c>
       <c r="W44">
-        <v>0.2613604884117033</v>
+        <v>0.2627160290881513</v>
       </c>
       <c r="X44" t="inlineStr">
         <is>
@@ -4921,7 +4921,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>0.5210026976426804</v>
+        <v>0.5088863558370366</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4929,22 +4929,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.3147819326779892</v>
+        <v>0.3175204200529788</v>
       </c>
       <c r="C45">
-        <v>9556.235418499748</v>
+        <v>9060.683572956201</v>
       </c>
       <c r="D45">
-        <v>20922.30541849975</v>
+        <v>20711.4435729562</v>
       </c>
       <c r="E45">
-        <v>2962.77</v>
+        <v>3247.460000000001</v>
       </c>
       <c r="F45">
-        <v>12241.67</v>
+        <v>12526.36</v>
       </c>
       <c r="G45">
         <v>875.6</v>
@@ -4965,37 +4965,37 @@
         <v>1991.289795918367</v>
       </c>
       <c r="M45">
-        <v>3913.034360378978</v>
+        <v>4004.035159457559</v>
       </c>
       <c r="N45">
-        <v>-1921.74456446061</v>
+        <v>-2012.745363539192</v>
       </c>
       <c r="O45">
-        <v>-672.6105975612136</v>
+        <v>-704.460877238717</v>
       </c>
       <c r="P45">
-        <v>-1249.133966899397</v>
+        <v>-1308.284486300475</v>
       </c>
       <c r="Q45">
-        <v>719.0660331006034</v>
+        <v>659.9155136995255</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.3540597195966387</v>
+        <v>0.3595643574465786</v>
       </c>
       <c r="T45">
-        <v>1.514594732074965</v>
+        <v>1.541641066576304</v>
       </c>
       <c r="U45">
         <v>0.3196487374989669</v>
       </c>
       <c r="V45">
-        <v>0.1781102245429628</v>
+        <v>0.1740622648942591</v>
       </c>
       <c r="W45">
-        <v>0.2627160290881513</v>
+        <v>0.2640099542793062</v>
       </c>
       <c r="X45" t="inlineStr">
         <is>
@@ -5003,7 +5003,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>0.5088863558370366</v>
+        <v>0.4973207568407403</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5011,22 +5011,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.3175204200529788</v>
+        <v>0.3202589074279685</v>
       </c>
       <c r="C46">
-        <v>9060.683572956201</v>
+        <v>8569.339588671728</v>
       </c>
       <c r="D46">
-        <v>20711.4435729562</v>
+        <v>20504.78958867173</v>
       </c>
       <c r="E46">
-        <v>3247.460000000001</v>
+        <v>3532.150000000001</v>
       </c>
       <c r="F46">
-        <v>12526.36</v>
+        <v>12811.05</v>
       </c>
       <c r="G46">
         <v>875.6</v>
@@ -5047,37 +5047,37 @@
         <v>1991.289795918367</v>
       </c>
       <c r="M46">
-        <v>4004.035159457559</v>
+        <v>4095.03595853614</v>
       </c>
       <c r="N46">
-        <v>-2012.745363539192</v>
+        <v>-2103.746162617773</v>
       </c>
       <c r="O46">
-        <v>-704.460877238717</v>
+        <v>-736.3111569162204</v>
       </c>
       <c r="P46">
-        <v>-1308.284486300475</v>
+        <v>-1367.435005701552</v>
       </c>
       <c r="Q46">
-        <v>659.9155136995255</v>
+        <v>600.7649942984478</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.3595643574465786</v>
+        <v>0.3652691639456074</v>
       </c>
       <c r="T46">
-        <v>1.541641066576304</v>
+        <v>1.569670904150419</v>
       </c>
       <c r="U46">
         <v>0.3196487374989669</v>
       </c>
       <c r="V46">
-        <v>0.1740622648942591</v>
+        <v>0.1701942145632755</v>
       </c>
       <c r="W46">
-        <v>0.2640099542793062</v>
+        <v>0.2652463716841876</v>
       </c>
       <c r="X46" t="inlineStr">
         <is>
@@ -5085,7 +5085,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>0.4973207568407403</v>
+        <v>0.4862691844665016</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5093,22 +5093,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.3202589074279685</v>
+        <v>0.3229973948029581</v>
       </c>
       <c r="C47">
-        <v>8569.339588671728</v>
+        <v>8082.078754788852</v>
       </c>
       <c r="D47">
-        <v>20504.78958867173</v>
+        <v>20302.21875478885</v>
       </c>
       <c r="E47">
-        <v>3532.150000000001</v>
+        <v>3816.84</v>
       </c>
       <c r="F47">
-        <v>12811.05</v>
+        <v>13095.74</v>
       </c>
       <c r="G47">
         <v>875.6</v>
@@ -5129,37 +5129,37 @@
         <v>1991.289795918367</v>
       </c>
       <c r="M47">
-        <v>4095.03595853614</v>
+        <v>4186.036757614721</v>
       </c>
       <c r="N47">
-        <v>-2103.746162617773</v>
+        <v>-2194.746961696354</v>
       </c>
       <c r="O47">
-        <v>-736.3111569162204</v>
+        <v>-768.1614365937237</v>
       </c>
       <c r="P47">
-        <v>-1367.435005701552</v>
+        <v>-1426.58552510263</v>
       </c>
       <c r="Q47">
-        <v>600.7649942984478</v>
+        <v>541.6144748973704</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.3652691639456074</v>
+        <v>0.3711852595742297</v>
       </c>
       <c r="T47">
-        <v>1.569670904150419</v>
+        <v>1.598738883856908</v>
       </c>
       <c r="U47">
         <v>0.3196487374989669</v>
       </c>
       <c r="V47">
-        <v>0.1701942145632755</v>
+        <v>0.1664943403336391</v>
       </c>
       <c r="W47">
-        <v>0.2652463716841876</v>
+        <v>0.2664290318105959</v>
       </c>
       <c r="X47" t="inlineStr">
         <is>
@@ -5167,7 +5167,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>0.4862691844665016</v>
+        <v>0.475698115238969</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5175,22 +5175,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.3229973948029581</v>
+        <v>0.3257358821779478</v>
       </c>
       <c r="C48">
-        <v>8082.078754788852</v>
+        <v>7598.781240411947</v>
       </c>
       <c r="D48">
-        <v>20302.21875478885</v>
+        <v>20103.61124041195</v>
       </c>
       <c r="E48">
-        <v>3816.84</v>
+        <v>4101.530000000001</v>
       </c>
       <c r="F48">
-        <v>13095.74</v>
+        <v>13380.43</v>
       </c>
       <c r="G48">
         <v>875.6</v>
@@ -5211,37 +5211,37 @@
         <v>1991.289795918367</v>
       </c>
       <c r="M48">
-        <v>4186.036757614721</v>
+        <v>4277.037556693302</v>
       </c>
       <c r="N48">
-        <v>-2194.746961696354</v>
+        <v>-2285.747760774934</v>
       </c>
       <c r="O48">
-        <v>-768.1614365937237</v>
+        <v>-800.011716271227</v>
       </c>
       <c r="P48">
-        <v>-1426.58552510263</v>
+        <v>-1485.736044503707</v>
       </c>
       <c r="Q48">
-        <v>541.6144748973704</v>
+        <v>482.463955496293</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.3711852595742297</v>
+        <v>0.3773246040944982</v>
       </c>
       <c r="T48">
-        <v>1.598738883856908</v>
+        <v>1.628903768457982</v>
       </c>
       <c r="U48">
         <v>0.3196487374989669</v>
       </c>
       <c r="V48">
-        <v>0.1664943403336391</v>
+        <v>0.162951907560583</v>
       </c>
       <c r="W48">
-        <v>0.2664290318105959</v>
+        <v>0.2675613659741782</v>
       </c>
       <c r="X48" t="inlineStr">
         <is>
@@ -5249,7 +5249,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>0.475698115238969</v>
+        <v>0.4655768787445228</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5257,22 +5257,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.3257358821779478</v>
+        <v>0.3284743695529375</v>
       </c>
       <c r="C49">
-        <v>7598.781240411947</v>
+        <v>7119.331858227286</v>
       </c>
       <c r="D49">
-        <v>20103.61124041195</v>
+        <v>19908.85185822729</v>
       </c>
       <c r="E49">
-        <v>4101.530000000001</v>
+        <v>4386.220000000001</v>
       </c>
       <c r="F49">
-        <v>13380.43</v>
+        <v>13665.12</v>
       </c>
       <c r="G49">
         <v>875.6</v>
@@ -5293,37 +5293,37 @@
         <v>1991.289795918367</v>
       </c>
       <c r="M49">
-        <v>4277.037556693302</v>
+        <v>4368.038355771882</v>
       </c>
       <c r="N49">
-        <v>-2285.747760774934</v>
+        <v>-2376.748559853515</v>
       </c>
       <c r="O49">
-        <v>-800.011716271227</v>
+        <v>-831.8619959487302</v>
       </c>
       <c r="P49">
-        <v>-1485.736044503707</v>
+        <v>-1544.886563904785</v>
       </c>
       <c r="Q49">
-        <v>482.463955496293</v>
+        <v>423.3134360952154</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.3773246040944982</v>
+        <v>0.3837000772501616</v>
       </c>
       <c r="T49">
-        <v>1.628903768457982</v>
+        <v>1.660228840928327</v>
       </c>
       <c r="U49">
         <v>0.3196487374989669</v>
       </c>
       <c r="V49">
-        <v>0.162951907560583</v>
+        <v>0.1595570761530708</v>
       </c>
       <c r="W49">
-        <v>0.2675613659741782</v>
+        <v>0.2686465195476113</v>
       </c>
       <c r="X49" t="inlineStr">
         <is>
@@ -5331,7 +5331,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>0.4655768787445228</v>
+        <v>0.4558773604373453</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5339,22 +5339,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.3284743695529374</v>
+        <v>0.3312128569279271</v>
       </c>
       <c r="C50">
-        <v>7119.331858227295</v>
+        <v>6643.619841731159</v>
       </c>
       <c r="D50">
-        <v>19908.8518582273</v>
+        <v>19717.82984173116</v>
       </c>
       <c r="E50">
-        <v>4386.219999999999</v>
+        <v>4670.91</v>
       </c>
       <c r="F50">
-        <v>13665.12</v>
+        <v>13949.81</v>
       </c>
       <c r="G50">
         <v>875.6</v>
@@ -5375,37 +5375,37 @@
         <v>1991.289795918367</v>
       </c>
       <c r="M50">
-        <v>4368.038355771882</v>
+        <v>4459.039154850463</v>
       </c>
       <c r="N50">
-        <v>-2376.748559853515</v>
+        <v>-2467.749358932096</v>
       </c>
       <c r="O50">
-        <v>-831.8619959487302</v>
+        <v>-863.7122756262335</v>
       </c>
       <c r="P50">
-        <v>-1544.886563904785</v>
+        <v>-1604.037083305862</v>
       </c>
       <c r="Q50">
-        <v>423.3134360952154</v>
+        <v>364.1629166941379</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.3837000772501616</v>
+        <v>0.3903255689609491</v>
       </c>
       <c r="T50">
-        <v>1.660228840928327</v>
+        <v>1.692782347613196</v>
       </c>
       <c r="U50">
         <v>0.3196487374989669</v>
       </c>
       <c r="V50">
-        <v>0.1595570761530708</v>
+        <v>0.1563008092928041</v>
       </c>
       <c r="W50">
-        <v>0.2686465195476113</v>
+        <v>0.2696873811384553</v>
       </c>
       <c r="X50" t="inlineStr">
         <is>
@@ -5413,7 +5413,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>0.4558773604373453</v>
+        <v>0.4465737408365832</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5421,22 +5421,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.3312128569279271</v>
+        <v>0.3339513443029168</v>
       </c>
       <c r="C51">
-        <v>6643.619841731159</v>
+        <v>6171.538635160865</v>
       </c>
       <c r="D51">
-        <v>19717.82984173116</v>
+        <v>19530.43863516087</v>
       </c>
       <c r="E51">
-        <v>4670.91</v>
+        <v>4955.6</v>
       </c>
       <c r="F51">
-        <v>13949.81</v>
+        <v>14234.5</v>
       </c>
       <c r="G51">
         <v>875.6</v>
@@ -5457,37 +5457,37 @@
         <v>1991.289795918367</v>
       </c>
       <c r="M51">
-        <v>4459.039154850463</v>
+        <v>4550.039953929044</v>
       </c>
       <c r="N51">
-        <v>-2467.749358932096</v>
+        <v>-2558.750158010676</v>
       </c>
       <c r="O51">
-        <v>-863.7122756262335</v>
+        <v>-895.5625553037366</v>
       </c>
       <c r="P51">
-        <v>-1604.037083305862</v>
+        <v>-1663.18760270694</v>
       </c>
       <c r="Q51">
-        <v>364.1629166941379</v>
+        <v>305.0123972930605</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.3903255689609491</v>
+        <v>0.3972160803401681</v>
       </c>
       <c r="T51">
-        <v>1.692782347613196</v>
+        <v>1.72663799456546</v>
       </c>
       <c r="U51">
         <v>0.3196487374989669</v>
       </c>
       <c r="V51">
-        <v>0.1563008092928041</v>
+        <v>0.153174793106948</v>
       </c>
       <c r="W51">
-        <v>0.2696873811384553</v>
+        <v>0.2706866082656655</v>
       </c>
       <c r="X51" t="inlineStr">
         <is>
@@ -5495,7 +5495,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>0.4465737408365832</v>
+        <v>0.4376422660198515</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5503,22 +5503,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.3339513443029168</v>
+        <v>0.3366898316779066</v>
       </c>
       <c r="C52">
-        <v>6171.538635160865</v>
+        <v>5702.985695291516</v>
       </c>
       <c r="D52">
-        <v>19530.43863516087</v>
+        <v>19346.57569529152</v>
       </c>
       <c r="E52">
-        <v>4955.6</v>
+        <v>5240.290000000001</v>
       </c>
       <c r="F52">
-        <v>14234.5</v>
+        <v>14519.19</v>
       </c>
       <c r="G52">
         <v>875.6</v>
@@ -5539,37 +5539,37 @@
         <v>1991.289795918367</v>
       </c>
       <c r="M52">
-        <v>4550.039953929044</v>
+        <v>4641.040753007625</v>
       </c>
       <c r="N52">
-        <v>-2558.750158010676</v>
+        <v>-2649.750957089258</v>
       </c>
       <c r="O52">
-        <v>-895.5625553037366</v>
+        <v>-927.4128349812403</v>
       </c>
       <c r="P52">
-        <v>-1663.18760270694</v>
+        <v>-1722.338122108018</v>
       </c>
       <c r="Q52">
-        <v>305.0123972930605</v>
+        <v>245.8618778919827</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.3972160803401681</v>
+        <v>0.4043878370818043</v>
       </c>
       <c r="T52">
-        <v>1.72663799456546</v>
+        <v>1.761875504658633</v>
       </c>
       <c r="U52">
         <v>0.3196487374989669</v>
       </c>
       <c r="V52">
-        <v>0.153174793106948</v>
+        <v>0.1501713657911255</v>
       </c>
       <c r="W52">
-        <v>0.2706866082656655</v>
+        <v>0.2716466500153381</v>
       </c>
       <c r="X52" t="inlineStr">
         <is>
@@ -5577,7 +5577,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>0.4376422660198515</v>
+        <v>0.4290610451175014</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5585,22 +5585,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.3366898316779066</v>
+        <v>0.3394283190528962</v>
       </c>
       <c r="C53">
-        <v>5702.985695291516</v>
+        <v>5237.862304323891</v>
       </c>
       <c r="D53">
-        <v>19346.57569529152</v>
+        <v>19166.14230432389</v>
       </c>
       <c r="E53">
-        <v>5240.290000000001</v>
+        <v>5524.980000000001</v>
       </c>
       <c r="F53">
-        <v>14519.19</v>
+        <v>14803.88</v>
       </c>
       <c r="G53">
         <v>875.6</v>
@@ -5621,37 +5621,37 @@
         <v>1991.289795918367</v>
       </c>
       <c r="M53">
-        <v>4641.040753007625</v>
+        <v>4732.041552086206</v>
       </c>
       <c r="N53">
-        <v>-2649.750957089258</v>
+        <v>-2740.751756167839</v>
       </c>
       <c r="O53">
-        <v>-927.4128349812403</v>
+        <v>-959.2631146587435</v>
       </c>
       <c r="P53">
-        <v>-1722.338122108018</v>
+        <v>-1781.488641509095</v>
       </c>
       <c r="Q53">
-        <v>245.8618778919827</v>
+        <v>186.711358490905</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.4043878370818043</v>
+        <v>0.4118584170210084</v>
       </c>
       <c r="T53">
-        <v>1.761875504658633</v>
+        <v>1.798581244339021</v>
       </c>
       <c r="U53">
         <v>0.3196487374989669</v>
       </c>
       <c r="V53">
-        <v>0.1501713657911255</v>
+        <v>0.1472834549105269</v>
       </c>
       <c r="W53">
-        <v>0.2716466500153381</v>
+        <v>0.2725697670823309</v>
       </c>
       <c r="X53" t="inlineStr">
         <is>
@@ -5659,7 +5659,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>0.4290610451175014</v>
+        <v>0.4208098711729341</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5667,22 +5667,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.3394283190528962</v>
+        <v>0.3421668064278858</v>
       </c>
       <c r="C54">
-        <v>5237.862304323891</v>
+        <v>4776.073393146004</v>
       </c>
       <c r="D54">
-        <v>19166.14230432389</v>
+        <v>18989.04339314601</v>
       </c>
       <c r="E54">
-        <v>5524.980000000001</v>
+        <v>5809.670000000002</v>
       </c>
       <c r="F54">
-        <v>14803.88</v>
+        <v>15088.57</v>
       </c>
       <c r="G54">
         <v>875.6</v>
@@ -5703,37 +5703,37 @@
         <v>1991.289795918367</v>
       </c>
       <c r="M54">
-        <v>4732.041552086206</v>
+        <v>4823.042351164787</v>
       </c>
       <c r="N54">
-        <v>-2740.751756167839</v>
+        <v>-2831.752555246419</v>
       </c>
       <c r="O54">
-        <v>-959.2631146587435</v>
+        <v>-991.1133943362468</v>
       </c>
       <c r="P54">
-        <v>-1781.488641509095</v>
+        <v>-1840.639160910173</v>
       </c>
       <c r="Q54">
-        <v>186.711358490905</v>
+        <v>127.5608390898276</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.4118584170210084</v>
+        <v>0.4196468939789023</v>
       </c>
       <c r="T54">
-        <v>1.798581244339021</v>
+        <v>1.836848930388788</v>
       </c>
       <c r="U54">
         <v>0.3196487374989669</v>
       </c>
       <c r="V54">
-        <v>0.1472834549105269</v>
+        <v>0.1445045217990076</v>
       </c>
       <c r="W54">
-        <v>0.2725697670823309</v>
+        <v>0.2734580495430222</v>
       </c>
       <c r="X54" t="inlineStr">
         <is>
@@ -5741,7 +5741,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>0.4208098711729341</v>
+        <v>0.4128700622828787</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5749,22 +5749,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.3421668064278858</v>
+        <v>0.3449052938028755</v>
       </c>
       <c r="C55">
-        <v>4776.073393146004</v>
+        <v>4317.527374303585</v>
       </c>
       <c r="D55">
-        <v>18989.04339314601</v>
+        <v>18815.18737430359</v>
       </c>
       <c r="E55">
-        <v>5809.670000000002</v>
+        <v>6094.360000000001</v>
       </c>
       <c r="F55">
-        <v>15088.57</v>
+        <v>15373.26</v>
       </c>
       <c r="G55">
         <v>875.6</v>
@@ -5785,37 +5785,37 @@
         <v>1991.289795918367</v>
       </c>
       <c r="M55">
-        <v>4823.042351164787</v>
+        <v>4914.043150243368</v>
       </c>
       <c r="N55">
-        <v>-2831.752555246419</v>
+        <v>-2922.753354325</v>
       </c>
       <c r="O55">
-        <v>-991.1133943362468</v>
+        <v>-1022.96367401375</v>
       </c>
       <c r="P55">
-        <v>-1840.639160910173</v>
+        <v>-1899.78968031125</v>
       </c>
       <c r="Q55">
-        <v>127.5608390898276</v>
+        <v>68.41031968874995</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.4196468939789023</v>
+        <v>0.427774000369748</v>
       </c>
       <c r="T55">
-        <v>1.836848930388788</v>
+        <v>1.876780428875501</v>
       </c>
       <c r="U55">
         <v>0.3196487374989669</v>
       </c>
       <c r="V55">
-        <v>0.1445045217990076</v>
+        <v>0.141828512136063</v>
       </c>
       <c r="W55">
-        <v>0.2734580495430222</v>
+        <v>0.2743134326533175</v>
       </c>
       <c r="X55" t="inlineStr">
         <is>
@@ -5823,7 +5823,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>0.4128700622828787</v>
+        <v>0.4052243203887513</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5831,22 +5831,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.3449052938028755</v>
+        <v>0.3476437811778652</v>
       </c>
       <c r="C56">
-        <v>4317.527374303585</v>
+        <v>3862.135984062799</v>
       </c>
       <c r="D56">
-        <v>18815.18737430359</v>
+        <v>18644.4859840628</v>
       </c>
       <c r="E56">
-        <v>6094.360000000001</v>
+        <v>6379.050000000001</v>
       </c>
       <c r="F56">
-        <v>15373.26</v>
+        <v>15657.95</v>
       </c>
       <c r="G56">
         <v>875.6</v>
@@ -5867,37 +5867,37 @@
         <v>1991.289795918367</v>
       </c>
       <c r="M56">
-        <v>4914.043150243368</v>
+        <v>5005.043949321949</v>
       </c>
       <c r="N56">
-        <v>-2922.753354325</v>
+        <v>-3013.754153403582</v>
       </c>
       <c r="O56">
-        <v>-1022.96367401375</v>
+        <v>-1054.813953691254</v>
       </c>
       <c r="P56">
-        <v>-1899.78968031125</v>
+        <v>-1958.940199712328</v>
       </c>
       <c r="Q56">
-        <v>68.41031968874995</v>
+        <v>9.259800287672078</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.427774000369748</v>
+        <v>0.4362623114890758</v>
       </c>
       <c r="T56">
-        <v>1.876780428875501</v>
+        <v>1.91848666062829</v>
       </c>
       <c r="U56">
         <v>0.3196487374989669</v>
       </c>
       <c r="V56">
-        <v>0.141828512136063</v>
+        <v>0.1392498119154073</v>
       </c>
       <c r="W56">
-        <v>0.2743134326533175</v>
+        <v>0.2751377109232384</v>
       </c>
       <c r="X56" t="inlineStr">
         <is>
@@ -5905,7 +5905,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>0.4052243203887513</v>
+        <v>0.3978566054725922</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5913,22 +5913,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.3476437811778652</v>
+        <v>0.3503822685528548</v>
       </c>
       <c r="C57">
-        <v>3862.135984062799</v>
+        <v>3409.81413299309</v>
       </c>
       <c r="D57">
-        <v>18644.4859840628</v>
+        <v>18476.85413299309</v>
       </c>
       <c r="E57">
-        <v>6379.050000000001</v>
+        <v>6663.740000000002</v>
       </c>
       <c r="F57">
-        <v>15657.95</v>
+        <v>15942.64</v>
       </c>
       <c r="G57">
         <v>875.6</v>
@@ -5949,37 +5949,37 @@
         <v>1991.289795918367</v>
       </c>
       <c r="M57">
-        <v>5005.043949321949</v>
+        <v>5096.04474840053</v>
       </c>
       <c r="N57">
-        <v>-3013.754153403582</v>
+        <v>-3104.754952482162</v>
       </c>
       <c r="O57">
-        <v>-1054.813953691254</v>
+        <v>-1086.664233368757</v>
       </c>
       <c r="P57">
-        <v>-1958.940199712328</v>
+        <v>-2018.090719113406</v>
       </c>
       <c r="Q57">
-        <v>9.259800287672078</v>
+        <v>-49.89071911340534</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.4362623114890758</v>
+        <v>0.4451364549320092</v>
       </c>
       <c r="T57">
-        <v>1.91848666062829</v>
+        <v>1.962088630188023</v>
       </c>
       <c r="U57">
         <v>0.3196487374989669</v>
       </c>
       <c r="V57">
-        <v>0.1392498119154073</v>
+        <v>0.1367632081312035</v>
       </c>
       <c r="W57">
-        <v>0.2751377109232384</v>
+        <v>0.2759325506835192</v>
       </c>
       <c r="X57" t="inlineStr">
         <is>
@@ -5987,7 +5987,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>0.3978566054725922</v>
+        <v>0.3907520232320102</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -5995,22 +5995,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.3503822685528548</v>
+        <v>0.3531207559278445</v>
       </c>
       <c r="C58">
-        <v>3409.81413299309</v>
+        <v>2960.479764538493</v>
       </c>
       <c r="D58">
-        <v>18476.85413299309</v>
+        <v>18312.2097645385</v>
       </c>
       <c r="E58">
-        <v>6663.740000000002</v>
+        <v>6948.430000000002</v>
       </c>
       <c r="F58">
-        <v>15942.64</v>
+        <v>16227.33</v>
       </c>
       <c r="G58">
         <v>875.6</v>
@@ -6031,37 +6031,37 @@
         <v>1991.289795918367</v>
       </c>
       <c r="M58">
-        <v>5096.04474840053</v>
+        <v>5187.045547479111</v>
       </c>
       <c r="N58">
-        <v>-3104.754952482162</v>
+        <v>-3195.755751560743</v>
       </c>
       <c r="O58">
-        <v>-1086.664233368757</v>
+        <v>-1118.51451304626</v>
       </c>
       <c r="P58">
-        <v>-2018.090719113406</v>
+        <v>-2077.241238514483</v>
       </c>
       <c r="Q58">
-        <v>-49.89071911340534</v>
+        <v>-109.0412385144832</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.4451364549320092</v>
+        <v>0.4544233492327537</v>
       </c>
       <c r="T58">
-        <v>1.962088630188023</v>
+        <v>2.007718598331931</v>
       </c>
       <c r="U58">
         <v>0.3196487374989669</v>
       </c>
       <c r="V58">
-        <v>0.1367632081312035</v>
+        <v>0.134363853602586</v>
       </c>
       <c r="W58">
-        <v>0.2759325506835192</v>
+        <v>0.2766995013294043</v>
       </c>
       <c r="X58" t="inlineStr">
         <is>
@@ -6069,7 +6069,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>0.3907520232320102</v>
+        <v>0.3838967245788171</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6077,22 +6077,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.3531207559278445</v>
+        <v>0.3558592433028342</v>
       </c>
       <c r="C59">
-        <v>2960.479764538493</v>
+        <v>2514.053721083819</v>
       </c>
       <c r="D59">
-        <v>18312.2097645385</v>
+        <v>18150.47372108382</v>
       </c>
       <c r="E59">
-        <v>6948.430000000002</v>
+        <v>7233.120000000001</v>
       </c>
       <c r="F59">
-        <v>16227.33</v>
+        <v>16512.02</v>
       </c>
       <c r="G59">
         <v>875.6</v>
@@ -6113,37 +6113,37 @@
         <v>1991.289795918367</v>
       </c>
       <c r="M59">
-        <v>5187.045547479111</v>
+        <v>5278.046346557691</v>
       </c>
       <c r="N59">
-        <v>-3195.755751560743</v>
+        <v>-3286.756550639324</v>
       </c>
       <c r="O59">
-        <v>-1118.51451304626</v>
+        <v>-1150.364792723763</v>
       </c>
       <c r="P59">
-        <v>-2077.241238514483</v>
+        <v>-2136.39175791556</v>
       </c>
       <c r="Q59">
-        <v>-109.0412385144832</v>
+        <v>-168.1917579155602</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.4544233492327537</v>
+        <v>0.4641524765954383</v>
       </c>
       <c r="T59">
-        <v>2.007718598331931</v>
+        <v>2.055521422101739</v>
       </c>
       <c r="U59">
         <v>0.3196487374989669</v>
       </c>
       <c r="V59">
-        <v>0.134363853602586</v>
+        <v>0.1320472354370241</v>
       </c>
       <c r="W59">
-        <v>0.2766995013294043</v>
+        <v>0.2774400054012933</v>
       </c>
       <c r="X59" t="inlineStr">
         <is>
@@ -6151,7 +6151,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>0.3838967245788171</v>
+        <v>0.3772778155343547</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6159,22 +6159,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.3558592433028341</v>
+        <v>0.3585977306778237</v>
       </c>
       <c r="C60">
-        <v>2514.053721083823</v>
+        <v>2070.459617056087</v>
       </c>
       <c r="D60">
-        <v>18150.47372108382</v>
+        <v>17991.56961705609</v>
       </c>
       <c r="E60">
-        <v>7233.120000000001</v>
+        <v>7517.809999999999</v>
       </c>
       <c r="F60">
-        <v>16512.02</v>
+        <v>16796.71</v>
       </c>
       <c r="G60">
         <v>875.6</v>
@@ -6195,37 +6195,37 @@
         <v>1991.289795918367</v>
       </c>
       <c r="M60">
-        <v>5278.046346557691</v>
+        <v>5369.047145636272</v>
       </c>
       <c r="N60">
-        <v>-3286.756550639324</v>
+        <v>-3377.757349717905</v>
       </c>
       <c r="O60">
-        <v>-1150.364792723763</v>
+        <v>-1182.215072401267</v>
       </c>
       <c r="P60">
-        <v>-2136.39175791556</v>
+        <v>-2195.542277316638</v>
       </c>
       <c r="Q60">
-        <v>-168.1917579155602</v>
+        <v>-227.342277316638</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.4641524765954382</v>
+        <v>0.4743561955367903</v>
       </c>
       <c r="T60">
-        <v>2.055521422101739</v>
+        <v>2.105656090933488</v>
       </c>
       <c r="U60">
         <v>0.3196487374989669</v>
       </c>
       <c r="V60">
-        <v>0.1320472354370241</v>
+        <v>0.1298091467008034</v>
       </c>
       <c r="W60">
-        <v>0.2774400054012933</v>
+        <v>0.2781554076402369</v>
       </c>
       <c r="X60" t="inlineStr">
         <is>
@@ -6233,7 +6233,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>0.3772778155343547</v>
+        <v>0.3708832762880098</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6241,22 +6241,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.3585977306778237</v>
+        <v>0.3613362180528135</v>
       </c>
       <c r="C61">
-        <v>2070.459617056087</v>
+        <v>1629.62371863403</v>
       </c>
       <c r="D61">
-        <v>17991.56961705609</v>
+        <v>17835.42371863403</v>
       </c>
       <c r="E61">
-        <v>7517.809999999999</v>
+        <v>7802.499999999998</v>
       </c>
       <c r="F61">
-        <v>16796.71</v>
+        <v>17081.4</v>
       </c>
       <c r="G61">
         <v>875.6</v>
@@ -6277,37 +6277,37 @@
         <v>1991.289795918367</v>
       </c>
       <c r="M61">
-        <v>5369.047145636272</v>
+        <v>5460.047944714852</v>
       </c>
       <c r="N61">
-        <v>-3377.757349717905</v>
+        <v>-3468.758148796484</v>
       </c>
       <c r="O61">
-        <v>-1182.215072401267</v>
+        <v>-1214.065352078769</v>
       </c>
       <c r="P61">
-        <v>-2195.542277316638</v>
+        <v>-2254.692796717715</v>
       </c>
       <c r="Q61">
-        <v>-227.342277316638</v>
+        <v>-286.492796717715</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.4743561955367903</v>
+        <v>0.48507010042521</v>
       </c>
       <c r="T61">
-        <v>2.105656090933488</v>
+        <v>2.158297493206825</v>
       </c>
       <c r="U61">
         <v>0.3196487374989669</v>
       </c>
       <c r="V61">
-        <v>0.1298091467008034</v>
+        <v>0.1276456609224567</v>
       </c>
       <c r="W61">
-        <v>0.2781554076402369</v>
+        <v>0.2788469631378824</v>
       </c>
       <c r="X61" t="inlineStr">
         <is>
@@ -6315,7 +6315,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>0.3708832762880098</v>
+        <v>0.3647018883498763</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6323,22 +6323,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.3613362180528135</v>
+        <v>0.3640747054278032</v>
       </c>
       <c r="C62">
-        <v>1629.62371863403</v>
+        <v>1191.474829667586</v>
       </c>
       <c r="D62">
-        <v>17835.42371863403</v>
+        <v>17681.96482966759</v>
       </c>
       <c r="E62">
-        <v>7802.499999999998</v>
+        <v>8087.190000000001</v>
       </c>
       <c r="F62">
-        <v>17081.4</v>
+        <v>17366.09</v>
       </c>
       <c r="G62">
         <v>875.6</v>
@@ -6359,37 +6359,37 @@
         <v>1991.289795918367</v>
       </c>
       <c r="M62">
-        <v>5460.047944714852</v>
+        <v>5551.048743793433</v>
       </c>
       <c r="N62">
-        <v>-3468.758148796484</v>
+        <v>-3559.758947875066</v>
       </c>
       <c r="O62">
-        <v>-1214.065352078769</v>
+        <v>-1245.915631756273</v>
       </c>
       <c r="P62">
-        <v>-2254.692796717715</v>
+        <v>-2313.843316118793</v>
       </c>
       <c r="Q62">
-        <v>-286.492796717715</v>
+        <v>-345.6433161187929</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.48507010042521</v>
+        <v>0.4963334363335489</v>
       </c>
       <c r="T62">
-        <v>2.158297493206825</v>
+        <v>2.213638454571103</v>
       </c>
       <c r="U62">
         <v>0.3196487374989669</v>
       </c>
       <c r="V62">
-        <v>0.1276456609224567</v>
+        <v>0.1255531091040558</v>
       </c>
       <c r="W62">
-        <v>0.2788469631378824</v>
+        <v>0.2795158446847854</v>
       </c>
       <c r="X62" t="inlineStr">
         <is>
@@ -6397,7 +6397,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>0.3647018883498763</v>
+        <v>0.3587231688687307</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6405,22 +6405,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.3640747054278032</v>
+        <v>0.3668131928027928</v>
       </c>
       <c r="C63">
-        <v>1191.474829667586</v>
+        <v>755.9441834365716</v>
       </c>
       <c r="D63">
-        <v>17681.96482966759</v>
+        <v>17531.12418343657</v>
       </c>
       <c r="E63">
-        <v>8087.190000000001</v>
+        <v>8371.879999999999</v>
       </c>
       <c r="F63">
-        <v>17366.09</v>
+        <v>17650.78</v>
       </c>
       <c r="G63">
         <v>875.6</v>
@@ -6441,37 +6441,37 @@
         <v>1991.289795918367</v>
       </c>
       <c r="M63">
-        <v>5551.048743793433</v>
+        <v>5642.049542872014</v>
       </c>
       <c r="N63">
-        <v>-3559.758947875066</v>
+        <v>-3650.759746953647</v>
       </c>
       <c r="O63">
-        <v>-1245.915631756273</v>
+        <v>-1277.765911433776</v>
       </c>
       <c r="P63">
-        <v>-2313.843316118793</v>
+        <v>-2372.993835519871</v>
       </c>
       <c r="Q63">
-        <v>-345.6433161187929</v>
+        <v>-404.7938355198703</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.4963334363335489</v>
+        <v>0.508189579394958</v>
       </c>
       <c r="T63">
-        <v>2.213638454571103</v>
+        <v>2.271892098112448</v>
       </c>
       <c r="U63">
         <v>0.3196487374989669</v>
       </c>
       <c r="V63">
-        <v>0.1255531091040558</v>
+        <v>0.1235280589572161</v>
       </c>
       <c r="W63">
-        <v>0.2795158446847854</v>
+        <v>0.2801631494075948</v>
       </c>
       <c r="X63" t="inlineStr">
         <is>
@@ -6479,7 +6479,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>0.3587231688687307</v>
+        <v>0.3529373113063319</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6487,22 +6487,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.3668131928027928</v>
+        <v>0.3695516801777825</v>
       </c>
       <c r="C64">
-        <v>755.9441834365716</v>
+        <v>322.9653399026756</v>
       </c>
       <c r="D64">
-        <v>17531.12418343657</v>
+        <v>17382.83533990268</v>
       </c>
       <c r="E64">
-        <v>8371.879999999999</v>
+        <v>8656.570000000002</v>
       </c>
       <c r="F64">
-        <v>17650.78</v>
+        <v>17935.47</v>
       </c>
       <c r="G64">
         <v>875.6</v>
@@ -6523,37 +6523,37 @@
         <v>1991.289795918367</v>
       </c>
       <c r="M64">
-        <v>5642.049542872014</v>
+        <v>5733.050341950596</v>
       </c>
       <c r="N64">
-        <v>-3650.759746953647</v>
+        <v>-3741.760546032228</v>
       </c>
       <c r="O64">
-        <v>-1277.765911433776</v>
+        <v>-1309.61619111128</v>
       </c>
       <c r="P64">
-        <v>-2372.993835519871</v>
+        <v>-2432.144354920948</v>
       </c>
       <c r="Q64">
-        <v>-404.7938355198703</v>
+        <v>-463.9443549209482</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.508189579394958</v>
+        <v>0.5206865950542812</v>
       </c>
       <c r="T64">
-        <v>2.271892098112448</v>
+        <v>2.333294587250622</v>
       </c>
       <c r="U64">
         <v>0.3196487374989669</v>
       </c>
       <c r="V64">
-        <v>0.1235280589572161</v>
+        <v>0.1215672961166254</v>
       </c>
       <c r="W64">
-        <v>0.2801631494075948</v>
+        <v>0.2807899047741245</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
@@ -6561,7 +6561,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>0.3529373113063319</v>
+        <v>0.3473351317617869</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6569,22 +6569,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.3695516801777825</v>
+        <v>0.3722901675527722</v>
       </c>
       <c r="C65">
-        <v>322.9653399026756</v>
+        <v>-107.5259118674985</v>
       </c>
       <c r="D65">
-        <v>17382.83533990268</v>
+        <v>17237.0340881325</v>
       </c>
       <c r="E65">
-        <v>8656.570000000002</v>
+        <v>8941.26</v>
       </c>
       <c r="F65">
-        <v>17935.47</v>
+        <v>18220.16</v>
       </c>
       <c r="G65">
         <v>875.6</v>
@@ -6605,37 +6605,37 @@
         <v>1991.289795918367</v>
       </c>
       <c r="M65">
-        <v>5733.050341950596</v>
+        <v>5824.051141029177</v>
       </c>
       <c r="N65">
-        <v>-3741.760546032228</v>
+        <v>-3832.761345110809</v>
       </c>
       <c r="O65">
-        <v>-1309.61619111128</v>
+        <v>-1341.466470788783</v>
       </c>
       <c r="P65">
-        <v>-2432.144354920948</v>
+        <v>-2491.294874322026</v>
       </c>
       <c r="Q65">
-        <v>-463.9443549209482</v>
+        <v>-523.0948743220256</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.5206865950542812</v>
+        <v>0.5338778893613446</v>
       </c>
       <c r="T65">
-        <v>2.333294587250622</v>
+        <v>2.398108325785362</v>
       </c>
       <c r="U65">
         <v>0.3196487374989669</v>
       </c>
       <c r="V65">
-        <v>0.1215672961166254</v>
+        <v>0.1196678071148031</v>
       </c>
       <c r="W65">
-        <v>0.2807899047741245</v>
+        <v>0.2813970740354502</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
@@ -6643,7 +6643,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>0.3473351317617869</v>
+        <v>0.3419080203280089</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6651,22 +6651,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.3722901675527722</v>
+        <v>0.3750286549277618</v>
       </c>
       <c r="C66">
-        <v>-107.5259118674985</v>
+        <v>-535.5916464097245</v>
       </c>
       <c r="D66">
-        <v>17237.0340881325</v>
+        <v>17093.65835359028</v>
       </c>
       <c r="E66">
-        <v>8941.26</v>
+        <v>9225.950000000003</v>
       </c>
       <c r="F66">
-        <v>18220.16</v>
+        <v>18504.85</v>
       </c>
       <c r="G66">
         <v>875.6</v>
@@ -6687,37 +6687,37 @@
         <v>1991.289795918367</v>
       </c>
       <c r="M66">
-        <v>5824.051141029177</v>
+        <v>5915.051940107758</v>
       </c>
       <c r="N66">
-        <v>-3832.761345110809</v>
+        <v>-3923.762144189391</v>
       </c>
       <c r="O66">
-        <v>-1341.466470788783</v>
+        <v>-1373.316750466287</v>
       </c>
       <c r="P66">
-        <v>-2491.294874322026</v>
+        <v>-2550.445393723104</v>
       </c>
       <c r="Q66">
-        <v>-523.0948743220256</v>
+        <v>-582.2453937231035</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.5338778893613446</v>
+        <v>0.5478229719145259</v>
       </c>
       <c r="T66">
-        <v>2.398108325785362</v>
+        <v>2.466625706522087</v>
       </c>
       <c r="U66">
         <v>0.3196487374989669</v>
       </c>
       <c r="V66">
-        <v>0.1196678071148031</v>
+        <v>0.1178267639284215</v>
       </c>
       <c r="W66">
-        <v>0.2813970740354502</v>
+        <v>0.2819855611656581</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
@@ -6725,7 +6725,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>0.3419080203280089</v>
+        <v>0.3366478969383472</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6733,22 +6733,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.3750286549277618</v>
+        <v>0.3777671423027514</v>
       </c>
       <c r="C67">
-        <v>-535.5916464097245</v>
+        <v>-961.2918899807628</v>
       </c>
       <c r="D67">
-        <v>17093.65835359028</v>
+        <v>16952.64811001924</v>
       </c>
       <c r="E67">
-        <v>9225.950000000003</v>
+        <v>9510.640000000001</v>
       </c>
       <c r="F67">
-        <v>18504.85</v>
+        <v>18789.54</v>
       </c>
       <c r="G67">
         <v>875.6</v>
@@ -6769,37 +6769,37 @@
         <v>1991.289795918367</v>
       </c>
       <c r="M67">
-        <v>5915.051940107758</v>
+        <v>6006.052739186339</v>
       </c>
       <c r="N67">
-        <v>-3923.762144189391</v>
+        <v>-4014.762943267971</v>
       </c>
       <c r="O67">
-        <v>-1373.316750466287</v>
+        <v>-1405.16703014379</v>
       </c>
       <c r="P67">
-        <v>-2550.445393723104</v>
+        <v>-2609.595913124182</v>
       </c>
       <c r="Q67">
-        <v>-582.2453937231035</v>
+        <v>-641.3959131241813</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.5478229719145259</v>
+        <v>0.5625883534414235</v>
       </c>
       <c r="T67">
-        <v>2.466625706522087</v>
+        <v>2.539173521419795</v>
       </c>
       <c r="U67">
         <v>0.3196487374989669</v>
       </c>
       <c r="V67">
-        <v>0.1178267639284215</v>
+        <v>0.116041509929506</v>
       </c>
       <c r="W67">
-        <v>0.2819855611656581</v>
+        <v>0.2825562153525265</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
@@ -6807,7 +6807,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>0.3366478969383472</v>
+        <v>0.3315471712271602</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6815,22 +6815,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.3777671423027514</v>
+        <v>0.3805056296777412</v>
       </c>
       <c r="C68">
-        <v>-961.2918899807628</v>
+        <v>-1384.684704351199</v>
       </c>
       <c r="D68">
-        <v>16952.64811001924</v>
+        <v>16813.9452956488</v>
       </c>
       <c r="E68">
-        <v>9510.640000000001</v>
+        <v>9795.33</v>
       </c>
       <c r="F68">
-        <v>18789.54</v>
+        <v>19074.23</v>
       </c>
       <c r="G68">
         <v>875.6</v>
@@ -6851,37 +6851,37 @@
         <v>1991.289795918367</v>
       </c>
       <c r="M68">
-        <v>6006.052739186339</v>
+        <v>6097.053538264919</v>
       </c>
       <c r="N68">
-        <v>-4014.762943267971</v>
+        <v>-4105.763742346551</v>
       </c>
       <c r="O68">
-        <v>-1405.16703014379</v>
+        <v>-1437.017309821293</v>
       </c>
       <c r="P68">
-        <v>-2609.595913124182</v>
+        <v>-2668.746432525259</v>
       </c>
       <c r="Q68">
-        <v>-641.3959131241813</v>
+        <v>-700.5464325252583</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.5625883534414235</v>
+        <v>0.5782486065760124</v>
       </c>
       <c r="T68">
-        <v>2.539173521419795</v>
+        <v>2.616118173584032</v>
       </c>
       <c r="U68">
         <v>0.3196487374989669</v>
       </c>
       <c r="V68">
-        <v>0.116041509929506</v>
+        <v>0.1143095470947373</v>
       </c>
       <c r="W68">
-        <v>0.2825562153525265</v>
+        <v>0.2831098350860554</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
@@ -6889,7 +6889,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>0.3315471712271602</v>
+        <v>0.3265987059849638</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6897,22 +6897,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.3805056296777412</v>
+        <v>0.3832441170527308</v>
       </c>
       <c r="C69">
-        <v>-1384.684704351199</v>
+        <v>-1805.826266518176</v>
       </c>
       <c r="D69">
-        <v>16813.9452956488</v>
+        <v>16677.49373348183</v>
       </c>
       <c r="E69">
-        <v>9795.33</v>
+        <v>10080.02</v>
       </c>
       <c r="F69">
-        <v>19074.23</v>
+        <v>19358.92</v>
       </c>
       <c r="G69">
         <v>875.6</v>
@@ -6933,37 +6933,37 @@
         <v>1991.289795918367</v>
       </c>
       <c r="M69">
-        <v>6097.053538264919</v>
+        <v>6188.0543373435</v>
       </c>
       <c r="N69">
-        <v>-4105.763742346551</v>
+        <v>-4196.764541425133</v>
       </c>
       <c r="O69">
-        <v>-1437.017309821293</v>
+        <v>-1468.867589498796</v>
       </c>
       <c r="P69">
-        <v>-2668.746432525259</v>
+        <v>-2727.896951926336</v>
       </c>
       <c r="Q69">
-        <v>-700.5464325252583</v>
+        <v>-759.6969519263362</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.5782486065760124</v>
+        <v>0.5948876255315126</v>
       </c>
       <c r="T69">
-        <v>2.616118173584032</v>
+        <v>2.697871866508532</v>
       </c>
       <c r="U69">
         <v>0.3196487374989669</v>
       </c>
       <c r="V69">
-        <v>0.1143095470947373</v>
+        <v>0.1126285243433441</v>
       </c>
       <c r="W69">
-        <v>0.2831098350860554</v>
+        <v>0.2836471718862453</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
@@ -6971,7 +6971,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>0.3265987059849638</v>
+        <v>0.321795783838126</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6979,22 +6979,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.3832441170527308</v>
+        <v>0.3859826044277205</v>
       </c>
       <c r="C70">
-        <v>-1805.826266518176</v>
+        <v>-2224.770944568045</v>
       </c>
       <c r="D70">
-        <v>16677.49373348183</v>
+        <v>16543.23905543196</v>
       </c>
       <c r="E70">
-        <v>10080.02</v>
+        <v>10364.71</v>
       </c>
       <c r="F70">
-        <v>19358.92</v>
+        <v>19643.61</v>
       </c>
       <c r="G70">
         <v>875.6</v>
@@ -7015,37 +7015,37 @@
         <v>1991.289795918367</v>
       </c>
       <c r="M70">
-        <v>6188.0543373435</v>
+        <v>6279.055136422081</v>
       </c>
       <c r="N70">
-        <v>-4196.764541425133</v>
+        <v>-4287.765340503714</v>
       </c>
       <c r="O70">
-        <v>-1468.867589498796</v>
+        <v>-1500.7178691763</v>
       </c>
       <c r="P70">
-        <v>-2727.896951926336</v>
+        <v>-2787.047471327414</v>
       </c>
       <c r="Q70">
-        <v>-759.6969519263362</v>
+        <v>-818.8474713274136</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.5948876255315126</v>
+        <v>0.6126001295809164</v>
       </c>
       <c r="T70">
-        <v>2.697871866508532</v>
+        <v>2.784899991234615</v>
       </c>
       <c r="U70">
         <v>0.3196487374989669</v>
       </c>
       <c r="V70">
-        <v>0.1126285243433441</v>
+        <v>0.1109962268890928</v>
       </c>
       <c r="W70">
-        <v>0.2836471718862453</v>
+        <v>0.2841689337067195</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
@@ -7053,7 +7053,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>0.321795783838126</v>
+        <v>0.3171320768259793</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7061,22 +7061,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.3859826044277205</v>
+        <v>0.3887210918027101</v>
       </c>
       <c r="C71">
-        <v>-2224.770944568045</v>
+        <v>-2641.571369904028</v>
       </c>
       <c r="D71">
-        <v>16543.23905543196</v>
+        <v>16411.12863009598</v>
       </c>
       <c r="E71">
-        <v>10364.71</v>
+        <v>10649.4</v>
       </c>
       <c r="F71">
-        <v>19643.61</v>
+        <v>19928.3</v>
       </c>
       <c r="G71">
         <v>875.6</v>
@@ -7097,37 +7097,37 @@
         <v>1991.289795918367</v>
       </c>
       <c r="M71">
-        <v>6279.055136422081</v>
+        <v>6370.055935500663</v>
       </c>
       <c r="N71">
-        <v>-4287.765340503714</v>
+        <v>-4378.766139582295</v>
       </c>
       <c r="O71">
-        <v>-1500.7178691763</v>
+        <v>-1532.568148853803</v>
       </c>
       <c r="P71">
-        <v>-2787.047471327414</v>
+        <v>-2846.197990728492</v>
       </c>
       <c r="Q71">
-        <v>-818.8474713274136</v>
+        <v>-877.9979907284919</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.6126001295809164</v>
+        <v>0.6314934672336134</v>
       </c>
       <c r="T71">
-        <v>2.784899991234615</v>
+        <v>2.877729990942434</v>
       </c>
       <c r="U71">
         <v>0.3196487374989669</v>
       </c>
       <c r="V71">
-        <v>0.1109962268890928</v>
+        <v>0.1094105665049628</v>
       </c>
       <c r="W71">
-        <v>0.2841689337067195</v>
+        <v>0.2846757880466088</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
@@ -7135,7 +7135,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>0.3171320768259793</v>
+        <v>0.3126016185856082</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7143,22 +7143,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.3887210918027101</v>
+        <v>0.3914595791776999</v>
       </c>
       <c r="C72">
-        <v>-2641.571369904028</v>
+        <v>-3056.278506040577</v>
       </c>
       <c r="D72">
-        <v>16411.12863009598</v>
+        <v>16281.11149395942</v>
       </c>
       <c r="E72">
-        <v>10649.4</v>
+        <v>10934.09</v>
       </c>
       <c r="F72">
-        <v>19928.3</v>
+        <v>20212.99</v>
       </c>
       <c r="G72">
         <v>875.6</v>
@@ -7179,37 +7179,37 @@
         <v>1991.289795918367</v>
       </c>
       <c r="M72">
-        <v>6370.055935500663</v>
+        <v>6461.056734579243</v>
       </c>
       <c r="N72">
-        <v>-4378.766139582295</v>
+        <v>-4469.766938660876</v>
       </c>
       <c r="O72">
-        <v>-1532.568148853803</v>
+        <v>-1564.418428531307</v>
       </c>
       <c r="P72">
-        <v>-2846.197990728492</v>
+        <v>-2905.348510129569</v>
       </c>
       <c r="Q72">
-        <v>-877.9979907284919</v>
+        <v>-937.1485101295689</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.6314934672336134</v>
+        <v>0.6516897936899452</v>
       </c>
       <c r="T72">
-        <v>2.877729990942434</v>
+        <v>2.976962059595623</v>
       </c>
       <c r="U72">
         <v>0.3196487374989669</v>
       </c>
       <c r="V72">
-        <v>0.1094105665049628</v>
+        <v>0.1078695726105268</v>
       </c>
       <c r="W72">
-        <v>0.2846757880466088</v>
+        <v>0.2851683647994588</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
@@ -7217,7 +7217,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>0.3126016185856082</v>
+        <v>0.3081987788872194</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7225,22 +7225,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.3914595791776998</v>
+        <v>0.3941980665526895</v>
       </c>
       <c r="C73">
-        <v>-3056.278506040569</v>
+        <v>-3468.941714153269</v>
       </c>
       <c r="D73">
-        <v>16281.11149395943</v>
+        <v>16153.13828584673</v>
       </c>
       <c r="E73">
-        <v>10934.09</v>
+        <v>11218.78</v>
       </c>
       <c r="F73">
-        <v>20212.99</v>
+        <v>20497.68</v>
       </c>
       <c r="G73">
         <v>875.6</v>
@@ -7261,37 +7261,37 @@
         <v>1991.289795918367</v>
       </c>
       <c r="M73">
-        <v>6461.056734579242</v>
+        <v>6552.057533657824</v>
       </c>
       <c r="N73">
-        <v>-4469.766938660875</v>
+        <v>-4560.767737739457</v>
       </c>
       <c r="O73">
-        <v>-1564.418428531306</v>
+        <v>-1596.26870820881</v>
       </c>
       <c r="P73">
-        <v>-2905.348510129569</v>
+        <v>-2964.499029530647</v>
       </c>
       <c r="Q73">
-        <v>-937.1485101295689</v>
+        <v>-996.2990295306467</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.6516897936899448</v>
+        <v>0.6733287148931572</v>
       </c>
       <c r="T73">
-        <v>2.976962059595621</v>
+        <v>3.083282133152608</v>
       </c>
       <c r="U73">
         <v>0.3196487374989669</v>
       </c>
       <c r="V73">
-        <v>0.1078695726105268</v>
+        <v>0.1063713841020472</v>
       </c>
       <c r="W73">
-        <v>0.2851683647994588</v>
+        <v>0.2856472588647298</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
@@ -7299,7 +7299,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>0.3081987788872194</v>
+        <v>0.3039182402915634</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7307,22 +7307,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.3941980665526895</v>
+        <v>0.3969365539276791</v>
       </c>
       <c r="C74">
-        <v>-3468.941714153269</v>
+        <v>-3879.608815561409</v>
       </c>
       <c r="D74">
-        <v>16153.13828584673</v>
+        <v>16027.16118443859</v>
       </c>
       <c r="E74">
-        <v>11218.78</v>
+        <v>11503.47</v>
       </c>
       <c r="F74">
-        <v>20497.68</v>
+        <v>20782.37</v>
       </c>
       <c r="G74">
         <v>875.6</v>
@@ -7343,37 +7343,37 @@
         <v>1991.289795918367</v>
       </c>
       <c r="M74">
-        <v>6552.057533657824</v>
+        <v>6643.058332736404</v>
       </c>
       <c r="N74">
-        <v>-4560.767737739457</v>
+        <v>-4651.768536818036</v>
       </c>
       <c r="O74">
-        <v>-1596.26870820881</v>
+        <v>-1628.118987886313</v>
       </c>
       <c r="P74">
-        <v>-2964.499029530647</v>
+        <v>-3023.649548931724</v>
       </c>
       <c r="Q74">
-        <v>-996.2990295306467</v>
+        <v>-1055.449548931724</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.6733287148931572</v>
+        <v>0.6965705191484592</v>
       </c>
       <c r="T74">
-        <v>3.083282133152608</v>
+        <v>3.197477767713815</v>
       </c>
       <c r="U74">
         <v>0.3196487374989669</v>
       </c>
       <c r="V74">
-        <v>0.1063713841020472</v>
+        <v>0.104914241854074</v>
       </c>
       <c r="W74">
-        <v>0.2856472588647298</v>
+        <v>0.2861130325446509</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
@@ -7381,7 +7381,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>0.3039182402915634</v>
+        <v>0.2997549767259257</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7389,22 +7389,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.3969365539276791</v>
+        <v>0.3996750413026688</v>
       </c>
       <c r="C75">
-        <v>-3879.608815561409</v>
+        <v>-4288.326151309488</v>
       </c>
       <c r="D75">
-        <v>16027.16118443859</v>
+        <v>15903.13384869051</v>
       </c>
       <c r="E75">
-        <v>11503.47</v>
+        <v>11788.16</v>
       </c>
       <c r="F75">
-        <v>20782.37</v>
+        <v>21067.06</v>
       </c>
       <c r="G75">
         <v>875.6</v>
@@ -7425,37 +7425,37 @@
         <v>1991.289795918367</v>
       </c>
       <c r="M75">
-        <v>6643.058332736404</v>
+        <v>6734.059131814985</v>
       </c>
       <c r="N75">
-        <v>-4651.768536818036</v>
+        <v>-4742.769335896618</v>
       </c>
       <c r="O75">
-        <v>-1628.118987886313</v>
+        <v>-1659.969267563816</v>
       </c>
       <c r="P75">
-        <v>-3023.649548931724</v>
+        <v>-3082.800068332802</v>
       </c>
       <c r="Q75">
-        <v>-1055.449548931724</v>
+        <v>-1114.600068332802</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.6965705191484592</v>
+        <v>0.7216001545003231</v>
       </c>
       <c r="T75">
-        <v>3.197477767713815</v>
+        <v>3.320457681856654</v>
       </c>
       <c r="U75">
         <v>0.3196487374989669</v>
       </c>
       <c r="V75">
-        <v>0.104914241854074</v>
+        <v>0.1034964818290189</v>
       </c>
       <c r="W75">
-        <v>0.2861130325446509</v>
+        <v>0.2865662177467362</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
@@ -7463,7 +7463,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>0.2997549767259257</v>
+        <v>0.2957042337971969</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7471,22 +7471,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.3996750413026688</v>
+        <v>0.4024135286776585</v>
       </c>
       <c r="C76">
-        <v>-4288.326151309488</v>
+        <v>-4695.138639003369</v>
       </c>
       <c r="D76">
-        <v>15903.13384869051</v>
+        <v>15781.01136099663</v>
       </c>
       <c r="E76">
-        <v>11788.16</v>
+        <v>12072.85</v>
       </c>
       <c r="F76">
-        <v>21067.06</v>
+        <v>21351.75</v>
       </c>
       <c r="G76">
         <v>875.6</v>
@@ -7507,37 +7507,37 @@
         <v>1991.289795918367</v>
       </c>
       <c r="M76">
-        <v>6734.059131814985</v>
+        <v>6825.059930893566</v>
       </c>
       <c r="N76">
-        <v>-4742.769335896618</v>
+        <v>-4833.770134975199</v>
       </c>
       <c r="O76">
-        <v>-1659.969267563816</v>
+        <v>-1691.819547241319</v>
       </c>
       <c r="P76">
-        <v>-3082.800068332802</v>
+        <v>-3141.950587733879</v>
       </c>
       <c r="Q76">
-        <v>-1114.600068332802</v>
+        <v>-1173.750587733879</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.7216001545003231</v>
+        <v>0.7486321606803361</v>
       </c>
       <c r="T76">
-        <v>3.320457681856654</v>
+        <v>3.453275989130921</v>
       </c>
       <c r="U76">
         <v>0.3196487374989669</v>
       </c>
       <c r="V76">
-        <v>0.1034964818290189</v>
+        <v>0.1021165287379653</v>
       </c>
       <c r="W76">
-        <v>0.2865662177467362</v>
+        <v>0.2870073180100993</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
@@ -7545,7 +7545,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>0.2957042337971969</v>
+        <v>0.291761510679901</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7553,22 +7553,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.4024135286776585</v>
+        <v>0.4051520160526482</v>
       </c>
       <c r="C77">
-        <v>-4695.138639003369</v>
+        <v>-5100.08982704781</v>
       </c>
       <c r="D77">
-        <v>15781.01136099663</v>
+        <v>15660.75017295219</v>
       </c>
       <c r="E77">
-        <v>12072.85</v>
+        <v>12357.54</v>
       </c>
       <c r="F77">
-        <v>21351.75</v>
+        <v>21636.44</v>
       </c>
       <c r="G77">
         <v>875.6</v>
@@ -7589,37 +7589,37 @@
         <v>1991.289795918367</v>
       </c>
       <c r="M77">
-        <v>6825.059930893566</v>
+        <v>6916.060729972147</v>
       </c>
       <c r="N77">
-        <v>-4833.770134975199</v>
+        <v>-4924.770934053779</v>
       </c>
       <c r="O77">
-        <v>-1691.819547241319</v>
+        <v>-1723.669826918823</v>
       </c>
       <c r="P77">
-        <v>-3141.950587733879</v>
+        <v>-3201.101107134957</v>
       </c>
       <c r="Q77">
-        <v>-1173.750587733879</v>
+        <v>-1232.901107134956</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.7486321606803361</v>
+        <v>0.7779168340420168</v>
       </c>
       <c r="T77">
-        <v>3.453275989130921</v>
+        <v>3.597162488678043</v>
       </c>
       <c r="U77">
         <v>0.3196487374989669</v>
       </c>
       <c r="V77">
-        <v>0.1021165287379653</v>
+        <v>0.1007728902019395</v>
       </c>
       <c r="W77">
-        <v>0.2870073180100993</v>
+        <v>0.2874368103717949</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
@@ -7627,7 +7627,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>0.291761510679901</v>
+        <v>0.2879225434341128</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7635,22 +7635,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.4051520160526482</v>
+        <v>0.4078905034276379</v>
       </c>
       <c r="C78">
-        <v>-5100.08982704781</v>
+        <v>-5503.221946422727</v>
       </c>
       <c r="D78">
-        <v>15660.75017295219</v>
+        <v>15542.30805357728</v>
       </c>
       <c r="E78">
-        <v>12357.54</v>
+        <v>12642.23</v>
       </c>
       <c r="F78">
-        <v>21636.44</v>
+        <v>21921.13</v>
       </c>
       <c r="G78">
         <v>875.6</v>
@@ -7671,37 +7671,37 @@
         <v>1991.289795918367</v>
       </c>
       <c r="M78">
-        <v>6916.060729972147</v>
+        <v>7007.061529050728</v>
       </c>
       <c r="N78">
-        <v>-4924.770934053779</v>
+        <v>-5015.771733132361</v>
       </c>
       <c r="O78">
-        <v>-1723.669826918823</v>
+        <v>-1755.520106596326</v>
       </c>
       <c r="P78">
-        <v>-3201.101107134957</v>
+        <v>-3260.251626536035</v>
       </c>
       <c r="Q78">
-        <v>-1232.901107134956</v>
+        <v>-1292.051626536034</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.7779168340420168</v>
+        <v>0.8097480007394959</v>
       </c>
       <c r="T78">
-        <v>3.597162488678043</v>
+        <v>3.753560857751002</v>
       </c>
       <c r="U78">
         <v>0.3196487374989669</v>
       </c>
       <c r="V78">
-        <v>0.1007728902019395</v>
+        <v>0.09946415136814805</v>
       </c>
       <c r="W78">
-        <v>0.2874368103717949</v>
+        <v>0.2878551470877322</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
@@ -7709,7 +7709,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>0.2879225434341128</v>
+        <v>0.2841832896232801</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7717,22 +7717,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.4078905034276379</v>
+        <v>0.4106289908026275</v>
       </c>
       <c r="C79">
-        <v>-5503.221946422727</v>
+        <v>-5904.575960127562</v>
       </c>
       <c r="D79">
-        <v>15542.30805357728</v>
+        <v>15425.64403987244</v>
       </c>
       <c r="E79">
-        <v>12642.23</v>
+        <v>12926.92</v>
       </c>
       <c r="F79">
-        <v>21921.13</v>
+        <v>22205.82</v>
       </c>
       <c r="G79">
         <v>875.6</v>
@@ -7753,37 +7753,37 @@
         <v>1991.289795918367</v>
       </c>
       <c r="M79">
-        <v>7007.061529050728</v>
+        <v>7098.062328129308</v>
       </c>
       <c r="N79">
-        <v>-5015.771733132361</v>
+        <v>-5106.772532210941</v>
       </c>
       <c r="O79">
-        <v>-1755.520106596326</v>
+        <v>-1787.370386273829</v>
       </c>
       <c r="P79">
-        <v>-3260.251626536035</v>
+        <v>-3319.402145937112</v>
       </c>
       <c r="Q79">
-        <v>-1292.051626536034</v>
+        <v>-1351.202145937111</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.8097480007394959</v>
+        <v>0.8444729098640184</v>
       </c>
       <c r="T79">
-        <v>3.753560857751002</v>
+        <v>3.924177260376047</v>
       </c>
       <c r="U79">
         <v>0.3196487374989669</v>
       </c>
       <c r="V79">
-        <v>0.09946415136814805</v>
+        <v>0.0981889699403513</v>
       </c>
       <c r="W79">
-        <v>0.2878551470877322</v>
+        <v>0.2882627572212096</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
@@ -7791,7 +7791,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>0.2841832896232801</v>
+        <v>0.2805399141152894</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7799,22 +7799,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.4106289908026275</v>
+        <v>0.4133674781776172</v>
       </c>
       <c r="C80">
-        <v>-5904.575960127562</v>
+        <v>-6304.191610415544</v>
       </c>
       <c r="D80">
-        <v>15425.64403987244</v>
+        <v>15310.71838958446</v>
       </c>
       <c r="E80">
-        <v>12926.92</v>
+        <v>13211.61</v>
       </c>
       <c r="F80">
-        <v>22205.82</v>
+        <v>22490.51</v>
       </c>
       <c r="G80">
         <v>875.6</v>
@@ -7835,37 +7835,37 @@
         <v>1991.289795918367</v>
       </c>
       <c r="M80">
-        <v>7098.062328129308</v>
+        <v>7189.06312720789</v>
       </c>
       <c r="N80">
-        <v>-5106.772532210941</v>
+        <v>-5197.773331289523</v>
       </c>
       <c r="O80">
-        <v>-1787.370386273829</v>
+        <v>-1819.220665951333</v>
       </c>
       <c r="P80">
-        <v>-3319.402145937112</v>
+        <v>-3378.55266533819</v>
       </c>
       <c r="Q80">
-        <v>-1351.202145937111</v>
+        <v>-1410.35266533819</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.8444729098640184</v>
+        <v>0.8825049531908766</v>
       </c>
       <c r="T80">
-        <v>3.924177260376047</v>
+        <v>4.111042844203479</v>
       </c>
       <c r="U80">
         <v>0.3196487374989669</v>
       </c>
       <c r="V80">
-        <v>0.0981889699403513</v>
+        <v>0.09694607158667594</v>
       </c>
       <c r="W80">
-        <v>0.2882627572212096</v>
+        <v>0.2886600481108015</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
@@ -7873,7 +7873,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>0.2805399141152894</v>
+        <v>0.2769887759619313</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7881,22 +7881,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.4133674781776172</v>
+        <v>0.4161059655526068</v>
       </c>
       <c r="C81">
-        <v>-6304.191610415544</v>
+        <v>-6702.107463931916</v>
       </c>
       <c r="D81">
-        <v>15310.71838958446</v>
+        <v>15197.49253606808</v>
       </c>
       <c r="E81">
-        <v>13211.61</v>
+        <v>13496.3</v>
       </c>
       <c r="F81">
-        <v>22490.51</v>
+        <v>22775.2</v>
       </c>
       <c r="G81">
         <v>875.6</v>
@@ -7917,37 +7917,37 @@
         <v>1991.289795918367</v>
       </c>
       <c r="M81">
-        <v>7189.06312720789</v>
+        <v>7280.063926286471</v>
       </c>
       <c r="N81">
-        <v>-5197.773331289523</v>
+        <v>-5288.774130368103</v>
       </c>
       <c r="O81">
-        <v>-1819.220665951333</v>
+        <v>-1851.070945628836</v>
       </c>
       <c r="P81">
-        <v>-3378.55266533819</v>
+        <v>-3437.703184739267</v>
       </c>
       <c r="Q81">
-        <v>-1410.35266533819</v>
+        <v>-1469.503184739267</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.8825049531908766</v>
+        <v>0.9243402008504205</v>
       </c>
       <c r="T81">
-        <v>4.111042844203479</v>
+        <v>4.316594986413652</v>
       </c>
       <c r="U81">
         <v>0.3196487374989669</v>
       </c>
       <c r="V81">
-        <v>0.09694607158667594</v>
+        <v>0.0957342456918425</v>
       </c>
       <c r="W81">
-        <v>0.2886600481108015</v>
+        <v>0.2890474067281535</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
@@ -7955,7 +7955,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>0.2769887759619313</v>
+        <v>0.2735264162624071</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7963,22 +7963,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.4161059655526068</v>
+        <v>0.4188444529275965</v>
       </c>
       <c r="C82">
-        <v>-6702.107463931916</v>
+        <v>-7098.360954864193</v>
       </c>
       <c r="D82">
-        <v>15197.49253606808</v>
+        <v>15085.92904513581</v>
       </c>
       <c r="E82">
-        <v>13496.3</v>
+        <v>13780.99</v>
       </c>
       <c r="F82">
-        <v>22775.2</v>
+        <v>23059.89</v>
       </c>
       <c r="G82">
         <v>875.6</v>
@@ -7999,37 +7999,37 @@
         <v>1991.289795918367</v>
       </c>
       <c r="M82">
-        <v>7280.063926286471</v>
+        <v>7371.064725365052</v>
       </c>
       <c r="N82">
-        <v>-5288.774130368103</v>
+        <v>-5379.774929446685</v>
       </c>
       <c r="O82">
-        <v>-1851.070945628836</v>
+        <v>-1882.921225306339</v>
       </c>
       <c r="P82">
-        <v>-3437.703184739267</v>
+        <v>-3496.853704140345</v>
       </c>
       <c r="Q82">
-        <v>-1469.503184739267</v>
+        <v>-1528.653704140345</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.9243402008504205</v>
+        <v>0.9705791587899162</v>
       </c>
       <c r="T82">
-        <v>4.316594986413652</v>
+        <v>4.543784196224897</v>
       </c>
       <c r="U82">
         <v>0.3196487374989669</v>
       </c>
       <c r="V82">
-        <v>0.0957342456918425</v>
+        <v>0.09455234142404197</v>
       </c>
       <c r="W82">
-        <v>0.2890474067281535</v>
+        <v>0.2894252009352006</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
@@ -8037,7 +8037,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>0.2735264162624071</v>
+        <v>0.2701495469258343</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8045,22 +8045,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.4188444529275965</v>
+        <v>0.4215829403025862</v>
       </c>
       <c r="C83">
-        <v>-7098.360954864193</v>
+        <v>-7492.988426205568</v>
       </c>
       <c r="D83">
-        <v>15085.92904513581</v>
+        <v>14975.99157379443</v>
       </c>
       <c r="E83">
-        <v>13780.99</v>
+        <v>14065.68</v>
       </c>
       <c r="F83">
-        <v>23059.89</v>
+        <v>23344.58</v>
       </c>
       <c r="G83">
         <v>875.6</v>
@@ -8081,37 +8081,37 @@
         <v>1991.289795918367</v>
       </c>
       <c r="M83">
-        <v>7371.064725365052</v>
+        <v>7462.065524443633</v>
       </c>
       <c r="N83">
-        <v>-5379.774929446685</v>
+        <v>-5470.775728525266</v>
       </c>
       <c r="O83">
-        <v>-1882.921225306339</v>
+        <v>-1914.771504983843</v>
       </c>
       <c r="P83">
-        <v>-3496.853704140345</v>
+        <v>-3556.004223541423</v>
       </c>
       <c r="Q83">
-        <v>-1528.653704140345</v>
+        <v>-1587.804223541423</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.9705791587899162</v>
+        <v>1.021955778722689</v>
       </c>
       <c r="T83">
-        <v>4.543784196224897</v>
+        <v>4.796216651570725</v>
       </c>
       <c r="U83">
         <v>0.3196487374989669</v>
       </c>
       <c r="V83">
-        <v>0.09455234142404197</v>
+        <v>0.09339926408960243</v>
       </c>
       <c r="W83">
-        <v>0.2894252009352006</v>
+        <v>0.2897937806493929</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
@@ -8119,7 +8119,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>0.2701495469258343</v>
+        <v>0.2668550402560069</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8127,22 +8127,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.4215829403025862</v>
+        <v>0.424321427677576</v>
       </c>
       <c r="C84">
-        <v>-7492.988426205568</v>
+        <v>-7886.025169227267</v>
       </c>
       <c r="D84">
-        <v>14975.99157379443</v>
+        <v>14867.64483077273</v>
       </c>
       <c r="E84">
-        <v>14065.68</v>
+        <v>14350.37</v>
       </c>
       <c r="F84">
-        <v>23344.58</v>
+        <v>23629.27</v>
       </c>
       <c r="G84">
         <v>875.6</v>
@@ -8163,37 +8163,37 @@
         <v>1991.289795918367</v>
       </c>
       <c r="M84">
-        <v>7462.065524443633</v>
+        <v>7553.066323522214</v>
       </c>
       <c r="N84">
-        <v>-5470.775728525266</v>
+        <v>-5561.776527603846</v>
       </c>
       <c r="O84">
-        <v>-1914.771504983843</v>
+        <v>-1946.621784661346</v>
       </c>
       <c r="P84">
-        <v>-3556.004223541423</v>
+        <v>-3615.1547429425</v>
       </c>
       <c r="Q84">
-        <v>-1587.804223541423</v>
+        <v>-1646.9547429425</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>1.021955778722689</v>
+        <v>1.079376706882848</v>
       </c>
       <c r="T84">
-        <v>4.796216651570725</v>
+        <v>5.078347042839592</v>
       </c>
       <c r="U84">
         <v>0.3196487374989669</v>
       </c>
       <c r="V84">
-        <v>0.09339926408960243</v>
+        <v>0.09227397175117348</v>
       </c>
       <c r="W84">
-        <v>0.2897937806493929</v>
+        <v>0.290153478924689</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
@@ -8201,7 +8201,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>0.2668550402560069</v>
+        <v>0.2636399192890672</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8209,22 +8209,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.424321427677576</v>
+        <v>0.4270599150525656</v>
       </c>
       <c r="C85">
-        <v>-7886.025169227267</v>
+        <v>-8277.505461249671</v>
       </c>
       <c r="D85">
-        <v>14867.64483077273</v>
+        <v>14760.85453875033</v>
       </c>
       <c r="E85">
-        <v>14350.37</v>
+        <v>14635.06</v>
       </c>
       <c r="F85">
-        <v>23629.27</v>
+        <v>23913.96</v>
       </c>
       <c r="G85">
         <v>875.6</v>
@@ -8245,37 +8245,37 @@
         <v>1991.289795918367</v>
       </c>
       <c r="M85">
-        <v>7553.066323522214</v>
+        <v>7644.067122600795</v>
       </c>
       <c r="N85">
-        <v>-5561.776527603846</v>
+        <v>-5652.777326682428</v>
       </c>
       <c r="O85">
-        <v>-1946.621784661346</v>
+        <v>-1978.47206433885</v>
       </c>
       <c r="P85">
-        <v>-3615.1547429425</v>
+        <v>-3674.305262343578</v>
       </c>
       <c r="Q85">
-        <v>-1646.9547429425</v>
+        <v>-1706.105262343578</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>1.079376706882848</v>
+        <v>1.143975251063026</v>
       </c>
       <c r="T85">
-        <v>5.078347042839592</v>
+        <v>5.395743733017067</v>
       </c>
       <c r="U85">
         <v>0.3196487374989669</v>
       </c>
       <c r="V85">
-        <v>0.09227397175117348</v>
+        <v>0.09117547208746904</v>
       </c>
       <c r="W85">
-        <v>0.290153478924689</v>
+        <v>0.2905046129553351</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -8283,7 +8283,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>0.2636399192890672</v>
+        <v>0.2605013488213401</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8291,22 +8291,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.4270599150525656</v>
+        <v>0.4297984024275552</v>
       </c>
       <c r="C86">
-        <v>-8277.505461249668</v>
+        <v>-8667.46260179735</v>
       </c>
       <c r="D86">
-        <v>14760.85453875033</v>
+        <v>14655.58739820265</v>
       </c>
       <c r="E86">
-        <v>14635.06</v>
+        <v>14919.75</v>
       </c>
       <c r="F86">
-        <v>23913.96</v>
+        <v>24198.65</v>
       </c>
       <c r="G86">
         <v>875.6</v>
@@ -8327,37 +8327,37 @@
         <v>1991.289795918367</v>
       </c>
       <c r="M86">
-        <v>7644.067122600793</v>
+        <v>7735.067921679374</v>
       </c>
       <c r="N86">
-        <v>-5652.777326682426</v>
+        <v>-5743.778125761007</v>
       </c>
       <c r="O86">
-        <v>-1978.472064338849</v>
+        <v>-2010.322344016352</v>
       </c>
       <c r="P86">
-        <v>-3674.305262343577</v>
+        <v>-3733.455781744655</v>
       </c>
       <c r="Q86">
-        <v>-1706.105262343577</v>
+        <v>-1765.255781744655</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>1.143975251063025</v>
+        <v>1.217186934467227</v>
       </c>
       <c r="T86">
-        <v>5.395743733017063</v>
+        <v>5.755459981884868</v>
       </c>
       <c r="U86">
         <v>0.3196487374989669</v>
       </c>
       <c r="V86">
-        <v>0.09117547208746905</v>
+        <v>0.09010281947467531</v>
       </c>
       <c r="W86">
-        <v>0.2905046129553351</v>
+        <v>0.2908474850087896</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -8365,7 +8365,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>0.2605013488213401</v>
+        <v>0.2574366270705009</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8373,22 +8373,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.4297984024275552</v>
+        <v>0.4325368898025449</v>
       </c>
       <c r="C87">
-        <v>-8667.46260179735</v>
+        <v>-9055.928947217948</v>
       </c>
       <c r="D87">
-        <v>14655.58739820265</v>
+        <v>14551.81105278205</v>
       </c>
       <c r="E87">
-        <v>14919.75</v>
+        <v>15204.44</v>
       </c>
       <c r="F87">
-        <v>24198.65</v>
+        <v>24483.34</v>
       </c>
       <c r="G87">
         <v>875.6</v>
@@ -8409,37 +8409,37 @@
         <v>1991.289795918367</v>
       </c>
       <c r="M87">
-        <v>7735.067921679374</v>
+        <v>7826.068720757956</v>
       </c>
       <c r="N87">
-        <v>-5743.778125761007</v>
+        <v>-5834.778924839588</v>
       </c>
       <c r="O87">
-        <v>-2010.322344016352</v>
+        <v>-2042.172623693856</v>
       </c>
       <c r="P87">
-        <v>-3733.455781744655</v>
+        <v>-3792.606301145733</v>
       </c>
       <c r="Q87">
-        <v>-1765.255781744655</v>
+        <v>-1824.406301145732</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>1.217186934467227</v>
+        <v>1.300857429786314</v>
       </c>
       <c r="T87">
-        <v>5.755459981884868</v>
+        <v>6.166564266305215</v>
       </c>
       <c r="U87">
         <v>0.3196487374989669</v>
       </c>
       <c r="V87">
-        <v>0.09010281947467531</v>
+        <v>0.0890551122714814</v>
       </c>
       <c r="W87">
-        <v>0.2908474850087896</v>
+        <v>0.2911823832935591</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8447,7 +8447,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.2574366270705009</v>
+        <v>0.2544431779185183</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8455,22 +8455,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.4325368898025449</v>
+        <v>0.4352753771775345</v>
       </c>
       <c r="C88">
-        <v>-9055.928947217948</v>
+        <v>-9442.935943840594</v>
       </c>
       <c r="D88">
-        <v>14551.81105278205</v>
+        <v>14449.4940561594</v>
       </c>
       <c r="E88">
-        <v>15204.44</v>
+        <v>15489.13</v>
       </c>
       <c r="F88">
-        <v>24483.34</v>
+        <v>24768.03</v>
       </c>
       <c r="G88">
         <v>875.6</v>
@@ -8491,37 +8491,37 @@
         <v>1991.289795918367</v>
       </c>
       <c r="M88">
-        <v>7826.068720757956</v>
+        <v>7917.069519836537</v>
       </c>
       <c r="N88">
-        <v>-5834.778924839588</v>
+        <v>-5925.779723918169</v>
       </c>
       <c r="O88">
-        <v>-2042.172623693856</v>
+        <v>-2074.022903371359</v>
       </c>
       <c r="P88">
-        <v>-3792.606301145733</v>
+        <v>-3851.75682054681</v>
       </c>
       <c r="Q88">
-        <v>-1824.406301145732</v>
+        <v>-1883.55682054681</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>1.300857429786314</v>
+        <v>1.397400309000646</v>
       </c>
       <c r="T88">
-        <v>6.166564266305215</v>
+        <v>6.640915363713308</v>
       </c>
       <c r="U88">
         <v>0.3196487374989669</v>
       </c>
       <c r="V88">
-        <v>0.0890551122714814</v>
+        <v>0.08803149029134943</v>
       </c>
       <c r="W88">
-        <v>0.2911823832935591</v>
+        <v>0.2915095827671845</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8529,7 +8529,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.2544431779185183</v>
+        <v>0.2515185436895698</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8537,22 +8537,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.4352753771775345</v>
+        <v>0.4380138645525242</v>
       </c>
       <c r="C89">
-        <v>-9442.935943840594</v>
+        <v>-9828.514159745269</v>
       </c>
       <c r="D89">
-        <v>14449.4940561594</v>
+        <v>14348.60584025473</v>
       </c>
       <c r="E89">
-        <v>15489.13</v>
+        <v>15773.82</v>
       </c>
       <c r="F89">
-        <v>24768.03</v>
+        <v>25052.72</v>
       </c>
       <c r="G89">
         <v>875.6</v>
@@ -8573,37 +8573,37 @@
         <v>1991.289795918367</v>
       </c>
       <c r="M89">
-        <v>7917.069519836537</v>
+        <v>8008.070318915118</v>
       </c>
       <c r="N89">
-        <v>-5925.779723918169</v>
+        <v>-6016.780522996751</v>
       </c>
       <c r="O89">
-        <v>-2074.022903371359</v>
+        <v>-2105.873183048863</v>
       </c>
       <c r="P89">
-        <v>-3851.75682054681</v>
+        <v>-3910.907339947888</v>
       </c>
       <c r="Q89">
-        <v>-1883.55682054681</v>
+        <v>-1942.707339947888</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>1.397400309000646</v>
+        <v>1.510033668084034</v>
       </c>
       <c r="T89">
-        <v>6.640915363713308</v>
+        <v>7.194324977356086</v>
       </c>
       <c r="U89">
         <v>0.3196487374989669</v>
       </c>
       <c r="V89">
-        <v>0.08803149029134943</v>
+        <v>0.08703113244712954</v>
       </c>
       <c r="W89">
-        <v>0.2915095827671845</v>
+        <v>0.2918293458891366</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8611,7 +8611,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.2515185436895698</v>
+        <v>0.2486603784203701</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8619,22 +8619,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.4380138645525242</v>
+        <v>0.4407523519275138</v>
       </c>
       <c r="C90">
-        <v>-9828.514159745269</v>
+        <v>-10212.69331521041</v>
       </c>
       <c r="D90">
-        <v>14348.60584025473</v>
+        <v>14249.11668478959</v>
       </c>
       <c r="E90">
-        <v>15773.82</v>
+        <v>16058.51</v>
       </c>
       <c r="F90">
-        <v>25052.72</v>
+        <v>25337.41</v>
       </c>
       <c r="G90">
         <v>875.6</v>
@@ -8655,37 +8655,37 @@
         <v>1991.289795918367</v>
       </c>
       <c r="M90">
-        <v>8008.070318915118</v>
+        <v>8099.071117993699</v>
       </c>
       <c r="N90">
-        <v>-6016.780522996751</v>
+        <v>-6107.781322075331</v>
       </c>
       <c r="O90">
-        <v>-2105.873183048863</v>
+        <v>-2137.723462726366</v>
       </c>
       <c r="P90">
-        <v>-3910.907339947888</v>
+        <v>-3970.057859348965</v>
       </c>
       <c r="Q90">
-        <v>-1942.707339947888</v>
+        <v>-2001.857859348965</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>1.510033668084034</v>
+        <v>1.643145819728037</v>
       </c>
       <c r="T90">
-        <v>7.194324977356086</v>
+        <v>7.848354520752093</v>
       </c>
       <c r="U90">
         <v>0.3196487374989669</v>
       </c>
       <c r="V90">
-        <v>0.08703113244712954</v>
+        <v>0.08605325455446518</v>
       </c>
       <c r="W90">
-        <v>0.2918293458891366</v>
+        <v>0.2921419233229549</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8693,7 +8693,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.2486603784203701</v>
+        <v>0.2458664415841862</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8701,22 +8701,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.4407523519275138</v>
+        <v>0.4434908393025035</v>
       </c>
       <c r="C91">
-        <v>-10212.69331521041</v>
+        <v>-10595.50231190264</v>
       </c>
       <c r="D91">
-        <v>14249.11668478959</v>
+        <v>14150.99768809736</v>
       </c>
       <c r="E91">
-        <v>16058.51</v>
+        <v>16343.2</v>
       </c>
       <c r="F91">
-        <v>25337.41</v>
+        <v>25622.1</v>
       </c>
       <c r="G91">
         <v>875.6</v>
@@ -8737,37 +8737,37 @@
         <v>1991.289795918367</v>
       </c>
       <c r="M91">
-        <v>8099.071117993699</v>
+        <v>8190.07191707228</v>
       </c>
       <c r="N91">
-        <v>-6107.781322075331</v>
+        <v>-6198.782121153913</v>
       </c>
       <c r="O91">
-        <v>-2137.723462726366</v>
+        <v>-2169.573742403869</v>
       </c>
       <c r="P91">
-        <v>-3970.057859348965</v>
+        <v>-4029.208378750044</v>
       </c>
       <c r="Q91">
-        <v>-2001.857859348965</v>
+        <v>-2061.008378750043</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>1.643145819728037</v>
+        <v>1.802880401700841</v>
       </c>
       <c r="T91">
-        <v>7.848354520752093</v>
+        <v>8.633189972827305</v>
       </c>
       <c r="U91">
         <v>0.3196487374989669</v>
       </c>
       <c r="V91">
-        <v>0.08605325455446518</v>
+        <v>0.08509710728163777</v>
       </c>
       <c r="W91">
-        <v>0.2921419233229549</v>
+        <v>0.2924475545915772</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8775,7 +8775,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.2458664415841862</v>
+        <v>0.2431345922332507</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8783,22 +8783,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.4434908393025035</v>
+        <v>0.4462293266774932</v>
       </c>
       <c r="C92">
-        <v>-10595.50231190264</v>
+        <v>-10976.96926086865</v>
       </c>
       <c r="D92">
-        <v>14150.99768809736</v>
+        <v>14054.22073913135</v>
       </c>
       <c r="E92">
-        <v>16343.2</v>
+        <v>16627.89</v>
       </c>
       <c r="F92">
-        <v>25622.1</v>
+        <v>25906.79</v>
       </c>
       <c r="G92">
         <v>875.6</v>
@@ -8819,37 +8819,37 @@
         <v>1991.289795918367</v>
       </c>
       <c r="M92">
-        <v>8190.07191707228</v>
+        <v>8281.07271615086</v>
       </c>
       <c r="N92">
-        <v>-6198.782121153913</v>
+        <v>-6289.782920232493</v>
       </c>
       <c r="O92">
-        <v>-2169.573742403869</v>
+        <v>-2201.424022081372</v>
       </c>
       <c r="P92">
-        <v>-4029.208378750044</v>
+        <v>-4088.358898151121</v>
       </c>
       <c r="Q92">
-        <v>-2061.008378750043</v>
+        <v>-2120.15889815112</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>1.802880401700841</v>
+        <v>1.998111557445379</v>
       </c>
       <c r="T92">
-        <v>8.633189972827305</v>
+        <v>9.592433303141449</v>
       </c>
       <c r="U92">
         <v>0.3196487374989669</v>
       </c>
       <c r="V92">
-        <v>0.08509710728163777</v>
+        <v>0.08416197423458682</v>
       </c>
       <c r="W92">
-        <v>0.2924475545915772</v>
+        <v>0.2927464686894606</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -8857,7 +8857,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.2431345922332507</v>
+        <v>0.2404627835273909</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8865,22 +8865,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.4462293266774932</v>
+        <v>0.4489678140524829</v>
       </c>
       <c r="C93">
-        <v>-10976.96926086865</v>
+        <v>-11357.12150938638</v>
       </c>
       <c r="D93">
-        <v>14054.22073913135</v>
+        <v>13958.75849061362</v>
       </c>
       <c r="E93">
-        <v>16627.89</v>
+        <v>16912.58</v>
       </c>
       <c r="F93">
-        <v>25906.79</v>
+        <v>26191.48</v>
       </c>
       <c r="G93">
         <v>875.6</v>
@@ -8901,37 +8901,37 @@
         <v>1991.289795918367</v>
       </c>
       <c r="M93">
-        <v>8281.07271615086</v>
+        <v>8372.073515229442</v>
       </c>
       <c r="N93">
-        <v>-6289.782920232493</v>
+        <v>-6380.783719311074</v>
       </c>
       <c r="O93">
-        <v>-2201.424022081372</v>
+        <v>-2233.274301758876</v>
       </c>
       <c r="P93">
-        <v>-4088.358898151121</v>
+        <v>-4147.509417552199</v>
       </c>
       <c r="Q93">
-        <v>-2120.15889815112</v>
+        <v>-2179.309417552199</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>1.998111557445379</v>
+        <v>2.242150502126051</v>
       </c>
       <c r="T93">
-        <v>9.592433303141449</v>
+        <v>10.79148746603413</v>
       </c>
       <c r="U93">
         <v>0.3196487374989669</v>
       </c>
       <c r="V93">
-        <v>0.08416197423458682</v>
+        <v>0.08324717016681955</v>
       </c>
       <c r="W93">
-        <v>0.2927464686894606</v>
+        <v>0.2930388846547813</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -8939,7 +8939,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.2404627835273909</v>
+        <v>0.2378490576194845</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8947,22 +8947,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.4489678140524829</v>
+        <v>0.4517063014274726</v>
       </c>
       <c r="C94">
-        <v>-11357.12150938638</v>
+        <v>-11735.98566672921</v>
       </c>
       <c r="D94">
-        <v>13958.75849061362</v>
+        <v>13864.58433327079</v>
       </c>
       <c r="E94">
-        <v>16912.58</v>
+        <v>17197.27</v>
       </c>
       <c r="F94">
-        <v>26191.48</v>
+        <v>26476.17</v>
       </c>
       <c r="G94">
         <v>875.6</v>
@@ -8983,37 +8983,37 @@
         <v>1991.289795918367</v>
       </c>
       <c r="M94">
-        <v>8372.073515229442</v>
+        <v>8463.074314308024</v>
       </c>
       <c r="N94">
-        <v>-6380.783719311074</v>
+        <v>-6471.784518389656</v>
       </c>
       <c r="O94">
-        <v>-2233.274301758876</v>
+        <v>-2265.12458143638</v>
       </c>
       <c r="P94">
-        <v>-4147.509417552199</v>
+        <v>-4206.659936953276</v>
       </c>
       <c r="Q94">
-        <v>-2179.309417552199</v>
+        <v>-2238.459936953276</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>2.242150502126051</v>
+        <v>2.555914859572631</v>
       </c>
       <c r="T94">
-        <v>10.79148746603413</v>
+        <v>12.33312853261044</v>
       </c>
       <c r="U94">
         <v>0.3196487374989669</v>
       </c>
       <c r="V94">
-        <v>0.08324717016681955</v>
+        <v>0.08235203930481075</v>
       </c>
       <c r="W94">
-        <v>0.2930388846547813</v>
+        <v>0.2933250121047188</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9021,7 +9021,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.2378490576194845</v>
+        <v>0.2352915408708879</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9029,22 +9029,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.4517063014274726</v>
+        <v>0.4544447888024623</v>
       </c>
       <c r="C95">
-        <v>-11735.98566672921</v>
+        <v>-12113.58762889422</v>
       </c>
       <c r="D95">
-        <v>13864.58433327079</v>
+        <v>13771.67237110578</v>
       </c>
       <c r="E95">
-        <v>17197.27</v>
+        <v>17481.96</v>
       </c>
       <c r="F95">
-        <v>26476.17</v>
+        <v>26760.86</v>
       </c>
       <c r="G95">
         <v>875.6</v>
@@ -9065,37 +9065,37 @@
         <v>1991.289795918367</v>
       </c>
       <c r="M95">
-        <v>8463.074314308024</v>
+        <v>8554.075113386603</v>
       </c>
       <c r="N95">
-        <v>-6471.784518389656</v>
+        <v>-6562.785317468236</v>
       </c>
       <c r="O95">
-        <v>-2265.12458143638</v>
+        <v>-2296.974861113883</v>
       </c>
       <c r="P95">
-        <v>-4206.659936953276</v>
+        <v>-4265.810456354353</v>
       </c>
       <c r="Q95">
-        <v>-2238.459936953276</v>
+        <v>-2297.610456354353</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>2.555914859572631</v>
+        <v>2.97426733616807</v>
       </c>
       <c r="T95">
-        <v>12.33312853261044</v>
+        <v>14.38864995471218</v>
       </c>
       <c r="U95">
         <v>0.3196487374989669</v>
       </c>
       <c r="V95">
-        <v>0.08235203930481075</v>
+        <v>0.08147595378029149</v>
       </c>
       <c r="W95">
-        <v>0.2933250121047188</v>
+        <v>0.2936050517365725</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9103,7 +9103,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.2352915408708879</v>
+        <v>0.2327884393722615</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9111,22 +9111,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.4544447888024623</v>
+        <v>0.4571832761774519</v>
       </c>
       <c r="C96">
-        <v>-12113.58762889422</v>
+        <v>-12489.95260234282</v>
       </c>
       <c r="D96">
-        <v>13771.67237110578</v>
+        <v>13679.99739765718</v>
       </c>
       <c r="E96">
-        <v>17481.96</v>
+        <v>17766.65</v>
       </c>
       <c r="F96">
-        <v>26760.86</v>
+        <v>27045.55</v>
       </c>
       <c r="G96">
         <v>875.6</v>
@@ -9147,37 +9147,37 @@
         <v>1991.289795918367</v>
       </c>
       <c r="M96">
-        <v>8554.075113386603</v>
+        <v>8645.075912465185</v>
       </c>
       <c r="N96">
-        <v>-6562.785317468236</v>
+        <v>-6653.786116546818</v>
       </c>
       <c r="O96">
-        <v>-2296.974861113883</v>
+        <v>-2328.825140791386</v>
       </c>
       <c r="P96">
-        <v>-4265.810456354353</v>
+        <v>-4324.960975755432</v>
       </c>
       <c r="Q96">
-        <v>-2297.610456354353</v>
+        <v>-2356.760975755431</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>2.97426733616807</v>
+        <v>3.559960803401686</v>
       </c>
       <c r="T96">
-        <v>14.38864995471218</v>
+        <v>17.26637994565463</v>
       </c>
       <c r="U96">
         <v>0.3196487374989669</v>
       </c>
       <c r="V96">
-        <v>0.08147595378029149</v>
+        <v>0.08061831216155158</v>
       </c>
       <c r="W96">
-        <v>0.2936050517365725</v>
+        <v>0.2938791957972293</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9185,7 +9185,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.2327884393722615</v>
+        <v>0.2303380347472902</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9193,22 +9193,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.4571832761774519</v>
+        <v>0.4599217635524415</v>
       </c>
       <c r="C97">
-        <v>-12489.95260234282</v>
+        <v>-12865.10512679943</v>
       </c>
       <c r="D97">
-        <v>13679.99739765718</v>
+        <v>13589.53487320058</v>
       </c>
       <c r="E97">
-        <v>17766.65</v>
+        <v>18051.34</v>
       </c>
       <c r="F97">
-        <v>27045.55</v>
+        <v>27330.24</v>
       </c>
       <c r="G97">
         <v>875.6</v>
@@ -9229,37 +9229,37 @@
         <v>1991.289795918367</v>
       </c>
       <c r="M97">
-        <v>8645.075912465185</v>
+        <v>8736.076711543765</v>
       </c>
       <c r="N97">
-        <v>-6653.786116546818</v>
+        <v>-6744.786915625397</v>
       </c>
       <c r="O97">
-        <v>-2328.825140791386</v>
+        <v>-2360.675420468889</v>
       </c>
       <c r="P97">
-        <v>-4324.960975755432</v>
+        <v>-4384.111495156509</v>
       </c>
       <c r="Q97">
-        <v>-2356.760975755431</v>
+        <v>-2415.911495156508</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>3.559960803401686</v>
+        <v>4.438501004252109</v>
       </c>
       <c r="T97">
-        <v>17.26637994565463</v>
+        <v>21.5829749320683</v>
       </c>
       <c r="U97">
         <v>0.3196487374989669</v>
       </c>
       <c r="V97">
-        <v>0.08061831216155158</v>
+        <v>0.07977853807653541</v>
       </c>
       <c r="W97">
-        <v>0.2938791957972293</v>
+        <v>0.2941476285232891</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9267,7 +9267,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.2303380347472902</v>
+        <v>0.2279386802186726</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9275,22 +9275,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.4599217635524415</v>
+        <v>0.4626602509274312</v>
       </c>
       <c r="C98">
-        <v>-12865.10512679942</v>
+        <v>-13239.06909715147</v>
       </c>
       <c r="D98">
-        <v>13589.53487320058</v>
+        <v>13500.26090284853</v>
       </c>
       <c r="E98">
-        <v>18051.34</v>
+        <v>18336.03</v>
       </c>
       <c r="F98">
-        <v>27330.24</v>
+        <v>27614.93</v>
       </c>
       <c r="G98">
         <v>875.6</v>
@@ -9311,37 +9311,37 @@
         <v>1991.289795918367</v>
       </c>
       <c r="M98">
-        <v>8736.076711543765</v>
+        <v>8827.077510622346</v>
       </c>
       <c r="N98">
-        <v>-6744.786915625397</v>
+        <v>-6835.787714703979</v>
       </c>
       <c r="O98">
-        <v>-2360.675420468889</v>
+        <v>-2392.525700146392</v>
       </c>
       <c r="P98">
-        <v>-4384.111495156509</v>
+        <v>-4443.262014557587</v>
       </c>
       <c r="Q98">
-        <v>-2415.911495156508</v>
+        <v>-2475.062014557586</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>4.438501004252097</v>
+        <v>5.90273467233613</v>
       </c>
       <c r="T98">
-        <v>21.58297493206824</v>
+        <v>28.77729990942432</v>
       </c>
       <c r="U98">
         <v>0.3196487374989669</v>
       </c>
       <c r="V98">
-        <v>0.07977853807653541</v>
+        <v>0.0789560789211072</v>
       </c>
       <c r="W98">
-        <v>0.2941476285232891</v>
+        <v>0.2944105265539662</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9349,7 +9349,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.2279386802186726</v>
+        <v>0.2255887969174492</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9357,22 +9357,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.4626602509274312</v>
+        <v>0.4653987383024208</v>
       </c>
       <c r="C99">
-        <v>-13239.06909715147</v>
+        <v>-13611.86778449187</v>
       </c>
       <c r="D99">
-        <v>13500.26090284853</v>
+        <v>13412.15221550812</v>
       </c>
       <c r="E99">
-        <v>18336.03</v>
+        <v>18620.72</v>
       </c>
       <c r="F99">
-        <v>27614.93</v>
+        <v>27899.62</v>
       </c>
       <c r="G99">
         <v>875.6</v>
@@ -9393,37 +9393,37 @@
         <v>1991.289795918367</v>
       </c>
       <c r="M99">
-        <v>8827.077510622346</v>
+        <v>8918.078309700926</v>
       </c>
       <c r="N99">
-        <v>-6835.787714703979</v>
+        <v>-6926.788513782559</v>
       </c>
       <c r="O99">
-        <v>-2392.525700146392</v>
+        <v>-2424.375979823895</v>
       </c>
       <c r="P99">
-        <v>-4443.262014557587</v>
+        <v>-4502.412533958664</v>
       </c>
       <c r="Q99">
-        <v>-2475.062014557586</v>
+        <v>-2534.212533958663</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>5.90273467233613</v>
+        <v>8.831202008504194</v>
       </c>
       <c r="T99">
-        <v>28.77729990942432</v>
+        <v>43.16594986413647</v>
       </c>
       <c r="U99">
         <v>0.3196487374989669</v>
       </c>
       <c r="V99">
-        <v>0.0789560789211072</v>
+        <v>0.07815040464640205</v>
       </c>
       <c r="W99">
-        <v>0.2944105265539662</v>
+        <v>0.294668059318711</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9431,7 +9431,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.2255887969174492</v>
+        <v>0.2232868704182915</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9439,22 +9439,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.4653987383024208</v>
+        <v>0.4681372256774106</v>
       </c>
       <c r="C100">
-        <v>-13611.86778449187</v>
+        <v>-13983.52385634287</v>
       </c>
       <c r="D100">
-        <v>13412.15221550812</v>
+        <v>13325.18614365713</v>
       </c>
       <c r="E100">
-        <v>18620.72</v>
+        <v>18905.41</v>
       </c>
       <c r="F100">
-        <v>27899.62</v>
+        <v>28184.31</v>
       </c>
       <c r="G100">
         <v>875.6</v>
@@ -9475,37 +9475,37 @@
         <v>1991.289795918367</v>
       </c>
       <c r="M100">
-        <v>8918.078309700926</v>
+        <v>9009.079108779508</v>
       </c>
       <c r="N100">
-        <v>-6926.788513782559</v>
+        <v>-7017.78931286114</v>
       </c>
       <c r="O100">
-        <v>-2424.375979823895</v>
+        <v>-2456.226259501399</v>
       </c>
       <c r="P100">
-        <v>-4502.412533958664</v>
+        <v>-4561.563053359741</v>
       </c>
       <c r="Q100">
-        <v>-2534.212533958663</v>
+        <v>-2593.363053359741</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>8.831202008504194</v>
+        <v>17.61660401700839</v>
       </c>
       <c r="T100">
-        <v>43.16594986413647</v>
+        <v>86.33189972827296</v>
       </c>
       <c r="U100">
         <v>0.3196487374989669</v>
       </c>
       <c r="V100">
-        <v>0.07815040464640205</v>
+        <v>0.07736100661967071</v>
       </c>
       <c r="W100">
-        <v>0.294668059318711</v>
+        <v>0.2949203894013399</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9513,91 +9513,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.2232868704182915</v>
+        <v>0.2210314474847734</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.4681372256774106</v>
-      </c>
-      <c r="C101">
-        <v>-13983.52385634287</v>
-      </c>
-      <c r="D101">
-        <v>13325.18614365713</v>
-      </c>
-      <c r="E101">
-        <v>18905.41</v>
-      </c>
-      <c r="F101">
-        <v>28184.31</v>
-      </c>
-      <c r="G101">
-        <v>875.6</v>
-      </c>
-      <c r="H101">
-        <v>19190.1</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>3959.489795918368</v>
-      </c>
-      <c r="K101">
-        <v>1968.2</v>
-      </c>
-      <c r="L101">
-        <v>1991.289795918367</v>
-      </c>
-      <c r="M101">
-        <v>9009.079108779508</v>
-      </c>
-      <c r="N101">
-        <v>-7017.78931286114</v>
-      </c>
-      <c r="O101">
-        <v>-2456.226259501399</v>
-      </c>
-      <c r="P101">
-        <v>-4561.563053359741</v>
-      </c>
-      <c r="Q101">
-        <v>-2593.363053359741</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>17.61660401700839</v>
-      </c>
-      <c r="T101">
-        <v>86.33189972827296</v>
-      </c>
-      <c r="U101">
-        <v>0.3196487374989669</v>
-      </c>
-      <c r="V101">
-        <v>0.07736100661967071</v>
-      </c>
-      <c r="W101">
-        <v>0.2949203894013399</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>C2/C</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.2210314474847734</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
